--- a/obras-arquivos/Controle GEOPB.xlsx
+++ b/obras-arquivos/Controle GEOPB.xlsx
@@ -5,20 +5,23 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dougl\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dougl\Desktop\Eng\Work\RELATÓRIOS\prefeitura-docs\obras-arquivos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC90A579-8D4E-4EA8-A506-9CF288A8731D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED220898-AC96-4C1C-91A8-D8FDF10DAA94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{54458EFF-5590-4B6C-91D8-F0B852F5A9C3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="6" xr2:uid="{54458EFF-5590-4B6C-91D8-F0B852F5A9C3}"/>
   </bookViews>
   <sheets>
     <sheet name="ESCOLA FLORIDO" sheetId="1" r:id="rId1"/>
     <sheet name="CAMPO DE FUTEBOL" sheetId="5" r:id="rId2"/>
-    <sheet name="QUADRA POLIESPORTIVA" sheetId="8" r:id="rId3"/>
-    <sheet name="CAPS" sheetId="9" r:id="rId4"/>
-    <sheet name="Controle de Obras (GeoPB)" sheetId="2" r:id="rId5"/>
-    <sheet name="Checklist de Documentos (GeoPB)" sheetId="3" r:id="rId6"/>
+    <sheet name="CAPS" sheetId="9" r:id="rId3"/>
+    <sheet name="QUADRA POLIESPORTIVA" sheetId="8" r:id="rId4"/>
+    <sheet name="ESCOLA 6 SALAS" sheetId="10" r:id="rId5"/>
+    <sheet name="GARAGEM MUNICIPAL" sheetId="11" r:id="rId6"/>
+    <sheet name="PAVIMENTAÇÃO OFICIAL DE JUSTIÇA" sheetId="12" r:id="rId7"/>
+    <sheet name="Controle de Obras (GeoPB)" sheetId="2" r:id="rId8"/>
+    <sheet name="Checklist de Documentos (GeoPB)" sheetId="3" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="891" uniqueCount="224">
   <si>
     <t>Contratação de empresa especializada para prestar serviço de engenharia na reforma da Escola Municipal Flórido Nitão Diniz, localizada no Município de Coremas, conforme plano de trabalho e projeto básico do Termo de Convênio 0470/2019 celebrado com a Secretaria de Estado da Educação.</t>
   </si>
@@ -519,6 +522,201 @@
   </si>
   <si>
     <t>&lt;&lt; --   Enviar pro GEOPB</t>
+  </si>
+  <si>
+    <t>C:\Users\dougl\Desktop\Eng\Work\RELATÓRIOS\prefeitura-docs\obras-arquivos\or0019-campo-futebol-conc100022025-geo\campo-futebol-geopb\3-campo-futebol-medicoes\campo-futebol-bm04</t>
+  </si>
+  <si>
+    <t>29/07/2026 À 08/09/2026</t>
+  </si>
+  <si>
+    <t>campo-futebol-nota-fiscal-bm04.pdf</t>
+  </si>
+  <si>
+    <t>campo-futebol-planilha-medicao-bm04.xlsx</t>
+  </si>
+  <si>
+    <t>07/05/2026 À 25/06/2026</t>
+  </si>
+  <si>
+    <t>caps-nota-fiscal-bm01.pdf</t>
+  </si>
+  <si>
+    <t>caps-planilha-medicao-bm01.xlsx</t>
+  </si>
+  <si>
+    <t>C:\Users\dougl\Desktop\Eng\Work\RELATÓRIOS\prefeitura-docs\obras-arquivos\or0020-caps-conc100012026-geo\caps-geopb\3-caps-medicoes\caps-bm01</t>
+  </si>
+  <si>
+    <t>26/06/2026 À 08/09/2026</t>
+  </si>
+  <si>
+    <t>caps-planilha-medicao-bm02.xlsx</t>
+  </si>
+  <si>
+    <t>caps-nota-fiscal-bm02.pdf</t>
+  </si>
+  <si>
+    <t>C:\Users\dougl\Desktop\Eng\Work\RELATÓRIOS\prefeitura-docs\obras-arquivos\or0020-caps-conc100012026-geo\caps-geopb\3-caps-medicoes\caps-bm02</t>
+  </si>
+  <si>
+    <t>caps-imagens-bm01.rar</t>
+  </si>
+  <si>
+    <t>CONSTRUÇÃO - ESCOLA 6 SALAS</t>
+  </si>
+  <si>
+    <t>Contratação direta do terceiro colocado na Tomada de Preços nº 004/2022, para prestação de serviços de engenharia complementar para conclusão da construção de uma Unidade Escolar de 06 (seis) salas de aula para o município de Coremas-PB, conforme planilhas orçamentárias de custos (Convênio com Estado da Paraíba CV n (199/2021).</t>
+  </si>
+  <si>
+    <t>600,00m²</t>
+  </si>
+  <si>
+    <t>PB20250777479</t>
+  </si>
+  <si>
+    <t>C:\Users\dougl\Desktop\Eng\Work\RELATÓRIOS\prefeitura-docs\obras-arquivos\or0004-escola-6salas-tp042022-geo00042022\escola-6salas-geo\1-escola-6salas-cadastro</t>
+  </si>
+  <si>
+    <t>11044/2025</t>
+  </si>
+  <si>
+    <t>escola-6salas-contrato.pdf</t>
+  </si>
+  <si>
+    <t>escola-6salas-ordem-servico.pdf</t>
+  </si>
+  <si>
+    <t>escola-6salas-planilha-contratada.xlsx</t>
+  </si>
+  <si>
+    <t>escola-6salas-projeto-basico.pdf</t>
+  </si>
+  <si>
+    <t>campo-futebol-imagens-bm04.rar</t>
+  </si>
+  <si>
+    <t>CONSTRUÇÃO - GARAGEM MUNICIPAL</t>
+  </si>
+  <si>
+    <t>Contratação de pessoa jurídica especializada na área da construção civil, para reforma da garagem municipal da prefeitura municipal de Coremas/PB.</t>
+  </si>
+  <si>
+    <t>250,00m²</t>
+  </si>
+  <si>
+    <t>RUA MARIA DO SOCORRO DA SILVA SÁ</t>
+  </si>
+  <si>
+    <t>PB20260808576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00065/2026 </t>
+  </si>
+  <si>
+    <t>C:\Users\dougl\Desktop\Eng\Work\RELATÓRIOS\prefeitura-docs\obras-arquivos\or0015-garagem-conc022025-geo\garagem-geopb\1-garagem-cadastro</t>
+  </si>
+  <si>
+    <t>garagem-contrato.pdf</t>
+  </si>
+  <si>
+    <t>garagem-ordem-servico.pdf</t>
+  </si>
+  <si>
+    <t>garagem-planilha-contratada.xlsx</t>
+  </si>
+  <si>
+    <t>garagem-projeto-basico.pdf</t>
+  </si>
+  <si>
+    <t>Lat. -7.02130, Long. -37.95504</t>
+  </si>
+  <si>
+    <t>C:\Users\dougl\Desktop\Eng\Work\RELATÓRIOS\prefeitura-docs\obras-arquivos\or0015-garagem-conc022025-geo\garagem-geopb\2-garagem-condicoes-iniciais</t>
+  </si>
+  <si>
+    <t>garagem-orcamento-detalhado.pdf</t>
+  </si>
+  <si>
+    <t>garagem-imagens-iniciais.rar</t>
+  </si>
+  <si>
+    <t>C:\Users\dougl\Desktop\Eng\Work\RELATÓRIOS\prefeitura-docs\obras-arquivos\or0015-garagem-conc022025-geo\garagem-geopb\3-garagem-medicoes\garagem-bm01</t>
+  </si>
+  <si>
+    <t>garagem-nota-fiscal.pdf</t>
+  </si>
+  <si>
+    <t>09/03/2026 À 08/06/2026</t>
+  </si>
+  <si>
+    <t>garagem-planilha-medicao-bm01.xlsx</t>
+  </si>
+  <si>
+    <t>garagem-imagens-bm01.rar</t>
+  </si>
+  <si>
+    <t>PAVIMENTAÇÃO - RUA OFICIAL DE JUSTIÇA VICENTE GREGÓRIO ANTÃO</t>
+  </si>
+  <si>
+    <t>Rua Oficial de Justiça Vicente Gregório Antão; Rua Francisca Garrido de Souza; Rua Francisco Batista Silva; Rua Bartolomeu Buriti; Rua Maria Farias de Assis; Rua Roberto Wilson Moura; Rua Cícero Eufrásio da Silva; Rua Firmino da Silva Lacerda.</t>
+  </si>
+  <si>
+    <t>Contratação de uma pessoa jurídica para prestar serviços de engenharia na Execução de pavimentação em paralelepípedo nas Rua Oficial de Justiça Vicente Gregório Antão Rua Francisca Garrido de Sousa Rua Francisco Batista Silva Rua Bartolomeu Buriti Rua Maria Farias de Assis Rua Roberto Wilson Moura Rua Cícero Eufrásio da Silva Rua Firmino da Silva Lacerda na sede da Cidade de CoremasPB conforme planilha orçamentária de custo Fonte de Recursos Contrato de repasse 1080659092021CAIXA e Próprio Diversos do Município</t>
+  </si>
+  <si>
+    <t>Nº GEO</t>
+  </si>
+  <si>
+    <t>LINK GEO</t>
+  </si>
+  <si>
+    <t>https://geopb.tce.pb.gov.br/consulta/detalhes/6876</t>
+  </si>
+  <si>
+    <t>859,46m²</t>
+  </si>
+  <si>
+    <t>PB20250773029</t>
+  </si>
+  <si>
+    <t>150/2023</t>
+  </si>
+  <si>
+    <t>pavimentacao-oficial-contrato.pdf</t>
+  </si>
+  <si>
+    <t>pavimentacao-oficial-projeto-basico.pdf</t>
+  </si>
+  <si>
+    <t>pavimentacao-oficial-ordem-servico.pdf</t>
+  </si>
+  <si>
+    <t>pavimentacao-oficial-planilha-contratada.xlsx</t>
+  </si>
+  <si>
+    <t>C:\Users\dougl\Desktop\Eng\Work\RELATÓRIOS\prefeitura-docs\obras-arquivos\or0021-pavimentacao-oficial-vicente-gregorio-tp400042023-geo01502023\pavimentacao-oficial-geo\1-pavimentacao-oficial-cadastro</t>
+  </si>
+  <si>
+    <t>Lat. -7.01419, Long. -37.93917</t>
+  </si>
+  <si>
+    <t>pavimentacao-oficial-imagens-iniciais.rar</t>
+  </si>
+  <si>
+    <t>pavimentacao-oficial-orcamento-detalhado.pdf</t>
+  </si>
+  <si>
+    <t>C:\Users\dougl\Desktop\Eng\Work\RELATÓRIOS\prefeitura-docs\obras-arquivos\or0021-pavimentacao-oficial-vicente-gregorio-tp400042023-geo01502023\pavimentacao-oficial-geo\2-pavimentacao-oficial-condicoes-iniciais</t>
+  </si>
+  <si>
+    <t>C:\Users\dougl\Desktop\Eng\Work\RELATÓRIOS\prefeitura-docs\obras-arquivos\or0021-pavimentacao-oficial-vicente-gregorio-tp400042023-geo01502023\pavimentacao-oficial-geo\3-pavimentacao-oficial-medicoes\pavimentacao-oficial-bm01</t>
+  </si>
+  <si>
+    <t>C:\Users\dougl\Desktop\Eng\Work\RELATÓRIOS\prefeitura-docs\obras-arquivos\or0021-pavimentacao-oficial-vicente-gregorio-tp400042023-geo01502023\pavimentacao-oficial-geo\3-pavimentacao-oficial-medicoes\pavimentacao-oficial-bm02</t>
+  </si>
+  <si>
+    <t>&lt;&lt; --   AGUARDAR PAGAMENTO</t>
   </si>
 </sst>
 </file>
@@ -528,9 +726,9 @@
   <numFmts count="3">
     <numFmt numFmtId="8" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="&quot;R$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -604,8 +802,31 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -666,6 +887,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="63">
     <border>
@@ -1442,11 +1669,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="203">
+  <cellXfs count="236">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1565,479 +1793,579 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="1" fillId="7" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="1" fillId="7" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="1" fillId="7" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="1" fillId="7" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="1" fillId="7" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="1" fillId="7" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="1" fillId="7" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="1" fillId="7" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="1" fillId="7" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="1" fillId="7" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="1" fillId="7" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="1" fillId="7" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Hiperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -2364,82 +2692,82 @@
   <sheetData>
     <row r="1" spans="5:16" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="5:16" x14ac:dyDescent="0.3">
-      <c r="E2" s="138" t="s">
+      <c r="E2" s="118" t="s">
         <v>53</v>
       </c>
-      <c r="F2" s="139"/>
-      <c r="G2" s="139"/>
-      <c r="H2" s="139"/>
-      <c r="I2" s="139"/>
-      <c r="J2" s="139"/>
-      <c r="K2" s="139"/>
-      <c r="L2" s="140"/>
+      <c r="F2" s="119"/>
+      <c r="G2" s="119"/>
+      <c r="H2" s="119"/>
+      <c r="I2" s="119"/>
+      <c r="J2" s="119"/>
+      <c r="K2" s="119"/>
+      <c r="L2" s="120"/>
     </row>
     <row r="3" spans="5:16" x14ac:dyDescent="0.3">
-      <c r="E3" s="141"/>
-      <c r="F3" s="142"/>
-      <c r="G3" s="142"/>
-      <c r="H3" s="142"/>
-      <c r="I3" s="142"/>
-      <c r="J3" s="142"/>
-      <c r="K3" s="142"/>
-      <c r="L3" s="143"/>
+      <c r="E3" s="121"/>
+      <c r="F3" s="122"/>
+      <c r="G3" s="122"/>
+      <c r="H3" s="122"/>
+      <c r="I3" s="122"/>
+      <c r="J3" s="122"/>
+      <c r="K3" s="122"/>
+      <c r="L3" s="123"/>
     </row>
     <row r="4" spans="5:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E4" s="144"/>
-      <c r="F4" s="145"/>
-      <c r="G4" s="145"/>
-      <c r="H4" s="145"/>
-      <c r="I4" s="145"/>
-      <c r="J4" s="145"/>
-      <c r="K4" s="145"/>
-      <c r="L4" s="146"/>
+      <c r="E4" s="124"/>
+      <c r="F4" s="125"/>
+      <c r="G4" s="125"/>
+      <c r="H4" s="125"/>
+      <c r="I4" s="125"/>
+      <c r="J4" s="125"/>
+      <c r="K4" s="125"/>
+      <c r="L4" s="126"/>
     </row>
     <row r="5" spans="5:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E5" s="147" t="s">
+      <c r="E5" s="132" t="s">
         <v>1</v>
       </c>
-      <c r="F5" s="148"/>
-      <c r="G5" s="148"/>
-      <c r="H5" s="148"/>
-      <c r="I5" s="148"/>
-      <c r="J5" s="148"/>
-      <c r="K5" s="148"/>
-      <c r="L5" s="149"/>
+      <c r="F5" s="133"/>
+      <c r="G5" s="133"/>
+      <c r="H5" s="133"/>
+      <c r="I5" s="133"/>
+      <c r="J5" s="133"/>
+      <c r="K5" s="133"/>
+      <c r="L5" s="134"/>
       <c r="M5" s="23"/>
       <c r="N5" s="23"/>
       <c r="O5" s="23"/>
       <c r="P5" s="23"/>
     </row>
     <row r="6" spans="5:16" ht="69" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E6" s="101" t="s">
+      <c r="E6" s="135" t="s">
         <v>0</v>
       </c>
-      <c r="F6" s="102"/>
-      <c r="G6" s="102"/>
-      <c r="H6" s="102"/>
-      <c r="I6" s="102"/>
-      <c r="J6" s="102"/>
-      <c r="K6" s="102"/>
-      <c r="L6" s="103"/>
+      <c r="F6" s="136"/>
+      <c r="G6" s="136"/>
+      <c r="H6" s="136"/>
+      <c r="I6" s="136"/>
+      <c r="J6" s="136"/>
+      <c r="K6" s="136"/>
+      <c r="L6" s="137"/>
       <c r="M6" s="24"/>
       <c r="N6" s="24"/>
       <c r="O6" s="24"/>
       <c r="P6" s="24"/>
     </row>
     <row r="7" spans="5:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E7" s="104" t="s">
+      <c r="E7" s="138" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="105"/>
-      <c r="G7" s="105"/>
-      <c r="H7" s="105"/>
-      <c r="I7" s="105" t="s">
+      <c r="F7" s="139"/>
+      <c r="G7" s="139"/>
+      <c r="H7" s="139"/>
+      <c r="I7" s="139" t="s">
         <v>3</v>
       </c>
-      <c r="J7" s="105"/>
-      <c r="K7" s="105"/>
-      <c r="L7" s="106"/>
+      <c r="J7" s="139"/>
+      <c r="K7" s="139"/>
+      <c r="L7" s="140"/>
       <c r="M7" s="25"/>
       <c r="N7" s="25"/>
       <c r="O7" s="25"/>
@@ -2449,11 +2777,11 @@
       <c r="E8" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="F8" s="124" t="s">
+      <c r="F8" s="141" t="s">
         <v>5</v>
       </c>
-      <c r="G8" s="125"/>
-      <c r="H8" s="113"/>
+      <c r="G8" s="142"/>
+      <c r="H8" s="101"/>
       <c r="I8" s="26" t="s">
         <v>62</v>
       </c>
@@ -2471,12 +2799,12 @@
       <c r="E9" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="F9" s="126" t="s">
+      <c r="F9" s="127" t="s">
         <v>7</v>
       </c>
-      <c r="G9" s="127"/>
-      <c r="H9" s="128"/>
-      <c r="I9" s="126" t="s">
+      <c r="G9" s="128"/>
+      <c r="H9" s="129"/>
+      <c r="I9" s="127" t="s">
         <v>54</v>
       </c>
       <c r="J9" s="32" t="s">
@@ -2491,12 +2819,12 @@
       <c r="E10" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="F10" s="126" t="s">
+      <c r="F10" s="127" t="s">
         <v>11</v>
       </c>
-      <c r="G10" s="127"/>
-      <c r="H10" s="128"/>
-      <c r="I10" s="129"/>
+      <c r="G10" s="128"/>
+      <c r="H10" s="129"/>
+      <c r="I10" s="130"/>
       <c r="J10" s="32" t="s">
         <v>58</v>
       </c>
@@ -2509,12 +2837,12 @@
       <c r="E11" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="F11" s="126" t="s">
+      <c r="F11" s="127" t="s">
         <v>10</v>
       </c>
-      <c r="G11" s="127"/>
-      <c r="H11" s="127"/>
-      <c r="I11" s="130" t="s">
+      <c r="G11" s="128"/>
+      <c r="H11" s="128"/>
+      <c r="I11" s="143" t="s">
         <v>55</v>
       </c>
       <c r="J11" s="32" t="s">
@@ -2529,12 +2857,12 @@
       <c r="E12" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="F12" s="129" t="s">
+      <c r="F12" s="130" t="s">
         <v>14</v>
       </c>
-      <c r="G12" s="132"/>
-      <c r="H12" s="132"/>
-      <c r="I12" s="131"/>
+      <c r="G12" s="131"/>
+      <c r="H12" s="131"/>
+      <c r="I12" s="144"/>
       <c r="J12" s="32" t="s">
         <v>60</v>
       </c>
@@ -2544,348 +2872,394 @@
       <c r="L12" s="28"/>
     </row>
     <row r="13" spans="5:16" x14ac:dyDescent="0.3">
-      <c r="E13" s="87" t="s">
+      <c r="E13" s="93" t="s">
         <v>12</v>
       </c>
-      <c r="F13" s="107">
+      <c r="F13" s="95">
         <v>300273.46999999997</v>
       </c>
-      <c r="G13" s="108"/>
-      <c r="H13" s="109"/>
-      <c r="I13" s="113" t="s">
+      <c r="G13" s="96"/>
+      <c r="H13" s="97"/>
+      <c r="I13" s="101" t="s">
         <v>56</v>
       </c>
-      <c r="J13" s="115" t="s">
+      <c r="J13" s="103" t="s">
         <v>61</v>
       </c>
-      <c r="K13" s="117"/>
-      <c r="L13" s="119"/>
+      <c r="K13" s="105"/>
+      <c r="L13" s="145"/>
     </row>
     <row r="14" spans="5:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E14" s="88"/>
-      <c r="F14" s="110"/>
-      <c r="G14" s="111"/>
-      <c r="H14" s="112"/>
-      <c r="I14" s="114"/>
-      <c r="J14" s="116"/>
-      <c r="K14" s="118"/>
-      <c r="L14" s="120"/>
+      <c r="E14" s="94"/>
+      <c r="F14" s="98"/>
+      <c r="G14" s="99"/>
+      <c r="H14" s="100"/>
+      <c r="I14" s="102"/>
+      <c r="J14" s="104"/>
+      <c r="K14" s="106"/>
+      <c r="L14" s="146"/>
     </row>
     <row r="15" spans="5:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E15" s="150"/>
-      <c r="F15" s="150"/>
+      <c r="E15" s="116"/>
+      <c r="F15" s="116"/>
     </row>
     <row r="16" spans="5:16" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E16" s="60" t="s">
+      <c r="E16" s="83" t="s">
         <v>15</v>
       </c>
-      <c r="F16" s="61"/>
-      <c r="G16" s="61"/>
-      <c r="H16" s="61"/>
-      <c r="I16" s="61"/>
-      <c r="J16" s="61"/>
-      <c r="K16" s="61"/>
-      <c r="L16" s="62"/>
-    </row>
-    <row r="17" spans="5:12" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F16" s="84"/>
+      <c r="G16" s="84"/>
+      <c r="H16" s="84"/>
+      <c r="I16" s="84"/>
+      <c r="J16" s="84"/>
+      <c r="K16" s="84"/>
+      <c r="L16" s="85"/>
+    </row>
+    <row r="17" spans="5:16" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E17" s="9"/>
-      <c r="F17" s="75" t="s">
+      <c r="F17" s="113" t="s">
         <v>2</v>
       </c>
-      <c r="G17" s="76"/>
-      <c r="H17" s="77"/>
+      <c r="G17" s="114"/>
+      <c r="H17" s="115"/>
       <c r="I17" s="14"/>
       <c r="J17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="K17" s="63" t="s">
+      <c r="K17" s="72" t="s">
         <v>25</v>
       </c>
-      <c r="L17" s="65"/>
-    </row>
-    <row r="18" spans="5:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L17" s="74"/>
+    </row>
+    <row r="18" spans="5:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E18" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="F18" s="162" t="s">
+      <c r="F18" s="86" t="s">
         <v>72</v>
       </c>
-      <c r="G18" s="163"/>
-      <c r="H18" s="164"/>
+      <c r="G18" s="87"/>
+      <c r="H18" s="88"/>
       <c r="I18" s="36" t="s">
         <v>30</v>
       </c>
       <c r="J18" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="K18" s="152" t="s">
+      <c r="K18" s="107" t="s">
         <v>81</v>
       </c>
-      <c r="L18" s="153"/>
-    </row>
-    <row r="19" spans="5:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L18" s="108"/>
+    </row>
+    <row r="19" spans="5:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E19" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="F19" s="133" t="s">
+      <c r="F19" s="89" t="s">
         <v>5</v>
       </c>
-      <c r="G19" s="134"/>
-      <c r="H19" s="135"/>
+      <c r="G19" s="90"/>
+      <c r="H19" s="91"/>
       <c r="I19" s="37" t="s">
         <v>52</v>
       </c>
       <c r="J19" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="K19" s="154"/>
-      <c r="L19" s="155"/>
-    </row>
-    <row r="20" spans="5:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K19" s="109"/>
+      <c r="L19" s="110"/>
+    </row>
+    <row r="20" spans="5:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E20" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="F20" s="133" t="s">
+      <c r="F20" s="89" t="s">
         <v>7</v>
       </c>
-      <c r="G20" s="134"/>
-      <c r="H20" s="135"/>
+      <c r="G20" s="90"/>
+      <c r="H20" s="91"/>
       <c r="I20" s="37" t="s">
         <v>32</v>
       </c>
       <c r="J20" s="40" t="s">
         <v>84</v>
       </c>
-      <c r="K20" s="154"/>
-      <c r="L20" s="155"/>
-    </row>
-    <row r="21" spans="5:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K20" s="109"/>
+      <c r="L20" s="110"/>
+    </row>
+    <row r="21" spans="5:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E21" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="F21" s="133" t="s">
+      <c r="F21" s="89" t="s">
         <v>14</v>
       </c>
-      <c r="G21" s="134"/>
-      <c r="H21" s="135"/>
+      <c r="G21" s="90"/>
+      <c r="H21" s="91"/>
       <c r="I21" s="37" t="s">
         <v>33</v>
       </c>
       <c r="J21" s="40" t="s">
         <v>85</v>
       </c>
-      <c r="K21" s="154"/>
-      <c r="L21" s="155"/>
-    </row>
-    <row r="22" spans="5:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K21" s="109"/>
+      <c r="L21" s="110"/>
+    </row>
+    <row r="22" spans="5:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E22" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="F22" s="136">
+      <c r="F22" s="92">
         <v>44022</v>
       </c>
-      <c r="G22" s="134"/>
-      <c r="H22" s="135"/>
+      <c r="G22" s="90"/>
+      <c r="H22" s="91"/>
       <c r="I22" s="37" t="s">
         <v>34</v>
       </c>
       <c r="J22" s="40" t="s">
         <v>86</v>
       </c>
-      <c r="K22" s="154"/>
-      <c r="L22" s="155"/>
-    </row>
-    <row r="23" spans="5:12" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K22" s="109"/>
+      <c r="L22" s="110"/>
+    </row>
+    <row r="23" spans="5:16" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E23" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="F23" s="137">
+      <c r="F23" s="59">
         <v>44145</v>
       </c>
-      <c r="G23" s="67"/>
-      <c r="H23" s="68"/>
-      <c r="I23" s="151"/>
-      <c r="J23" s="55"/>
-      <c r="K23" s="156"/>
-      <c r="L23" s="157"/>
-    </row>
-    <row r="24" spans="5:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="25" spans="5:12" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E25" s="60" t="s">
+      <c r="G23" s="60"/>
+      <c r="H23" s="61"/>
+      <c r="I23" s="147"/>
+      <c r="J23" s="67"/>
+      <c r="K23" s="111"/>
+      <c r="L23" s="112"/>
+    </row>
+    <row r="24" spans="5:16" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="25" spans="5:16" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E25" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="F25" s="61"/>
-      <c r="G25" s="61"/>
-      <c r="H25" s="61"/>
-      <c r="I25" s="61"/>
-      <c r="J25" s="61"/>
-      <c r="K25" s="61"/>
-      <c r="L25" s="62"/>
-    </row>
-    <row r="26" spans="5:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F25" s="84"/>
+      <c r="G25" s="84"/>
+      <c r="H25" s="84"/>
+      <c r="I25" s="84"/>
+      <c r="J25" s="84"/>
+      <c r="K25" s="84"/>
+      <c r="L25" s="85"/>
+    </row>
+    <row r="26" spans="5:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E26" s="12"/>
-      <c r="F26" s="63" t="s">
+      <c r="F26" s="72" t="s">
         <v>2</v>
       </c>
-      <c r="G26" s="64"/>
-      <c r="H26" s="65"/>
+      <c r="G26" s="73"/>
+      <c r="H26" s="74"/>
       <c r="I26" s="14"/>
       <c r="J26" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="K26" s="63" t="s">
+      <c r="K26" s="72" t="s">
         <v>25</v>
       </c>
-      <c r="L26" s="65"/>
-    </row>
-    <row r="27" spans="5:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L26" s="74"/>
+    </row>
+    <row r="27" spans="5:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E27" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="F27" s="160" t="s">
+      <c r="F27" s="57" t="s">
         <v>73</v>
       </c>
-      <c r="G27" s="160"/>
-      <c r="H27" s="161"/>
+      <c r="G27" s="57"/>
+      <c r="H27" s="58"/>
       <c r="I27" s="6" t="s">
         <v>41</v>
       </c>
       <c r="J27" s="35" t="s">
         <v>79</v>
       </c>
-      <c r="K27" s="166" t="s">
+      <c r="K27" s="62" t="s">
         <v>78</v>
       </c>
-      <c r="L27" s="167"/>
-    </row>
-    <row r="28" spans="5:12" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E28" s="57"/>
-      <c r="F28" s="58"/>
-      <c r="G28" s="58"/>
-      <c r="H28" s="59"/>
+      <c r="L27" s="63"/>
+    </row>
+    <row r="28" spans="5:16" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E28" s="80"/>
+      <c r="F28" s="81"/>
+      <c r="G28" s="81"/>
+      <c r="H28" s="82"/>
       <c r="I28" s="7" t="s">
         <v>42</v>
       </c>
       <c r="J28" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="K28" s="168"/>
-      <c r="L28" s="169"/>
-    </row>
-    <row r="29" spans="5:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="30" spans="5:12" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E30" s="60" t="s">
+      <c r="K28" s="64"/>
+      <c r="L28" s="65"/>
+    </row>
+    <row r="29" spans="5:16" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="30" spans="5:16" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E30" s="77" t="s">
         <v>28</v>
       </c>
-      <c r="F30" s="61"/>
-      <c r="G30" s="61"/>
-      <c r="H30" s="61"/>
-      <c r="I30" s="61"/>
-      <c r="J30" s="61"/>
-      <c r="K30" s="61"/>
-      <c r="L30" s="62"/>
-    </row>
-    <row r="31" spans="5:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F30" s="78"/>
+      <c r="G30" s="78"/>
+      <c r="H30" s="78"/>
+      <c r="I30" s="78"/>
+      <c r="J30" s="78"/>
+      <c r="K30" s="78"/>
+      <c r="L30" s="79"/>
+      <c r="N30" s="117" t="s">
+        <v>158</v>
+      </c>
+      <c r="O30" s="117"/>
+      <c r="P30" s="117"/>
+    </row>
+    <row r="31" spans="5:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E31" s="12"/>
-      <c r="F31" s="63" t="s">
+      <c r="F31" s="72" t="s">
         <v>2</v>
       </c>
-      <c r="G31" s="64"/>
-      <c r="H31" s="65"/>
+      <c r="G31" s="73"/>
+      <c r="H31" s="74"/>
       <c r="I31" s="14"/>
       <c r="J31" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="K31" s="63" t="s">
+      <c r="K31" s="72" t="s">
         <v>25</v>
       </c>
-      <c r="L31" s="65"/>
-    </row>
-    <row r="32" spans="5:12" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L31" s="74"/>
+    </row>
+    <row r="32" spans="5:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E32" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F32" s="48" t="s">
+      <c r="F32" s="75" t="s">
         <v>73</v>
       </c>
-      <c r="G32" s="48"/>
-      <c r="H32" s="49"/>
+      <c r="G32" s="75"/>
+      <c r="H32" s="76"/>
       <c r="I32" s="38" t="s">
         <v>50</v>
       </c>
       <c r="J32" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="K32" s="158" t="s">
+      <c r="K32" s="70" t="s">
         <v>77</v>
       </c>
-      <c r="L32" s="159"/>
-    </row>
-    <row r="33" spans="5:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="34" spans="5:12" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E34" s="60" t="s">
+      <c r="L32" s="71"/>
+    </row>
+    <row r="33" spans="5:16" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="34" spans="5:16" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E34" s="77" t="s">
         <v>29</v>
       </c>
-      <c r="F34" s="61"/>
-      <c r="G34" s="61"/>
-      <c r="H34" s="61"/>
-      <c r="I34" s="61"/>
-      <c r="J34" s="61"/>
-      <c r="K34" s="61"/>
-      <c r="L34" s="62"/>
-    </row>
-    <row r="35" spans="5:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F34" s="78"/>
+      <c r="G34" s="78"/>
+      <c r="H34" s="78"/>
+      <c r="I34" s="78"/>
+      <c r="J34" s="78"/>
+      <c r="K34" s="78"/>
+      <c r="L34" s="79"/>
+      <c r="N34" s="117" t="s">
+        <v>158</v>
+      </c>
+      <c r="O34" s="117"/>
+      <c r="P34" s="117"/>
+    </row>
+    <row r="35" spans="5:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E35" s="12"/>
-      <c r="F35" s="63" t="s">
+      <c r="F35" s="72" t="s">
         <v>2</v>
       </c>
-      <c r="G35" s="64"/>
-      <c r="H35" s="65"/>
+      <c r="G35" s="73"/>
+      <c r="H35" s="74"/>
       <c r="I35" s="41"/>
       <c r="J35" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="K35" s="63" t="s">
+      <c r="K35" s="72" t="s">
         <v>25</v>
       </c>
-      <c r="L35" s="65"/>
-    </row>
-    <row r="36" spans="5:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L35" s="74"/>
+    </row>
+    <row r="36" spans="5:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E36" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="F36" s="165">
+      <c r="F36" s="56">
         <v>46282</v>
       </c>
-      <c r="G36" s="160"/>
-      <c r="H36" s="161"/>
+      <c r="G36" s="57"/>
+      <c r="H36" s="58"/>
       <c r="I36" s="42" t="s">
         <v>51</v>
       </c>
       <c r="J36" s="35" t="s">
         <v>74</v>
       </c>
-      <c r="K36" s="170" t="s">
+      <c r="K36" s="68" t="s">
         <v>75</v>
       </c>
-      <c r="L36" s="171"/>
-    </row>
-    <row r="37" spans="5:12" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L36" s="69"/>
+    </row>
+    <row r="37" spans="5:16" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E37" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="F37" s="137">
+      <c r="F37" s="59">
         <v>46282</v>
       </c>
-      <c r="G37" s="67"/>
-      <c r="H37" s="68"/>
-      <c r="I37" s="54"/>
-      <c r="J37" s="55"/>
-      <c r="K37" s="158"/>
-      <c r="L37" s="159"/>
+      <c r="G37" s="60"/>
+      <c r="H37" s="61"/>
+      <c r="I37" s="66"/>
+      <c r="J37" s="67"/>
+      <c r="K37" s="70"/>
+      <c r="L37" s="71"/>
     </row>
   </sheetData>
-  <mergeCells count="48">
+  <mergeCells count="50">
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="E2:L4"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="F12:H12"/>
+    <mergeCell ref="E5:L5"/>
+    <mergeCell ref="E6:L6"/>
+    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="I7:L7"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="E16:L16"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="F13:H14"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="E25:L25"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="K18:L23"/>
     <mergeCell ref="F36:H36"/>
     <mergeCell ref="F37:H37"/>
     <mergeCell ref="K27:L28"/>
@@ -2893,13 +3267,6 @@
     <mergeCell ref="K36:L37"/>
     <mergeCell ref="F35:H35"/>
     <mergeCell ref="K35:L35"/>
-    <mergeCell ref="E25:L25"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="K26:L26"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="F20:H20"/>
     <mergeCell ref="F32:H32"/>
     <mergeCell ref="K32:L32"/>
     <mergeCell ref="E34:L34"/>
@@ -2907,33 +3274,6 @@
     <mergeCell ref="E30:L30"/>
     <mergeCell ref="F31:H31"/>
     <mergeCell ref="K31:L31"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="K13:K14"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="K18:L23"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="F13:H14"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="F21:H21"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="E2:L4"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="F12:H12"/>
-    <mergeCell ref="E5:L5"/>
-    <mergeCell ref="E6:L6"/>
-    <mergeCell ref="E16:L16"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="E7:H7"/>
-    <mergeCell ref="I7:L7"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -2962,82 +3302,82 @@
   <sheetData>
     <row r="1" spans="5:21" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="5:21" x14ac:dyDescent="0.3">
-      <c r="E2" s="138" t="s">
+      <c r="E2" s="118" t="s">
         <v>87</v>
       </c>
-      <c r="F2" s="139"/>
-      <c r="G2" s="139"/>
-      <c r="H2" s="139"/>
-      <c r="I2" s="139"/>
-      <c r="J2" s="139"/>
-      <c r="K2" s="139"/>
-      <c r="L2" s="140"/>
+      <c r="F2" s="119"/>
+      <c r="G2" s="119"/>
+      <c r="H2" s="119"/>
+      <c r="I2" s="119"/>
+      <c r="J2" s="119"/>
+      <c r="K2" s="119"/>
+      <c r="L2" s="120"/>
     </row>
     <row r="3" spans="5:21" x14ac:dyDescent="0.3">
-      <c r="E3" s="141"/>
-      <c r="F3" s="142"/>
-      <c r="G3" s="142"/>
-      <c r="H3" s="142"/>
-      <c r="I3" s="142"/>
-      <c r="J3" s="142"/>
-      <c r="K3" s="142"/>
-      <c r="L3" s="143"/>
+      <c r="E3" s="121"/>
+      <c r="F3" s="122"/>
+      <c r="G3" s="122"/>
+      <c r="H3" s="122"/>
+      <c r="I3" s="122"/>
+      <c r="J3" s="122"/>
+      <c r="K3" s="122"/>
+      <c r="L3" s="123"/>
     </row>
     <row r="4" spans="5:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E4" s="144"/>
-      <c r="F4" s="145"/>
-      <c r="G4" s="145"/>
-      <c r="H4" s="145"/>
-      <c r="I4" s="145"/>
-      <c r="J4" s="145"/>
-      <c r="K4" s="145"/>
-      <c r="L4" s="146"/>
+      <c r="E4" s="124"/>
+      <c r="F4" s="125"/>
+      <c r="G4" s="125"/>
+      <c r="H4" s="125"/>
+      <c r="I4" s="125"/>
+      <c r="J4" s="125"/>
+      <c r="K4" s="125"/>
+      <c r="L4" s="126"/>
     </row>
     <row r="5" spans="5:21" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E5" s="147" t="s">
+      <c r="E5" s="132" t="s">
         <v>1</v>
       </c>
-      <c r="F5" s="148"/>
-      <c r="G5" s="148"/>
-      <c r="H5" s="148"/>
-      <c r="I5" s="148"/>
-      <c r="J5" s="148"/>
-      <c r="K5" s="148"/>
-      <c r="L5" s="149"/>
+      <c r="F5" s="133"/>
+      <c r="G5" s="133"/>
+      <c r="H5" s="133"/>
+      <c r="I5" s="133"/>
+      <c r="J5" s="133"/>
+      <c r="K5" s="133"/>
+      <c r="L5" s="134"/>
       <c r="M5" s="23"/>
       <c r="N5" s="23"/>
       <c r="O5" s="23"/>
       <c r="P5" s="23"/>
     </row>
     <row r="6" spans="5:21" ht="69" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E6" s="101" t="s">
+      <c r="E6" s="135" t="s">
         <v>88</v>
       </c>
-      <c r="F6" s="102"/>
-      <c r="G6" s="102"/>
-      <c r="H6" s="102"/>
-      <c r="I6" s="102"/>
-      <c r="J6" s="102"/>
-      <c r="K6" s="102"/>
-      <c r="L6" s="103"/>
+      <c r="F6" s="136"/>
+      <c r="G6" s="136"/>
+      <c r="H6" s="136"/>
+      <c r="I6" s="136"/>
+      <c r="J6" s="136"/>
+      <c r="K6" s="136"/>
+      <c r="L6" s="137"/>
       <c r="M6" s="24"/>
       <c r="N6" s="24"/>
       <c r="O6" s="24"/>
       <c r="P6" s="24"/>
     </row>
     <row r="7" spans="5:21" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E7" s="104" t="s">
+      <c r="E7" s="138" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="105"/>
-      <c r="G7" s="105"/>
-      <c r="H7" s="105"/>
-      <c r="I7" s="105" t="s">
+      <c r="F7" s="139"/>
+      <c r="G7" s="139"/>
+      <c r="H7" s="139"/>
+      <c r="I7" s="139" t="s">
         <v>3</v>
       </c>
-      <c r="J7" s="105"/>
-      <c r="K7" s="105"/>
-      <c r="L7" s="106"/>
+      <c r="J7" s="139"/>
+      <c r="K7" s="139"/>
+      <c r="L7" s="140"/>
       <c r="M7" s="25"/>
       <c r="N7" s="25"/>
       <c r="O7" s="25"/>
@@ -3047,11 +3387,11 @@
       <c r="E8" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="F8" s="124" t="s">
+      <c r="F8" s="141" t="s">
         <v>89</v>
       </c>
-      <c r="G8" s="125"/>
-      <c r="H8" s="113"/>
+      <c r="G8" s="142"/>
+      <c r="H8" s="101"/>
       <c r="I8" s="26" t="s">
         <v>62</v>
       </c>
@@ -3069,12 +3409,12 @@
       <c r="E9" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="F9" s="126" t="s">
+      <c r="F9" s="127" t="s">
         <v>90</v>
       </c>
-      <c r="G9" s="127"/>
-      <c r="H9" s="128"/>
-      <c r="I9" s="126" t="s">
+      <c r="G9" s="128"/>
+      <c r="H9" s="129"/>
+      <c r="I9" s="127" t="s">
         <v>54</v>
       </c>
       <c r="J9" s="32" t="s">
@@ -3089,12 +3429,12 @@
       <c r="E10" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="F10" s="126" t="s">
+      <c r="F10" s="127" t="s">
         <v>11</v>
       </c>
-      <c r="G10" s="127"/>
-      <c r="H10" s="128"/>
-      <c r="I10" s="129"/>
+      <c r="G10" s="128"/>
+      <c r="H10" s="129"/>
+      <c r="I10" s="130"/>
       <c r="J10" s="32" t="s">
         <v>58</v>
       </c>
@@ -3107,12 +3447,12 @@
       <c r="E11" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="F11" s="126" t="s">
+      <c r="F11" s="127" t="s">
         <v>10</v>
       </c>
-      <c r="G11" s="127"/>
-      <c r="H11" s="127"/>
-      <c r="I11" s="126" t="s">
+      <c r="G11" s="128"/>
+      <c r="H11" s="128"/>
+      <c r="I11" s="127" t="s">
         <v>55</v>
       </c>
       <c r="J11" s="32" t="s">
@@ -3127,12 +3467,12 @@
       <c r="E12" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="F12" s="129" t="s">
+      <c r="F12" s="130" t="s">
         <v>91</v>
       </c>
-      <c r="G12" s="132"/>
-      <c r="H12" s="132"/>
-      <c r="I12" s="129"/>
+      <c r="G12" s="131"/>
+      <c r="H12" s="131"/>
+      <c r="I12" s="130"/>
       <c r="J12" s="32" t="s">
         <v>60</v>
       </c>
@@ -3142,632 +3482,678 @@
       <c r="L12" s="28"/>
     </row>
     <row r="13" spans="5:21" x14ac:dyDescent="0.3">
-      <c r="E13" s="87" t="s">
+      <c r="E13" s="93" t="s">
         <v>12</v>
       </c>
-      <c r="F13" s="107">
+      <c r="F13" s="95">
         <v>2234113.58</v>
       </c>
-      <c r="G13" s="108"/>
-      <c r="H13" s="109"/>
-      <c r="I13" s="130" t="s">
+      <c r="G13" s="96"/>
+      <c r="H13" s="97"/>
+      <c r="I13" s="143" t="s">
         <v>56</v>
       </c>
-      <c r="J13" s="130" t="s">
+      <c r="J13" s="143" t="s">
         <v>61</v>
       </c>
-      <c r="K13" s="174" t="s">
+      <c r="K13" s="167" t="s">
         <v>92</v>
       </c>
-      <c r="L13" s="172" t="s">
+      <c r="L13" s="169" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="14" spans="5:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E14" s="88"/>
-      <c r="F14" s="110"/>
-      <c r="G14" s="111"/>
-      <c r="H14" s="112"/>
-      <c r="I14" s="131"/>
-      <c r="J14" s="131"/>
-      <c r="K14" s="175"/>
-      <c r="L14" s="173"/>
+      <c r="E14" s="94"/>
+      <c r="F14" s="98"/>
+      <c r="G14" s="99"/>
+      <c r="H14" s="100"/>
+      <c r="I14" s="144"/>
+      <c r="J14" s="144"/>
+      <c r="K14" s="168"/>
+      <c r="L14" s="170"/>
     </row>
     <row r="15" spans="5:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E15" s="150"/>
-      <c r="F15" s="150"/>
+      <c r="E15" s="116"/>
+      <c r="F15" s="116"/>
     </row>
     <row r="16" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E16" s="60" t="s">
+      <c r="E16" s="83" t="s">
         <v>15</v>
       </c>
-      <c r="F16" s="61"/>
-      <c r="G16" s="61"/>
-      <c r="H16" s="61"/>
-      <c r="I16" s="61"/>
-      <c r="J16" s="61"/>
-      <c r="K16" s="61"/>
-      <c r="L16" s="62"/>
-      <c r="N16" s="60" t="s">
+      <c r="F16" s="84"/>
+      <c r="G16" s="84"/>
+      <c r="H16" s="84"/>
+      <c r="I16" s="84"/>
+      <c r="J16" s="84"/>
+      <c r="K16" s="84"/>
+      <c r="L16" s="85"/>
+      <c r="N16" s="83" t="s">
         <v>95</v>
       </c>
-      <c r="O16" s="61"/>
-      <c r="P16" s="61"/>
-      <c r="Q16" s="61"/>
-      <c r="R16" s="61"/>
-      <c r="S16" s="61"/>
-      <c r="T16" s="61"/>
-      <c r="U16" s="62"/>
+      <c r="O16" s="84"/>
+      <c r="P16" s="84"/>
+      <c r="Q16" s="84"/>
+      <c r="R16" s="84"/>
+      <c r="S16" s="84"/>
+      <c r="T16" s="84"/>
+      <c r="U16" s="85"/>
     </row>
     <row r="17" spans="5:23" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E17" s="9"/>
-      <c r="F17" s="75" t="s">
+      <c r="F17" s="113" t="s">
         <v>2</v>
       </c>
-      <c r="G17" s="76"/>
-      <c r="H17" s="77"/>
+      <c r="G17" s="114"/>
+      <c r="H17" s="115"/>
       <c r="I17" s="14"/>
       <c r="J17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="K17" s="63" t="s">
+      <c r="K17" s="72" t="s">
         <v>25</v>
       </c>
-      <c r="L17" s="65"/>
+      <c r="L17" s="74"/>
       <c r="N17" s="9"/>
-      <c r="O17" s="75" t="s">
+      <c r="O17" s="113" t="s">
         <v>2</v>
       </c>
-      <c r="P17" s="76"/>
-      <c r="Q17" s="77"/>
+      <c r="P17" s="114"/>
+      <c r="Q17" s="115"/>
       <c r="R17" s="8"/>
       <c r="S17" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="T17" s="75" t="s">
+      <c r="T17" s="113" t="s">
         <v>25</v>
       </c>
-      <c r="U17" s="77"/>
+      <c r="U17" s="115"/>
     </row>
     <row r="18" spans="5:23" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E18" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="F18" s="162" t="s">
+      <c r="F18" s="86" t="s">
         <v>100</v>
       </c>
-      <c r="G18" s="163"/>
-      <c r="H18" s="164"/>
+      <c r="G18" s="87"/>
+      <c r="H18" s="88"/>
       <c r="I18" s="36" t="s">
         <v>30</v>
       </c>
       <c r="J18" s="39" t="s">
         <v>104</v>
       </c>
-      <c r="K18" s="152" t="s">
+      <c r="K18" s="107" t="s">
         <v>102</v>
       </c>
-      <c r="L18" s="153"/>
+      <c r="L18" s="108"/>
       <c r="N18" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="O18" s="136" t="s">
+      <c r="O18" s="92" t="s">
         <v>108</v>
       </c>
-      <c r="P18" s="134"/>
-      <c r="Q18" s="135"/>
+      <c r="P18" s="90"/>
+      <c r="Q18" s="91"/>
       <c r="R18" s="6" t="s">
         <v>45</v>
       </c>
       <c r="S18" s="45" t="s">
         <v>110</v>
       </c>
-      <c r="T18" s="192" t="s">
+      <c r="T18" s="148" t="s">
         <v>109</v>
       </c>
-      <c r="U18" s="193"/>
+      <c r="U18" s="149"/>
     </row>
     <row r="19" spans="5:23" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E19" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="F19" s="133" t="s">
+      <c r="F19" s="89" t="s">
         <v>89</v>
       </c>
-      <c r="G19" s="134"/>
-      <c r="H19" s="135"/>
+      <c r="G19" s="90"/>
+      <c r="H19" s="91"/>
       <c r="I19" s="37" t="s">
         <v>52</v>
       </c>
       <c r="J19" s="40" t="s">
         <v>147</v>
       </c>
-      <c r="K19" s="154"/>
-      <c r="L19" s="155"/>
+      <c r="K19" s="109"/>
+      <c r="L19" s="110"/>
       <c r="N19" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="O19" s="189">
+      <c r="O19" s="152">
         <v>622036.57999999996</v>
       </c>
-      <c r="P19" s="190"/>
-      <c r="Q19" s="191"/>
+      <c r="P19" s="153"/>
+      <c r="Q19" s="154"/>
       <c r="R19" s="6" t="s">
         <v>46</v>
       </c>
       <c r="S19" s="45" t="s">
         <v>112</v>
       </c>
-      <c r="T19" s="194"/>
-      <c r="U19" s="195"/>
+      <c r="T19" s="150"/>
+      <c r="U19" s="151"/>
     </row>
     <row r="20" spans="5:23" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E20" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="F20" s="133" t="s">
+      <c r="F20" s="89" t="s">
         <v>90</v>
       </c>
-      <c r="G20" s="134"/>
-      <c r="H20" s="135"/>
+      <c r="G20" s="90"/>
+      <c r="H20" s="91"/>
       <c r="I20" s="37" t="s">
         <v>32</v>
       </c>
       <c r="J20" s="40" t="s">
         <v>103</v>
       </c>
-      <c r="K20" s="154"/>
-      <c r="L20" s="155"/>
-      <c r="N20" s="66"/>
-      <c r="O20" s="67"/>
-      <c r="P20" s="67"/>
-      <c r="Q20" s="68"/>
+      <c r="K20" s="109"/>
+      <c r="L20" s="110"/>
+      <c r="N20" s="155"/>
+      <c r="O20" s="60"/>
+      <c r="P20" s="60"/>
+      <c r="Q20" s="61"/>
       <c r="R20" s="7" t="s">
         <v>47</v>
       </c>
       <c r="S20" s="44" t="s">
         <v>111</v>
       </c>
-      <c r="T20" s="168"/>
-      <c r="U20" s="169"/>
+      <c r="T20" s="64"/>
+      <c r="U20" s="65"/>
     </row>
     <row r="21" spans="5:23" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E21" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="F21" s="133" t="s">
+      <c r="F21" s="89" t="s">
         <v>91</v>
       </c>
-      <c r="G21" s="134"/>
-      <c r="H21" s="135"/>
+      <c r="G21" s="90"/>
+      <c r="H21" s="91"/>
       <c r="I21" s="37" t="s">
         <v>33</v>
       </c>
       <c r="J21" s="40" t="s">
         <v>70</v>
       </c>
-      <c r="K21" s="154"/>
-      <c r="L21" s="155"/>
+      <c r="K21" s="109"/>
+      <c r="L21" s="110"/>
     </row>
     <row r="22" spans="5:23" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E22" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="F22" s="136">
+      <c r="F22" s="92">
         <v>46122</v>
       </c>
-      <c r="G22" s="134"/>
-      <c r="H22" s="135"/>
+      <c r="G22" s="90"/>
+      <c r="H22" s="91"/>
       <c r="I22" s="37" t="s">
         <v>34</v>
       </c>
       <c r="J22" s="40" t="s">
         <v>101</v>
       </c>
-      <c r="K22" s="154"/>
-      <c r="L22" s="155"/>
-      <c r="N22" s="60" t="s">
+      <c r="K22" s="109"/>
+      <c r="L22" s="110"/>
+      <c r="N22" s="83" t="s">
         <v>96</v>
       </c>
-      <c r="O22" s="61"/>
-      <c r="P22" s="61"/>
-      <c r="Q22" s="61"/>
-      <c r="R22" s="61"/>
-      <c r="S22" s="61"/>
-      <c r="T22" s="61"/>
-      <c r="U22" s="62"/>
+      <c r="O22" s="84"/>
+      <c r="P22" s="84"/>
+      <c r="Q22" s="84"/>
+      <c r="R22" s="84"/>
+      <c r="S22" s="84"/>
+      <c r="T22" s="84"/>
+      <c r="U22" s="85"/>
     </row>
     <row r="23" spans="5:23" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E23" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="F23" s="137">
+      <c r="F23" s="59">
         <v>46356</v>
       </c>
-      <c r="G23" s="67"/>
-      <c r="H23" s="68"/>
-      <c r="I23" s="151"/>
-      <c r="J23" s="55"/>
-      <c r="K23" s="156"/>
-      <c r="L23" s="157"/>
+      <c r="G23" s="60"/>
+      <c r="H23" s="61"/>
+      <c r="I23" s="147"/>
+      <c r="J23" s="67"/>
+      <c r="K23" s="111"/>
+      <c r="L23" s="112"/>
       <c r="N23" s="9"/>
-      <c r="O23" s="75" t="s">
+      <c r="O23" s="113" t="s">
         <v>2</v>
       </c>
-      <c r="P23" s="76"/>
-      <c r="Q23" s="77"/>
+      <c r="P23" s="114"/>
+      <c r="Q23" s="115"/>
       <c r="R23" s="8"/>
       <c r="S23" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="T23" s="75" t="s">
+      <c r="T23" s="113" t="s">
         <v>25</v>
       </c>
-      <c r="U23" s="77"/>
+      <c r="U23" s="115"/>
     </row>
     <row r="24" spans="5:23" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="N24" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="O24" s="133" t="s">
+      <c r="O24" s="89" t="s">
         <v>113</v>
       </c>
-      <c r="P24" s="134"/>
-      <c r="Q24" s="135"/>
+      <c r="P24" s="90"/>
+      <c r="Q24" s="91"/>
       <c r="R24" s="6" t="s">
         <v>45</v>
       </c>
       <c r="S24" s="45" t="s">
         <v>117</v>
       </c>
-      <c r="T24" s="192" t="s">
+      <c r="T24" s="148" t="s">
         <v>114</v>
       </c>
-      <c r="U24" s="193"/>
+      <c r="U24" s="149"/>
     </row>
     <row r="25" spans="5:23" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E25" s="60" t="s">
+      <c r="E25" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="F25" s="61"/>
-      <c r="G25" s="61"/>
-      <c r="H25" s="61"/>
-      <c r="I25" s="61"/>
-      <c r="J25" s="61"/>
-      <c r="K25" s="61"/>
-      <c r="L25" s="62"/>
+      <c r="F25" s="84"/>
+      <c r="G25" s="84"/>
+      <c r="H25" s="84"/>
+      <c r="I25" s="84"/>
+      <c r="J25" s="84"/>
+      <c r="K25" s="84"/>
+      <c r="L25" s="85"/>
       <c r="N25" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="O25" s="196">
+      <c r="O25" s="156">
         <v>150504.31</v>
       </c>
-      <c r="P25" s="197"/>
-      <c r="Q25" s="198"/>
+      <c r="P25" s="157"/>
+      <c r="Q25" s="158"/>
       <c r="R25" s="6" t="s">
         <v>46</v>
       </c>
       <c r="S25" s="45" t="s">
         <v>115</v>
       </c>
-      <c r="T25" s="194"/>
-      <c r="U25" s="195"/>
+      <c r="T25" s="150"/>
+      <c r="U25" s="151"/>
     </row>
     <row r="26" spans="5:23" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E26" s="12"/>
-      <c r="F26" s="63" t="s">
+      <c r="F26" s="72" t="s">
         <v>2</v>
       </c>
-      <c r="G26" s="64"/>
-      <c r="H26" s="65"/>
+      <c r="G26" s="73"/>
+      <c r="H26" s="74"/>
       <c r="I26" s="14"/>
       <c r="J26" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="K26" s="63" t="s">
+      <c r="K26" s="72" t="s">
         <v>25</v>
       </c>
-      <c r="L26" s="65"/>
-      <c r="N26" s="66"/>
-      <c r="O26" s="67"/>
-      <c r="P26" s="67"/>
-      <c r="Q26" s="68"/>
+      <c r="L26" s="74"/>
+      <c r="N26" s="155"/>
+      <c r="O26" s="60"/>
+      <c r="P26" s="60"/>
+      <c r="Q26" s="61"/>
       <c r="R26" s="7" t="s">
         <v>47</v>
       </c>
       <c r="S26" s="44" t="s">
         <v>116</v>
       </c>
-      <c r="T26" s="168"/>
-      <c r="U26" s="169"/>
+      <c r="T26" s="64"/>
+      <c r="U26" s="65"/>
     </row>
     <row r="27" spans="5:23" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E27" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="F27" s="160" t="s">
+      <c r="F27" s="57" t="s">
         <v>93</v>
       </c>
-      <c r="G27" s="160"/>
-      <c r="H27" s="161"/>
+      <c r="G27" s="57"/>
+      <c r="H27" s="58"/>
       <c r="I27" s="6" t="s">
         <v>41</v>
       </c>
       <c r="J27" s="35" t="s">
         <v>105</v>
       </c>
-      <c r="K27" s="166" t="s">
+      <c r="K27" s="62" t="s">
         <v>106</v>
       </c>
-      <c r="L27" s="167"/>
+      <c r="L27" s="63"/>
     </row>
     <row r="28" spans="5:23" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E28" s="57"/>
-      <c r="F28" s="58"/>
-      <c r="G28" s="58"/>
-      <c r="H28" s="59"/>
+      <c r="E28" s="80"/>
+      <c r="F28" s="81"/>
+      <c r="G28" s="81"/>
+      <c r="H28" s="82"/>
       <c r="I28" s="7" t="s">
         <v>42</v>
       </c>
       <c r="J28" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="K28" s="168"/>
-      <c r="L28" s="169"/>
-      <c r="N28" s="199" t="s">
+      <c r="K28" s="64"/>
+      <c r="L28" s="65"/>
+      <c r="N28" s="77" t="s">
         <v>98</v>
       </c>
-      <c r="O28" s="200"/>
-      <c r="P28" s="200"/>
-      <c r="Q28" s="200"/>
-      <c r="R28" s="200"/>
-      <c r="S28" s="200"/>
-      <c r="T28" s="200"/>
-      <c r="U28" s="201"/>
-      <c r="W28" s="202" t="s">
+      <c r="O28" s="78"/>
+      <c r="P28" s="78"/>
+      <c r="Q28" s="78"/>
+      <c r="R28" s="78"/>
+      <c r="S28" s="78"/>
+      <c r="T28" s="78"/>
+      <c r="U28" s="79"/>
+      <c r="W28" s="46" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="29" spans="5:23" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="N29" s="9"/>
-      <c r="O29" s="75" t="s">
+      <c r="O29" s="113" t="s">
         <v>2</v>
       </c>
-      <c r="P29" s="76"/>
-      <c r="Q29" s="77"/>
+      <c r="P29" s="114"/>
+      <c r="Q29" s="115"/>
       <c r="R29" s="8"/>
       <c r="S29" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="T29" s="75" t="s">
+      <c r="T29" s="113" t="s">
         <v>25</v>
       </c>
-      <c r="U29" s="77"/>
+      <c r="U29" s="115"/>
     </row>
     <row r="30" spans="5:23" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E30" s="60" t="s">
+      <c r="E30" s="83" t="s">
         <v>28</v>
       </c>
-      <c r="F30" s="61"/>
-      <c r="G30" s="61"/>
-      <c r="H30" s="61"/>
-      <c r="I30" s="61"/>
-      <c r="J30" s="61"/>
-      <c r="K30" s="61"/>
-      <c r="L30" s="62"/>
+      <c r="F30" s="84"/>
+      <c r="G30" s="84"/>
+      <c r="H30" s="84"/>
+      <c r="I30" s="84"/>
+      <c r="J30" s="84"/>
+      <c r="K30" s="84"/>
+      <c r="L30" s="85"/>
       <c r="N30" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="O30" s="133" t="s">
+      <c r="O30" s="89" t="s">
         <v>153</v>
       </c>
-      <c r="P30" s="134"/>
-      <c r="Q30" s="135"/>
+      <c r="P30" s="90"/>
+      <c r="Q30" s="91"/>
       <c r="R30" s="6" t="s">
         <v>45</v>
       </c>
       <c r="S30" s="45" t="s">
         <v>157</v>
       </c>
-      <c r="T30" s="192" t="s">
+      <c r="T30" s="148" t="s">
         <v>155</v>
       </c>
-      <c r="U30" s="193"/>
+      <c r="U30" s="149"/>
     </row>
     <row r="31" spans="5:23" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E31" s="12"/>
-      <c r="F31" s="63" t="s">
+      <c r="F31" s="72" t="s">
         <v>2</v>
       </c>
-      <c r="G31" s="64"/>
-      <c r="H31" s="65"/>
+      <c r="G31" s="73"/>
+      <c r="H31" s="74"/>
       <c r="I31" s="14"/>
       <c r="J31" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="K31" s="63" t="s">
+      <c r="K31" s="72" t="s">
         <v>25</v>
       </c>
-      <c r="L31" s="65"/>
+      <c r="L31" s="74"/>
       <c r="N31" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="O31" s="189">
+      <c r="O31" s="152">
         <v>285515.09000000003</v>
       </c>
-      <c r="P31" s="190"/>
-      <c r="Q31" s="191"/>
+      <c r="P31" s="153"/>
+      <c r="Q31" s="154"/>
       <c r="R31" s="6" t="s">
         <v>46</v>
       </c>
       <c r="S31" s="45" t="s">
         <v>156</v>
       </c>
-      <c r="T31" s="194"/>
-      <c r="U31" s="195"/>
+      <c r="T31" s="150"/>
+      <c r="U31" s="151"/>
     </row>
     <row r="32" spans="5:23" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E32" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F32" s="48" t="s">
+      <c r="F32" s="75" t="s">
         <v>93</v>
       </c>
-      <c r="G32" s="48"/>
-      <c r="H32" s="49"/>
+      <c r="G32" s="75"/>
+      <c r="H32" s="76"/>
       <c r="I32" s="38" t="s">
         <v>50</v>
       </c>
       <c r="J32" s="17"/>
-      <c r="K32" s="158"/>
-      <c r="L32" s="159"/>
-      <c r="N32" s="66"/>
-      <c r="O32" s="67"/>
-      <c r="P32" s="67"/>
-      <c r="Q32" s="68"/>
+      <c r="K32" s="70"/>
+      <c r="L32" s="71"/>
+      <c r="N32" s="155"/>
+      <c r="O32" s="60"/>
+      <c r="P32" s="60"/>
+      <c r="Q32" s="61"/>
       <c r="R32" s="7" t="s">
         <v>47</v>
       </c>
       <c r="S32" s="44" t="s">
         <v>154</v>
       </c>
-      <c r="T32" s="168"/>
-      <c r="U32" s="169"/>
+      <c r="T32" s="64"/>
+      <c r="U32" s="65"/>
     </row>
     <row r="33" spans="5:23" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="34" spans="5:23" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E34" s="60" t="s">
+      <c r="E34" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="F34" s="61"/>
-      <c r="G34" s="61"/>
-      <c r="H34" s="61"/>
-      <c r="I34" s="61"/>
-      <c r="J34" s="61"/>
-      <c r="K34" s="61"/>
-      <c r="L34" s="62"/>
-      <c r="N34" s="199" t="s">
+      <c r="F34" s="84"/>
+      <c r="G34" s="84"/>
+      <c r="H34" s="84"/>
+      <c r="I34" s="84"/>
+      <c r="J34" s="84"/>
+      <c r="K34" s="84"/>
+      <c r="L34" s="85"/>
+      <c r="N34" s="77" t="s">
         <v>97</v>
       </c>
-      <c r="O34" s="200"/>
-      <c r="P34" s="200"/>
-      <c r="Q34" s="200"/>
-      <c r="R34" s="200"/>
-      <c r="S34" s="200"/>
-      <c r="T34" s="200"/>
-      <c r="U34" s="201"/>
-      <c r="W34" s="202" t="s">
+      <c r="O34" s="78"/>
+      <c r="P34" s="78"/>
+      <c r="Q34" s="78"/>
+      <c r="R34" s="78"/>
+      <c r="S34" s="78"/>
+      <c r="T34" s="78"/>
+      <c r="U34" s="79"/>
+      <c r="W34" s="46" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="35" spans="5:23" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E35" s="12"/>
-      <c r="F35" s="176" t="s">
+      <c r="F35" s="159" t="s">
         <v>2</v>
       </c>
-      <c r="G35" s="177"/>
-      <c r="H35" s="178"/>
+      <c r="G35" s="160"/>
+      <c r="H35" s="161"/>
       <c r="I35" s="41"/>
       <c r="J35" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="K35" s="176" t="s">
+      <c r="K35" s="159" t="s">
         <v>25</v>
       </c>
-      <c r="L35" s="178"/>
+      <c r="L35" s="161"/>
       <c r="N35" s="9"/>
-      <c r="O35" s="75" t="s">
+      <c r="O35" s="113" t="s">
         <v>2</v>
       </c>
-      <c r="P35" s="76"/>
-      <c r="Q35" s="77"/>
+      <c r="P35" s="114"/>
+      <c r="Q35" s="115"/>
       <c r="R35" s="8"/>
       <c r="S35" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="T35" s="75" t="s">
+      <c r="T35" s="113" t="s">
         <v>25</v>
       </c>
-      <c r="U35" s="77"/>
+      <c r="U35" s="115"/>
     </row>
     <row r="36" spans="5:23" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E36" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="F36" s="136"/>
-      <c r="G36" s="179"/>
-      <c r="H36" s="180"/>
+      <c r="F36" s="92"/>
+      <c r="G36" s="162"/>
+      <c r="H36" s="163"/>
       <c r="I36" s="42" t="s">
         <v>51</v>
       </c>
       <c r="J36" s="35"/>
-      <c r="K36" s="166"/>
-      <c r="L36" s="167"/>
+      <c r="K36" s="62"/>
+      <c r="L36" s="63"/>
       <c r="N36" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="O36" s="70"/>
-      <c r="P36" s="71"/>
-      <c r="Q36" s="72"/>
+      <c r="O36" s="89" t="s">
+        <v>160</v>
+      </c>
+      <c r="P36" s="90"/>
+      <c r="Q36" s="91"/>
       <c r="R36" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="S36" s="3"/>
-      <c r="T36" s="183"/>
-      <c r="U36" s="184"/>
+      <c r="S36" s="47" t="s">
+        <v>162</v>
+      </c>
+      <c r="T36" s="148" t="s">
+        <v>159</v>
+      </c>
+      <c r="U36" s="149"/>
     </row>
     <row r="37" spans="5:23" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E37" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="F37" s="137"/>
-      <c r="G37" s="181"/>
-      <c r="H37" s="182"/>
-      <c r="I37" s="50"/>
-      <c r="J37" s="54"/>
-      <c r="K37" s="168"/>
-      <c r="L37" s="169"/>
+      <c r="F37" s="59"/>
+      <c r="G37" s="164"/>
+      <c r="H37" s="165"/>
+      <c r="I37" s="166"/>
+      <c r="J37" s="66"/>
+      <c r="K37" s="64"/>
+      <c r="L37" s="65"/>
       <c r="N37" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="O37" s="70"/>
-      <c r="P37" s="71"/>
-      <c r="Q37" s="72"/>
+      <c r="O37" s="152">
+        <v>114577.65</v>
+      </c>
+      <c r="P37" s="153"/>
+      <c r="Q37" s="154"/>
       <c r="R37" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="S37" s="3"/>
-      <c r="T37" s="185"/>
-      <c r="U37" s="186"/>
+      <c r="S37" s="40" t="s">
+        <v>182</v>
+      </c>
+      <c r="T37" s="150"/>
+      <c r="U37" s="151"/>
     </row>
     <row r="38" spans="5:23" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="N38" s="66"/>
-      <c r="O38" s="67"/>
-      <c r="P38" s="67"/>
-      <c r="Q38" s="68"/>
+      <c r="N38" s="155"/>
+      <c r="O38" s="60"/>
+      <c r="P38" s="60"/>
+      <c r="Q38" s="61"/>
       <c r="R38" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="S38" s="11"/>
-      <c r="T38" s="187"/>
-      <c r="U38" s="188"/>
+      <c r="S38" s="48" t="s">
+        <v>161</v>
+      </c>
+      <c r="T38" s="64"/>
+      <c r="U38" s="65"/>
     </row>
   </sheetData>
   <mergeCells count="76">
-    <mergeCell ref="N34:U34"/>
-    <mergeCell ref="O35:Q35"/>
-    <mergeCell ref="T35:U35"/>
-    <mergeCell ref="O36:Q36"/>
-    <mergeCell ref="T36:U38"/>
-    <mergeCell ref="O37:Q37"/>
-    <mergeCell ref="N38:Q38"/>
-    <mergeCell ref="N28:U28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="T29:U29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="T30:U32"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="N32:Q32"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="E2:L4"/>
+    <mergeCell ref="E5:L5"/>
+    <mergeCell ref="E6:L6"/>
+    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="I7:L7"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="F12:H12"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="F13:H14"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E16:L16"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="K18:L23"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="E34:L34"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="E25:L25"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="K27:L28"/>
+    <mergeCell ref="E28:H28"/>
+    <mergeCell ref="E30:L30"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="K31:L31"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="K35:L35"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="K36:L37"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="I37:J37"/>
     <mergeCell ref="N20:Q20"/>
     <mergeCell ref="T18:U20"/>
     <mergeCell ref="N26:Q26"/>
@@ -3782,36 +4168,2311 @@
     <mergeCell ref="O24:Q24"/>
     <mergeCell ref="T24:U26"/>
     <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="N28:U28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="T29:U29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="T30:U32"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="N32:Q32"/>
+    <mergeCell ref="N34:U34"/>
+    <mergeCell ref="O35:Q35"/>
+    <mergeCell ref="T35:U35"/>
+    <mergeCell ref="O36:Q36"/>
+    <mergeCell ref="T36:U38"/>
+    <mergeCell ref="O37:Q37"/>
+    <mergeCell ref="N38:Q38"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4561D198-C9B7-4DE2-8DF4-A0018AE8DF2D}">
+  <dimension ref="E1:Y38"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="5" max="5" width="25.77734375" customWidth="1"/>
+    <col min="6" max="6" width="20.77734375" customWidth="1"/>
+    <col min="7" max="8" width="10.77734375" customWidth="1"/>
+    <col min="9" max="9" width="30.77734375" customWidth="1"/>
+    <col min="10" max="10" width="45.77734375" customWidth="1"/>
+    <col min="11" max="12" width="25.77734375" customWidth="1"/>
+    <col min="14" max="14" width="25.77734375" customWidth="1"/>
+    <col min="15" max="15" width="20.77734375" customWidth="1"/>
+    <col min="16" max="17" width="10.77734375" customWidth="1"/>
+    <col min="18" max="18" width="30.77734375" customWidth="1"/>
+    <col min="19" max="19" width="45.77734375" customWidth="1"/>
+    <col min="20" max="21" width="25.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="5:25" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="5:25" x14ac:dyDescent="0.3">
+      <c r="E2" s="118" t="s">
+        <v>137</v>
+      </c>
+      <c r="F2" s="119"/>
+      <c r="G2" s="119"/>
+      <c r="H2" s="119"/>
+      <c r="I2" s="119"/>
+      <c r="J2" s="119"/>
+      <c r="K2" s="119"/>
+      <c r="L2" s="120"/>
+    </row>
+    <row r="3" spans="5:25" x14ac:dyDescent="0.3">
+      <c r="E3" s="121"/>
+      <c r="F3" s="122"/>
+      <c r="G3" s="122"/>
+      <c r="H3" s="122"/>
+      <c r="I3" s="122"/>
+      <c r="J3" s="122"/>
+      <c r="K3" s="122"/>
+      <c r="L3" s="123"/>
+    </row>
+    <row r="4" spans="5:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E4" s="124"/>
+      <c r="F4" s="125"/>
+      <c r="G4" s="125"/>
+      <c r="H4" s="125"/>
+      <c r="I4" s="125"/>
+      <c r="J4" s="125"/>
+      <c r="K4" s="125"/>
+      <c r="L4" s="126"/>
+    </row>
+    <row r="5" spans="5:25" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E5" s="132" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="133"/>
+      <c r="G5" s="133"/>
+      <c r="H5" s="133"/>
+      <c r="I5" s="133"/>
+      <c r="J5" s="133"/>
+      <c r="K5" s="133"/>
+      <c r="L5" s="134"/>
+      <c r="M5" s="23"/>
+      <c r="N5" s="23"/>
+      <c r="O5" s="23"/>
+      <c r="P5" s="23"/>
+    </row>
+    <row r="6" spans="5:25" ht="69" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E6" s="135" t="s">
+        <v>138</v>
+      </c>
+      <c r="F6" s="136"/>
+      <c r="G6" s="136"/>
+      <c r="H6" s="136"/>
+      <c r="I6" s="136"/>
+      <c r="J6" s="136"/>
+      <c r="K6" s="136"/>
+      <c r="L6" s="137"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="24"/>
+      <c r="O6" s="24"/>
+      <c r="P6" s="24"/>
+    </row>
+    <row r="7" spans="5:25" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E7" s="138" t="s">
+        <v>2</v>
+      </c>
+      <c r="F7" s="139"/>
+      <c r="G7" s="139"/>
+      <c r="H7" s="139"/>
+      <c r="I7" s="139" t="s">
+        <v>3</v>
+      </c>
+      <c r="J7" s="139"/>
+      <c r="K7" s="139"/>
+      <c r="L7" s="140"/>
+      <c r="M7" s="25"/>
+      <c r="N7" s="25"/>
+      <c r="O7" s="25"/>
+      <c r="P7" s="25"/>
+    </row>
+    <row r="8" spans="5:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E8" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="141" t="s">
+        <v>139</v>
+      </c>
+      <c r="G8" s="142"/>
+      <c r="H8" s="101"/>
+      <c r="I8" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="J8" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="K8" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="L8" s="27" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="5:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E9" s="30" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" s="127" t="s">
+        <v>121</v>
+      </c>
+      <c r="G9" s="128"/>
+      <c r="H9" s="129"/>
+      <c r="I9" s="127" t="s">
+        <v>54</v>
+      </c>
+      <c r="J9" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="K9" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="L9" s="33"/>
+    </row>
+    <row r="10" spans="5:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E10" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="127" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" s="128"/>
+      <c r="H10" s="129"/>
+      <c r="I10" s="130"/>
+      <c r="J10" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="K10" s="43" t="s">
+        <v>94</v>
+      </c>
+      <c r="L10" s="28"/>
+    </row>
+    <row r="11" spans="5:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E11" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="127" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="128"/>
+      <c r="H11" s="128"/>
+      <c r="I11" s="127" t="s">
+        <v>55</v>
+      </c>
+      <c r="J11" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="K11" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="L11" s="28"/>
+    </row>
+    <row r="12" spans="5:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E12" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="130" t="s">
+        <v>140</v>
+      </c>
+      <c r="G12" s="131"/>
+      <c r="H12" s="131"/>
+      <c r="I12" s="130"/>
+      <c r="J12" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="K12" s="43" t="s">
+        <v>94</v>
+      </c>
+      <c r="L12" s="28"/>
+    </row>
+    <row r="13" spans="5:25" x14ac:dyDescent="0.3">
+      <c r="E13" s="93" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="95">
+        <v>2450210.98</v>
+      </c>
+      <c r="G13" s="96"/>
+      <c r="H13" s="97"/>
+      <c r="I13" s="143" t="s">
+        <v>56</v>
+      </c>
+      <c r="J13" s="143" t="s">
+        <v>61</v>
+      </c>
+      <c r="K13" s="167" t="s">
+        <v>92</v>
+      </c>
+      <c r="L13" s="169" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="14" spans="5:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E14" s="94"/>
+      <c r="F14" s="98"/>
+      <c r="G14" s="99"/>
+      <c r="H14" s="100"/>
+      <c r="I14" s="144"/>
+      <c r="J14" s="144"/>
+      <c r="K14" s="168"/>
+      <c r="L14" s="170"/>
+    </row>
+    <row r="15" spans="5:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E15" s="116"/>
+      <c r="F15" s="116"/>
+    </row>
+    <row r="16" spans="5:25" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E16" s="83" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" s="84"/>
+      <c r="G16" s="84"/>
+      <c r="H16" s="84"/>
+      <c r="I16" s="84"/>
+      <c r="J16" s="84"/>
+      <c r="K16" s="84"/>
+      <c r="L16" s="85"/>
+      <c r="N16" s="77" t="s">
+        <v>95</v>
+      </c>
+      <c r="O16" s="78"/>
+      <c r="P16" s="78"/>
+      <c r="Q16" s="78"/>
+      <c r="R16" s="78"/>
+      <c r="S16" s="78"/>
+      <c r="T16" s="78"/>
+      <c r="U16" s="79"/>
+      <c r="W16" s="117" t="s">
+        <v>158</v>
+      </c>
+      <c r="X16" s="117"/>
+      <c r="Y16" s="117"/>
+    </row>
+    <row r="17" spans="5:25" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E17" s="9"/>
+      <c r="F17" s="113" t="s">
+        <v>2</v>
+      </c>
+      <c r="G17" s="114"/>
+      <c r="H17" s="115"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="K17" s="72" t="s">
+        <v>25</v>
+      </c>
+      <c r="L17" s="74"/>
+      <c r="N17" s="9"/>
+      <c r="O17" s="113" t="s">
+        <v>2</v>
+      </c>
+      <c r="P17" s="114"/>
+      <c r="Q17" s="115"/>
+      <c r="R17" s="8"/>
+      <c r="S17" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="T17" s="113" t="s">
+        <v>25</v>
+      </c>
+      <c r="U17" s="115"/>
+    </row>
+    <row r="18" spans="5:25" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E18" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="F18" s="86" t="s">
+        <v>141</v>
+      </c>
+      <c r="G18" s="87"/>
+      <c r="H18" s="88"/>
+      <c r="I18" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="J18" s="39" t="s">
+        <v>148</v>
+      </c>
+      <c r="K18" s="107" t="s">
+        <v>142</v>
+      </c>
+      <c r="L18" s="108"/>
+      <c r="N18" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="O18" s="89" t="s">
+        <v>163</v>
+      </c>
+      <c r="P18" s="90"/>
+      <c r="Q18" s="91"/>
+      <c r="R18" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="S18" s="47" t="s">
+        <v>165</v>
+      </c>
+      <c r="T18" s="148" t="s">
+        <v>166</v>
+      </c>
+      <c r="U18" s="149"/>
+    </row>
+    <row r="19" spans="5:25" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E19" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F19" s="89" t="s">
+        <v>139</v>
+      </c>
+      <c r="G19" s="90"/>
+      <c r="H19" s="91"/>
+      <c r="I19" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="J19" s="40" t="s">
+        <v>145</v>
+      </c>
+      <c r="K19" s="109"/>
+      <c r="L19" s="110"/>
+      <c r="N19" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="O19" s="152">
+        <v>350605.92</v>
+      </c>
+      <c r="P19" s="153"/>
+      <c r="Q19" s="154"/>
+      <c r="R19" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="S19" s="47" t="s">
+        <v>171</v>
+      </c>
+      <c r="T19" s="150"/>
+      <c r="U19" s="151"/>
+    </row>
+    <row r="20" spans="5:25" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E20" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F20" s="89" t="s">
+        <v>121</v>
+      </c>
+      <c r="G20" s="90"/>
+      <c r="H20" s="91"/>
+      <c r="I20" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="J20" s="40" t="s">
+        <v>144</v>
+      </c>
+      <c r="K20" s="109"/>
+      <c r="L20" s="110"/>
+      <c r="N20" s="155"/>
+      <c r="O20" s="60"/>
+      <c r="P20" s="60"/>
+      <c r="Q20" s="61"/>
+      <c r="R20" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="S20" s="48" t="s">
+        <v>164</v>
+      </c>
+      <c r="T20" s="64"/>
+      <c r="U20" s="65"/>
+    </row>
+    <row r="21" spans="5:25" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E21" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F21" s="89" t="s">
+        <v>140</v>
+      </c>
+      <c r="G21" s="90"/>
+      <c r="H21" s="91"/>
+      <c r="I21" s="37" t="s">
+        <v>33</v>
+      </c>
+      <c r="J21" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="K21" s="109"/>
+      <c r="L21" s="110"/>
+    </row>
+    <row r="22" spans="5:25" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E22" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F22" s="92">
+        <v>46162</v>
+      </c>
+      <c r="G22" s="90"/>
+      <c r="H22" s="91"/>
+      <c r="I22" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="J22" s="40" t="s">
+        <v>143</v>
+      </c>
+      <c r="K22" s="109"/>
+      <c r="L22" s="110"/>
+      <c r="N22" s="77" t="s">
+        <v>96</v>
+      </c>
+      <c r="O22" s="78"/>
+      <c r="P22" s="78"/>
+      <c r="Q22" s="78"/>
+      <c r="R22" s="78"/>
+      <c r="S22" s="78"/>
+      <c r="T22" s="78"/>
+      <c r="U22" s="79"/>
+      <c r="W22" s="117" t="s">
+        <v>158</v>
+      </c>
+      <c r="X22" s="117"/>
+      <c r="Y22" s="117"/>
+    </row>
+    <row r="23" spans="5:25" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E23" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F23" s="59">
+        <v>46497</v>
+      </c>
+      <c r="G23" s="60"/>
+      <c r="H23" s="61"/>
+      <c r="I23" s="147"/>
+      <c r="J23" s="67"/>
+      <c r="K23" s="111"/>
+      <c r="L23" s="112"/>
+      <c r="N23" s="9"/>
+      <c r="O23" s="113" t="s">
+        <v>2</v>
+      </c>
+      <c r="P23" s="114"/>
+      <c r="Q23" s="115"/>
+      <c r="R23" s="8"/>
+      <c r="S23" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="T23" s="113" t="s">
+        <v>25</v>
+      </c>
+      <c r="U23" s="115"/>
+    </row>
+    <row r="24" spans="5:25" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N24" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="O24" s="89" t="s">
+        <v>167</v>
+      </c>
+      <c r="P24" s="90"/>
+      <c r="Q24" s="91"/>
+      <c r="R24" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="S24" s="47" t="s">
+        <v>168</v>
+      </c>
+      <c r="T24" s="148" t="s">
+        <v>170</v>
+      </c>
+      <c r="U24" s="149"/>
+    </row>
+    <row r="25" spans="5:25" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E25" s="83" t="s">
+        <v>26</v>
+      </c>
+      <c r="F25" s="84"/>
+      <c r="G25" s="84"/>
+      <c r="H25" s="84"/>
+      <c r="I25" s="84"/>
+      <c r="J25" s="84"/>
+      <c r="K25" s="84"/>
+      <c r="L25" s="85"/>
+      <c r="N25" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="O25" s="152">
+        <v>262148.15999999997</v>
+      </c>
+      <c r="P25" s="153"/>
+      <c r="Q25" s="154"/>
+      <c r="R25" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="S25" s="51"/>
+      <c r="T25" s="150"/>
+      <c r="U25" s="151"/>
+    </row>
+    <row r="26" spans="5:25" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E26" s="12"/>
+      <c r="F26" s="72" t="s">
+        <v>2</v>
+      </c>
+      <c r="G26" s="73"/>
+      <c r="H26" s="74"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="K26" s="72" t="s">
+        <v>25</v>
+      </c>
+      <c r="L26" s="74"/>
+      <c r="N26" s="155"/>
+      <c r="O26" s="60"/>
+      <c r="P26" s="60"/>
+      <c r="Q26" s="61"/>
+      <c r="R26" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="S26" s="48" t="s">
+        <v>169</v>
+      </c>
+      <c r="T26" s="64"/>
+      <c r="U26" s="65"/>
+    </row>
+    <row r="27" spans="5:25" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E27" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F27" s="57" t="s">
+        <v>149</v>
+      </c>
+      <c r="G27" s="57"/>
+      <c r="H27" s="58"/>
+      <c r="I27" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J27" s="35" t="s">
+        <v>151</v>
+      </c>
+      <c r="K27" s="62" t="s">
+        <v>150</v>
+      </c>
+      <c r="L27" s="63"/>
+    </row>
+    <row r="28" spans="5:25" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E28" s="80"/>
+      <c r="F28" s="81"/>
+      <c r="G28" s="81"/>
+      <c r="H28" s="82"/>
+      <c r="I28" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="J28" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="K28" s="64"/>
+      <c r="L28" s="65"/>
+      <c r="N28" s="83" t="s">
+        <v>98</v>
+      </c>
+      <c r="O28" s="84"/>
+      <c r="P28" s="84"/>
+      <c r="Q28" s="84"/>
+      <c r="R28" s="84"/>
+      <c r="S28" s="84"/>
+      <c r="T28" s="84"/>
+      <c r="U28" s="85"/>
+    </row>
+    <row r="29" spans="5:25" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N29" s="9"/>
+      <c r="O29" s="113" t="s">
+        <v>2</v>
+      </c>
+      <c r="P29" s="114"/>
+      <c r="Q29" s="115"/>
+      <c r="R29" s="8"/>
+      <c r="S29" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="T29" s="113" t="s">
+        <v>25</v>
+      </c>
+      <c r="U29" s="115"/>
+    </row>
+    <row r="30" spans="5:25" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E30" s="83" t="s">
+        <v>28</v>
+      </c>
+      <c r="F30" s="84"/>
+      <c r="G30" s="84"/>
+      <c r="H30" s="84"/>
+      <c r="I30" s="84"/>
+      <c r="J30" s="84"/>
+      <c r="K30" s="84"/>
+      <c r="L30" s="85"/>
+      <c r="N30" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="O30" s="171"/>
+      <c r="P30" s="172"/>
+      <c r="Q30" s="173"/>
+      <c r="R30" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="S30" s="3"/>
+      <c r="T30" s="174"/>
+      <c r="U30" s="175"/>
+    </row>
+    <row r="31" spans="5:25" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E31" s="12"/>
+      <c r="F31" s="72" t="s">
+        <v>2</v>
+      </c>
+      <c r="G31" s="73"/>
+      <c r="H31" s="74"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="K31" s="72" t="s">
+        <v>25</v>
+      </c>
+      <c r="L31" s="74"/>
+      <c r="N31" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="O31" s="171"/>
+      <c r="P31" s="172"/>
+      <c r="Q31" s="173"/>
+      <c r="R31" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="S31" s="3"/>
+      <c r="T31" s="176"/>
+      <c r="U31" s="177"/>
+    </row>
+    <row r="32" spans="5:25" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E32" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F32" s="75"/>
+      <c r="G32" s="75"/>
+      <c r="H32" s="76"/>
+      <c r="I32" s="38" t="s">
+        <v>50</v>
+      </c>
+      <c r="J32" s="17"/>
+      <c r="K32" s="70"/>
+      <c r="L32" s="71"/>
+      <c r="N32" s="155"/>
+      <c r="O32" s="60"/>
+      <c r="P32" s="60"/>
+      <c r="Q32" s="61"/>
+      <c r="R32" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="S32" s="11"/>
+      <c r="T32" s="178"/>
+      <c r="U32" s="179"/>
+    </row>
+    <row r="33" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="34" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E34" s="83" t="s">
+        <v>29</v>
+      </c>
+      <c r="F34" s="84"/>
+      <c r="G34" s="84"/>
+      <c r="H34" s="84"/>
+      <c r="I34" s="84"/>
+      <c r="J34" s="84"/>
+      <c r="K34" s="84"/>
+      <c r="L34" s="85"/>
+      <c r="N34" s="83" t="s">
+        <v>97</v>
+      </c>
+      <c r="O34" s="84"/>
+      <c r="P34" s="84"/>
+      <c r="Q34" s="84"/>
+      <c r="R34" s="84"/>
+      <c r="S34" s="84"/>
+      <c r="T34" s="84"/>
+      <c r="U34" s="85"/>
+    </row>
+    <row r="35" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E35" s="12"/>
+      <c r="F35" s="159" t="s">
+        <v>2</v>
+      </c>
+      <c r="G35" s="160"/>
+      <c r="H35" s="161"/>
+      <c r="I35" s="41"/>
+      <c r="J35" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="K35" s="159" t="s">
+        <v>25</v>
+      </c>
+      <c r="L35" s="161"/>
+      <c r="N35" s="9"/>
+      <c r="O35" s="113" t="s">
+        <v>2</v>
+      </c>
+      <c r="P35" s="114"/>
+      <c r="Q35" s="115"/>
+      <c r="R35" s="8"/>
+      <c r="S35" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="T35" s="113" t="s">
+        <v>25</v>
+      </c>
+      <c r="U35" s="115"/>
+    </row>
+    <row r="36" spans="5:21" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E36" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F36" s="92"/>
+      <c r="G36" s="162"/>
+      <c r="H36" s="163"/>
+      <c r="I36" s="42" t="s">
+        <v>51</v>
+      </c>
+      <c r="J36" s="35"/>
+      <c r="K36" s="62"/>
+      <c r="L36" s="63"/>
+      <c r="N36" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="O36" s="171"/>
+      <c r="P36" s="172"/>
+      <c r="Q36" s="173"/>
+      <c r="R36" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="S36" s="3"/>
+      <c r="T36" s="174"/>
+      <c r="U36" s="175"/>
+    </row>
+    <row r="37" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E37" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F37" s="59"/>
+      <c r="G37" s="164"/>
+      <c r="H37" s="165"/>
+      <c r="I37" s="166"/>
+      <c r="J37" s="66"/>
+      <c r="K37" s="64"/>
+      <c r="L37" s="65"/>
+      <c r="N37" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="O37" s="171"/>
+      <c r="P37" s="172"/>
+      <c r="Q37" s="173"/>
+      <c r="R37" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="S37" s="3"/>
+      <c r="T37" s="176"/>
+      <c r="U37" s="177"/>
+    </row>
+    <row r="38" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N38" s="155"/>
+      <c r="O38" s="60"/>
+      <c r="P38" s="60"/>
+      <c r="Q38" s="61"/>
+      <c r="R38" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="S38" s="11"/>
+      <c r="T38" s="178"/>
+      <c r="U38" s="179"/>
+    </row>
+  </sheetData>
+  <mergeCells count="78">
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="E2:L4"/>
+    <mergeCell ref="E5:L5"/>
+    <mergeCell ref="E6:L6"/>
+    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="I7:L7"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="F12:H12"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="F13:H14"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E16:L16"/>
+    <mergeCell ref="N16:U16"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="T17:U17"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="K18:L23"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="T18:U20"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="N20:Q20"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="N22:U22"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="T23:U23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="T24:U26"/>
+    <mergeCell ref="E25:L25"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="N26:Q26"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="K27:L28"/>
+    <mergeCell ref="E28:H28"/>
+    <mergeCell ref="N28:U28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="T29:U29"/>
+    <mergeCell ref="E30:L30"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="T30:U32"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="K31:L31"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="N32:Q32"/>
+    <mergeCell ref="W16:Y16"/>
+    <mergeCell ref="W22:Y22"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="K36:L37"/>
+    <mergeCell ref="O36:Q36"/>
+    <mergeCell ref="T36:U38"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="O37:Q37"/>
+    <mergeCell ref="N38:Q38"/>
+    <mergeCell ref="E34:L34"/>
+    <mergeCell ref="N34:U34"/>
     <mergeCell ref="F35:H35"/>
     <mergeCell ref="K35:L35"/>
+    <mergeCell ref="O35:Q35"/>
+    <mergeCell ref="T35:U35"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D94A0E1-CBB3-466C-9330-3463FC42EC11}">
+  <dimension ref="E1:U38"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="5" max="5" width="25.77734375" customWidth="1"/>
+    <col min="6" max="6" width="20.77734375" customWidth="1"/>
+    <col min="7" max="8" width="10.77734375" customWidth="1"/>
+    <col min="9" max="9" width="30.77734375" customWidth="1"/>
+    <col min="10" max="10" width="45.77734375" customWidth="1"/>
+    <col min="11" max="12" width="25.77734375" customWidth="1"/>
+    <col min="14" max="14" width="25.77734375" customWidth="1"/>
+    <col min="15" max="15" width="20.77734375" customWidth="1"/>
+    <col min="16" max="17" width="10.77734375" customWidth="1"/>
+    <col min="18" max="18" width="30.77734375" customWidth="1"/>
+    <col min="19" max="19" width="45.77734375" customWidth="1"/>
+    <col min="20" max="21" width="25.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="5:21" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="5:21" x14ac:dyDescent="0.3">
+      <c r="E2" s="118" t="s">
+        <v>118</v>
+      </c>
+      <c r="F2" s="119"/>
+      <c r="G2" s="119"/>
+      <c r="H2" s="119"/>
+      <c r="I2" s="119"/>
+      <c r="J2" s="119"/>
+      <c r="K2" s="119"/>
+      <c r="L2" s="120"/>
+    </row>
+    <row r="3" spans="5:21" x14ac:dyDescent="0.3">
+      <c r="E3" s="121"/>
+      <c r="F3" s="122"/>
+      <c r="G3" s="122"/>
+      <c r="H3" s="122"/>
+      <c r="I3" s="122"/>
+      <c r="J3" s="122"/>
+      <c r="K3" s="122"/>
+      <c r="L3" s="123"/>
+    </row>
+    <row r="4" spans="5:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E4" s="124"/>
+      <c r="F4" s="125"/>
+      <c r="G4" s="125"/>
+      <c r="H4" s="125"/>
+      <c r="I4" s="125"/>
+      <c r="J4" s="125"/>
+      <c r="K4" s="125"/>
+      <c r="L4" s="126"/>
+    </row>
+    <row r="5" spans="5:21" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E5" s="132" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="133"/>
+      <c r="G5" s="133"/>
+      <c r="H5" s="133"/>
+      <c r="I5" s="133"/>
+      <c r="J5" s="133"/>
+      <c r="K5" s="133"/>
+      <c r="L5" s="134"/>
+      <c r="M5" s="23"/>
+      <c r="N5" s="23"/>
+      <c r="O5" s="23"/>
+      <c r="P5" s="23"/>
+    </row>
+    <row r="6" spans="5:21" ht="69" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E6" s="135" t="s">
+        <v>119</v>
+      </c>
+      <c r="F6" s="136"/>
+      <c r="G6" s="136"/>
+      <c r="H6" s="136"/>
+      <c r="I6" s="136"/>
+      <c r="J6" s="136"/>
+      <c r="K6" s="136"/>
+      <c r="L6" s="137"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="24"/>
+      <c r="O6" s="24"/>
+      <c r="P6" s="24"/>
+    </row>
+    <row r="7" spans="5:21" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E7" s="138" t="s">
+        <v>2</v>
+      </c>
+      <c r="F7" s="139"/>
+      <c r="G7" s="139"/>
+      <c r="H7" s="139"/>
+      <c r="I7" s="139" t="s">
+        <v>3</v>
+      </c>
+      <c r="J7" s="139"/>
+      <c r="K7" s="139"/>
+      <c r="L7" s="140"/>
+      <c r="M7" s="25"/>
+      <c r="N7" s="25"/>
+      <c r="O7" s="25"/>
+      <c r="P7" s="25"/>
+    </row>
+    <row r="8" spans="5:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E8" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="141" t="s">
+        <v>120</v>
+      </c>
+      <c r="G8" s="142"/>
+      <c r="H8" s="101"/>
+      <c r="I8" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="J8" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="K8" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="L8" s="27" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="5:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E9" s="30" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" s="127" t="s">
+        <v>121</v>
+      </c>
+      <c r="G9" s="128"/>
+      <c r="H9" s="129"/>
+      <c r="I9" s="127" t="s">
+        <v>54</v>
+      </c>
+      <c r="J9" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="K9" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="L9" s="33"/>
+    </row>
+    <row r="10" spans="5:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E10" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="127" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" s="128"/>
+      <c r="H10" s="129"/>
+      <c r="I10" s="130"/>
+      <c r="J10" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="K10" s="43" t="s">
+        <v>94</v>
+      </c>
+      <c r="L10" s="28"/>
+    </row>
+    <row r="11" spans="5:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E11" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="127" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="128"/>
+      <c r="H11" s="128"/>
+      <c r="I11" s="127" t="s">
+        <v>55</v>
+      </c>
+      <c r="J11" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="K11" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="L11" s="28"/>
+    </row>
+    <row r="12" spans="5:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E12" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="130" t="s">
+        <v>122</v>
+      </c>
+      <c r="G12" s="131"/>
+      <c r="H12" s="131"/>
+      <c r="I12" s="130"/>
+      <c r="J12" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="K12" s="43" t="s">
+        <v>94</v>
+      </c>
+      <c r="L12" s="28"/>
+    </row>
+    <row r="13" spans="5:21" x14ac:dyDescent="0.3">
+      <c r="E13" s="93" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="95">
+        <v>798771.82</v>
+      </c>
+      <c r="G13" s="96"/>
+      <c r="H13" s="97"/>
+      <c r="I13" s="143" t="s">
+        <v>56</v>
+      </c>
+      <c r="J13" s="143" t="s">
+        <v>61</v>
+      </c>
+      <c r="K13" s="167" t="s">
+        <v>92</v>
+      </c>
+      <c r="L13" s="169" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="14" spans="5:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E14" s="94"/>
+      <c r="F14" s="98"/>
+      <c r="G14" s="99"/>
+      <c r="H14" s="100"/>
+      <c r="I14" s="144"/>
+      <c r="J14" s="144"/>
+      <c r="K14" s="168"/>
+      <c r="L14" s="170"/>
+    </row>
+    <row r="15" spans="5:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E15" s="116"/>
+      <c r="F15" s="116"/>
+    </row>
+    <row r="16" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E16" s="83" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" s="84"/>
+      <c r="G16" s="84"/>
+      <c r="H16" s="84"/>
+      <c r="I16" s="84"/>
+      <c r="J16" s="84"/>
+      <c r="K16" s="84"/>
+      <c r="L16" s="85"/>
+      <c r="N16" s="83" t="s">
+        <v>95</v>
+      </c>
+      <c r="O16" s="84"/>
+      <c r="P16" s="84"/>
+      <c r="Q16" s="84"/>
+      <c r="R16" s="84"/>
+      <c r="S16" s="84"/>
+      <c r="T16" s="84"/>
+      <c r="U16" s="85"/>
+    </row>
+    <row r="17" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E17" s="9"/>
+      <c r="F17" s="113" t="s">
+        <v>2</v>
+      </c>
+      <c r="G17" s="114"/>
+      <c r="H17" s="115"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="K17" s="72" t="s">
+        <v>25</v>
+      </c>
+      <c r="L17" s="74"/>
+      <c r="N17" s="9"/>
+      <c r="O17" s="113" t="s">
+        <v>2</v>
+      </c>
+      <c r="P17" s="114"/>
+      <c r="Q17" s="115"/>
+      <c r="R17" s="8"/>
+      <c r="S17" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="T17" s="113" t="s">
+        <v>25</v>
+      </c>
+      <c r="U17" s="115"/>
+    </row>
+    <row r="18" spans="5:21" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E18" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="F18" s="86" t="s">
+        <v>124</v>
+      </c>
+      <c r="G18" s="87"/>
+      <c r="H18" s="88"/>
+      <c r="I18" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="J18" s="39" t="s">
+        <v>126</v>
+      </c>
+      <c r="K18" s="107" t="s">
+        <v>125</v>
+      </c>
+      <c r="L18" s="108"/>
+      <c r="N18" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="O18" s="89" t="s">
+        <v>113</v>
+      </c>
+      <c r="P18" s="90"/>
+      <c r="Q18" s="91"/>
+      <c r="R18" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="S18" s="45" t="s">
+        <v>146</v>
+      </c>
+      <c r="T18" s="148" t="s">
+        <v>134</v>
+      </c>
+      <c r="U18" s="149"/>
+    </row>
+    <row r="19" spans="5:21" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E19" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F19" s="89" t="s">
+        <v>120</v>
+      </c>
+      <c r="G19" s="90"/>
+      <c r="H19" s="91"/>
+      <c r="I19" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="J19" s="40" t="s">
+        <v>127</v>
+      </c>
+      <c r="K19" s="109"/>
+      <c r="L19" s="110"/>
+      <c r="N19" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="O19" s="152">
+        <v>240444.78</v>
+      </c>
+      <c r="P19" s="153"/>
+      <c r="Q19" s="154"/>
+      <c r="R19" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="S19" s="45" t="s">
+        <v>136</v>
+      </c>
+      <c r="T19" s="150"/>
+      <c r="U19" s="151"/>
+    </row>
+    <row r="20" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E20" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F20" s="89" t="s">
+        <v>121</v>
+      </c>
+      <c r="G20" s="90"/>
+      <c r="H20" s="91"/>
+      <c r="I20" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="J20" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="K20" s="109"/>
+      <c r="L20" s="110"/>
+      <c r="N20" s="155"/>
+      <c r="O20" s="60"/>
+      <c r="P20" s="60"/>
+      <c r="Q20" s="61"/>
+      <c r="R20" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="S20" s="44" t="s">
+        <v>70</v>
+      </c>
+      <c r="T20" s="64"/>
+      <c r="U20" s="65"/>
+    </row>
+    <row r="21" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E21" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F21" s="89" t="s">
+        <v>122</v>
+      </c>
+      <c r="G21" s="90"/>
+      <c r="H21" s="91"/>
+      <c r="I21" s="37" t="s">
+        <v>33</v>
+      </c>
+      <c r="J21" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="K21" s="109"/>
+      <c r="L21" s="110"/>
+    </row>
+    <row r="22" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E22" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F22" s="92">
+        <v>46132</v>
+      </c>
+      <c r="G22" s="90"/>
+      <c r="H22" s="91"/>
+      <c r="I22" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="J22" s="40" t="s">
+        <v>129</v>
+      </c>
+      <c r="K22" s="109"/>
+      <c r="L22" s="110"/>
+      <c r="N22" s="83" t="s">
+        <v>96</v>
+      </c>
+      <c r="O22" s="84"/>
+      <c r="P22" s="84"/>
+      <c r="Q22" s="84"/>
+      <c r="R22" s="84"/>
+      <c r="S22" s="84"/>
+      <c r="T22" s="84"/>
+      <c r="U22" s="85"/>
+    </row>
+    <row r="23" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E23" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F23" s="59">
+        <v>46315</v>
+      </c>
+      <c r="G23" s="60"/>
+      <c r="H23" s="61"/>
+      <c r="I23" s="147"/>
+      <c r="J23" s="67"/>
+      <c r="K23" s="111"/>
+      <c r="L23" s="112"/>
+      <c r="N23" s="9"/>
+      <c r="O23" s="113" t="s">
+        <v>2</v>
+      </c>
+      <c r="P23" s="114"/>
+      <c r="Q23" s="115"/>
+      <c r="R23" s="8"/>
+      <c r="S23" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="T23" s="113" t="s">
+        <v>25</v>
+      </c>
+      <c r="U23" s="115"/>
+    </row>
+    <row r="24" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N24" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="O24" s="171"/>
+      <c r="P24" s="172"/>
+      <c r="Q24" s="173"/>
+      <c r="R24" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="S24" s="3"/>
+      <c r="T24" s="174"/>
+      <c r="U24" s="175"/>
+    </row>
+    <row r="25" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E25" s="83" t="s">
+        <v>26</v>
+      </c>
+      <c r="F25" s="84"/>
+      <c r="G25" s="84"/>
+      <c r="H25" s="84"/>
+      <c r="I25" s="84"/>
+      <c r="J25" s="84"/>
+      <c r="K25" s="84"/>
+      <c r="L25" s="85"/>
+      <c r="N25" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="O25" s="171"/>
+      <c r="P25" s="172"/>
+      <c r="Q25" s="173"/>
+      <c r="R25" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="S25" s="3"/>
+      <c r="T25" s="176"/>
+      <c r="U25" s="177"/>
+    </row>
+    <row r="26" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E26" s="12"/>
+      <c r="F26" s="72" t="s">
+        <v>2</v>
+      </c>
+      <c r="G26" s="73"/>
+      <c r="H26" s="74"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="K26" s="72" t="s">
+        <v>25</v>
+      </c>
+      <c r="L26" s="74"/>
+      <c r="N26" s="155"/>
+      <c r="O26" s="60"/>
+      <c r="P26" s="60"/>
+      <c r="Q26" s="61"/>
+      <c r="R26" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="S26" s="11"/>
+      <c r="T26" s="178"/>
+      <c r="U26" s="179"/>
+    </row>
+    <row r="27" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E27" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F27" s="57" t="s">
+        <v>130</v>
+      </c>
+      <c r="G27" s="57"/>
+      <c r="H27" s="58"/>
+      <c r="I27" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J27" s="35" t="s">
+        <v>132</v>
+      </c>
+      <c r="K27" s="62" t="s">
+        <v>131</v>
+      </c>
+      <c r="L27" s="63"/>
+    </row>
+    <row r="28" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E28" s="80"/>
+      <c r="F28" s="81"/>
+      <c r="G28" s="81"/>
+      <c r="H28" s="82"/>
+      <c r="I28" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="J28" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="K28" s="64"/>
+      <c r="L28" s="65"/>
+      <c r="N28" s="83" t="s">
+        <v>98</v>
+      </c>
+      <c r="O28" s="84"/>
+      <c r="P28" s="84"/>
+      <c r="Q28" s="84"/>
+      <c r="R28" s="84"/>
+      <c r="S28" s="84"/>
+      <c r="T28" s="84"/>
+      <c r="U28" s="85"/>
+    </row>
+    <row r="29" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N29" s="9"/>
+      <c r="O29" s="113" t="s">
+        <v>2</v>
+      </c>
+      <c r="P29" s="114"/>
+      <c r="Q29" s="115"/>
+      <c r="R29" s="8"/>
+      <c r="S29" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="T29" s="113" t="s">
+        <v>25</v>
+      </c>
+      <c r="U29" s="115"/>
+    </row>
+    <row r="30" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E30" s="83" t="s">
+        <v>28</v>
+      </c>
+      <c r="F30" s="84"/>
+      <c r="G30" s="84"/>
+      <c r="H30" s="84"/>
+      <c r="I30" s="84"/>
+      <c r="J30" s="84"/>
+      <c r="K30" s="84"/>
+      <c r="L30" s="85"/>
+      <c r="N30" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="O30" s="171"/>
+      <c r="P30" s="172"/>
+      <c r="Q30" s="173"/>
+      <c r="R30" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="S30" s="3"/>
+      <c r="T30" s="174"/>
+      <c r="U30" s="175"/>
+    </row>
+    <row r="31" spans="5:21" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E31" s="12"/>
+      <c r="F31" s="72" t="s">
+        <v>2</v>
+      </c>
+      <c r="G31" s="73"/>
+      <c r="H31" s="74"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="K31" s="72" t="s">
+        <v>25</v>
+      </c>
+      <c r="L31" s="74"/>
+      <c r="N31" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="O31" s="171"/>
+      <c r="P31" s="172"/>
+      <c r="Q31" s="173"/>
+      <c r="R31" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="S31" s="3"/>
+      <c r="T31" s="176"/>
+      <c r="U31" s="177"/>
+    </row>
+    <row r="32" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E32" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F32" s="75"/>
+      <c r="G32" s="75"/>
+      <c r="H32" s="76"/>
+      <c r="I32" s="38" t="s">
+        <v>50</v>
+      </c>
+      <c r="J32" s="17"/>
+      <c r="K32" s="70"/>
+      <c r="L32" s="71"/>
+      <c r="N32" s="155"/>
+      <c r="O32" s="60"/>
+      <c r="P32" s="60"/>
+      <c r="Q32" s="61"/>
+      <c r="R32" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="S32" s="11"/>
+      <c r="T32" s="178"/>
+      <c r="U32" s="179"/>
+    </row>
+    <row r="33" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="34" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E34" s="83" t="s">
+        <v>29</v>
+      </c>
+      <c r="F34" s="84"/>
+      <c r="G34" s="84"/>
+      <c r="H34" s="84"/>
+      <c r="I34" s="84"/>
+      <c r="J34" s="84"/>
+      <c r="K34" s="84"/>
+      <c r="L34" s="85"/>
+      <c r="N34" s="83" t="s">
+        <v>97</v>
+      </c>
+      <c r="O34" s="84"/>
+      <c r="P34" s="84"/>
+      <c r="Q34" s="84"/>
+      <c r="R34" s="84"/>
+      <c r="S34" s="84"/>
+      <c r="T34" s="84"/>
+      <c r="U34" s="85"/>
+    </row>
+    <row r="35" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E35" s="12"/>
+      <c r="F35" s="159" t="s">
+        <v>2</v>
+      </c>
+      <c r="G35" s="160"/>
+      <c r="H35" s="161"/>
+      <c r="I35" s="41"/>
+      <c r="J35" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="K35" s="159" t="s">
+        <v>25</v>
+      </c>
+      <c r="L35" s="161"/>
+      <c r="N35" s="9"/>
+      <c r="O35" s="113" t="s">
+        <v>2</v>
+      </c>
+      <c r="P35" s="114"/>
+      <c r="Q35" s="115"/>
+      <c r="R35" s="8"/>
+      <c r="S35" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="T35" s="113" t="s">
+        <v>25</v>
+      </c>
+      <c r="U35" s="115"/>
+    </row>
+    <row r="36" spans="5:21" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E36" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F36" s="92"/>
+      <c r="G36" s="162"/>
+      <c r="H36" s="163"/>
+      <c r="I36" s="42" t="s">
+        <v>51</v>
+      </c>
+      <c r="J36" s="35"/>
+      <c r="K36" s="62"/>
+      <c r="L36" s="63"/>
+      <c r="N36" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="O36" s="171"/>
+      <c r="P36" s="172"/>
+      <c r="Q36" s="173"/>
+      <c r="R36" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="S36" s="3"/>
+      <c r="T36" s="174"/>
+      <c r="U36" s="175"/>
+    </row>
+    <row r="37" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E37" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F37" s="59"/>
+      <c r="G37" s="164"/>
+      <c r="H37" s="165"/>
+      <c r="I37" s="166"/>
+      <c r="J37" s="66"/>
+      <c r="K37" s="64"/>
+      <c r="L37" s="65"/>
+      <c r="N37" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="O37" s="171"/>
+      <c r="P37" s="172"/>
+      <c r="Q37" s="173"/>
+      <c r="R37" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="S37" s="3"/>
+      <c r="T37" s="176"/>
+      <c r="U37" s="177"/>
+    </row>
+    <row r="38" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N38" s="155"/>
+      <c r="O38" s="60"/>
+      <c r="P38" s="60"/>
+      <c r="Q38" s="61"/>
+      <c r="R38" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="S38" s="11"/>
+      <c r="T38" s="178"/>
+      <c r="U38" s="179"/>
+    </row>
+  </sheetData>
+  <mergeCells count="76">
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="E2:L4"/>
+    <mergeCell ref="E5:L5"/>
+    <mergeCell ref="E6:L6"/>
+    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="I7:L7"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="F12:H12"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="F13:H14"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E16:L16"/>
+    <mergeCell ref="N16:U16"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="T17:U17"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="K18:L23"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="T18:U20"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="N20:Q20"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="N22:U22"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="T23:U23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="T24:U26"/>
+    <mergeCell ref="E25:L25"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="N26:Q26"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="K27:L28"/>
+    <mergeCell ref="E28:H28"/>
+    <mergeCell ref="N28:U28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="T29:U29"/>
+    <mergeCell ref="E30:L30"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="T30:U32"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="K31:L31"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="N32:Q32"/>
+    <mergeCell ref="E34:L34"/>
+    <mergeCell ref="N34:U34"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="K35:L35"/>
+    <mergeCell ref="O35:Q35"/>
+    <mergeCell ref="T35:U35"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="K36:L37"/>
+    <mergeCell ref="O36:Q36"/>
+    <mergeCell ref="T36:U38"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="O37:Q37"/>
+    <mergeCell ref="N38:Q38"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{621D4197-6F6C-401B-A94B-8D2D5B073552}">
+  <dimension ref="E1:M38"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="5" max="5" width="25.77734375" customWidth="1"/>
+    <col min="6" max="6" width="20.77734375" customWidth="1"/>
+    <col min="7" max="8" width="10.77734375" customWidth="1"/>
+    <col min="9" max="9" width="30.77734375" customWidth="1"/>
+    <col min="10" max="10" width="45.77734375" customWidth="1"/>
+    <col min="11" max="12" width="25.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E2" s="118" t="s">
+        <v>172</v>
+      </c>
+      <c r="F2" s="119"/>
+      <c r="G2" s="119"/>
+      <c r="H2" s="119"/>
+      <c r="I2" s="119"/>
+      <c r="J2" s="119"/>
+      <c r="K2" s="119"/>
+      <c r="L2" s="120"/>
+    </row>
+    <row r="3" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E3" s="121"/>
+      <c r="F3" s="122"/>
+      <c r="G3" s="122"/>
+      <c r="H3" s="122"/>
+      <c r="I3" s="122"/>
+      <c r="J3" s="122"/>
+      <c r="K3" s="122"/>
+      <c r="L3" s="123"/>
+    </row>
+    <row r="4" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E4" s="124"/>
+      <c r="F4" s="125"/>
+      <c r="G4" s="125"/>
+      <c r="H4" s="125"/>
+      <c r="I4" s="125"/>
+      <c r="J4" s="125"/>
+      <c r="K4" s="125"/>
+      <c r="L4" s="126"/>
+    </row>
+    <row r="5" spans="5:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E5" s="132" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="133"/>
+      <c r="G5" s="133"/>
+      <c r="H5" s="133"/>
+      <c r="I5" s="133"/>
+      <c r="J5" s="133"/>
+      <c r="K5" s="133"/>
+      <c r="L5" s="134"/>
+      <c r="M5" s="23"/>
+    </row>
+    <row r="6" spans="5:13" ht="69" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E6" s="180" t="s">
+        <v>173</v>
+      </c>
+      <c r="F6" s="181"/>
+      <c r="G6" s="181"/>
+      <c r="H6" s="181"/>
+      <c r="I6" s="181"/>
+      <c r="J6" s="181"/>
+      <c r="K6" s="181"/>
+      <c r="L6" s="182"/>
+      <c r="M6" s="24"/>
+    </row>
+    <row r="7" spans="5:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E7" s="138" t="s">
+        <v>2</v>
+      </c>
+      <c r="F7" s="139"/>
+      <c r="G7" s="139"/>
+      <c r="H7" s="139"/>
+      <c r="I7" s="139" t="s">
+        <v>3</v>
+      </c>
+      <c r="J7" s="139"/>
+      <c r="K7" s="139"/>
+      <c r="L7" s="140"/>
+      <c r="M7" s="25"/>
+    </row>
+    <row r="8" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E8" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="141" t="s">
+        <v>174</v>
+      </c>
+      <c r="G8" s="142"/>
+      <c r="H8" s="101"/>
+      <c r="I8" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="J8" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="K8" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="L8" s="27" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E9" s="30" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" s="127" t="s">
+        <v>121</v>
+      </c>
+      <c r="G9" s="128"/>
+      <c r="H9" s="129"/>
+      <c r="I9" s="183" t="s">
+        <v>54</v>
+      </c>
+      <c r="J9" s="54" t="s">
+        <v>57</v>
+      </c>
+      <c r="K9" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="L9" s="33"/>
+    </row>
+    <row r="10" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E10" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="127" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" s="128"/>
+      <c r="H10" s="129"/>
+      <c r="I10" s="184"/>
+      <c r="J10" s="54" t="s">
+        <v>58</v>
+      </c>
+      <c r="K10" s="43" t="s">
+        <v>94</v>
+      </c>
+      <c r="L10" s="28"/>
+    </row>
+    <row r="11" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E11" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="127" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="128"/>
+      <c r="H11" s="128"/>
+      <c r="I11" s="185" t="s">
+        <v>55</v>
+      </c>
+      <c r="J11" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="K11" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="L11" s="28"/>
+    </row>
+    <row r="12" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E12" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="130" t="s">
+        <v>175</v>
+      </c>
+      <c r="G12" s="131"/>
+      <c r="H12" s="131"/>
+      <c r="I12" s="186"/>
+      <c r="J12" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="K12" s="43" t="s">
+        <v>94</v>
+      </c>
+      <c r="L12" s="28"/>
+    </row>
+    <row r="13" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E13" s="93" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="95">
+        <v>457556.31</v>
+      </c>
+      <c r="G13" s="96"/>
+      <c r="H13" s="96"/>
+      <c r="I13" s="103" t="s">
+        <v>56</v>
+      </c>
+      <c r="J13" s="103" t="s">
+        <v>61</v>
+      </c>
+      <c r="K13" s="103"/>
+      <c r="L13" s="169"/>
+    </row>
+    <row r="14" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E14" s="94"/>
+      <c r="F14" s="98"/>
+      <c r="G14" s="99"/>
+      <c r="H14" s="99"/>
+      <c r="I14" s="104"/>
+      <c r="J14" s="104"/>
+      <c r="K14" s="104"/>
+      <c r="L14" s="170"/>
+    </row>
+    <row r="15" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E15" s="116"/>
+      <c r="F15" s="116"/>
+    </row>
+    <row r="16" spans="5:13" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E16" s="190" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" s="191"/>
+      <c r="G16" s="191"/>
+      <c r="H16" s="191"/>
+      <c r="I16" s="191"/>
+      <c r="J16" s="191"/>
+      <c r="K16" s="191"/>
+      <c r="L16" s="192"/>
+    </row>
+    <row r="17" spans="5:12" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E17" s="9"/>
+      <c r="F17" s="113" t="s">
+        <v>2</v>
+      </c>
+      <c r="G17" s="114"/>
+      <c r="H17" s="115"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="K17" s="113" t="s">
+        <v>25</v>
+      </c>
+      <c r="L17" s="115"/>
+    </row>
+    <row r="18" spans="5:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E18" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="F18" s="86" t="s">
+        <v>177</v>
+      </c>
+      <c r="G18" s="87"/>
+      <c r="H18" s="88"/>
+      <c r="I18" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="J18" s="39" t="s">
+        <v>181</v>
+      </c>
+      <c r="K18" s="187" t="s">
+        <v>176</v>
+      </c>
+      <c r="L18" s="108"/>
+    </row>
+    <row r="19" spans="5:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E19" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F19" s="89" t="s">
+        <v>174</v>
+      </c>
+      <c r="G19" s="90"/>
+      <c r="H19" s="91"/>
+      <c r="I19" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="J19" s="40" t="s">
+        <v>180</v>
+      </c>
+      <c r="K19" s="188"/>
+      <c r="L19" s="110"/>
+    </row>
+    <row r="20" spans="5:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E20" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F20" s="89" t="s">
+        <v>121</v>
+      </c>
+      <c r="G20" s="90"/>
+      <c r="H20" s="91"/>
+      <c r="I20" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="J20" s="40" t="s">
+        <v>179</v>
+      </c>
+      <c r="K20" s="188"/>
+      <c r="L20" s="110"/>
+    </row>
+    <row r="21" spans="5:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E21" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F21" s="89" t="s">
+        <v>175</v>
+      </c>
+      <c r="G21" s="90"/>
+      <c r="H21" s="91"/>
+      <c r="I21" s="37" t="s">
+        <v>33</v>
+      </c>
+      <c r="J21" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="K21" s="188"/>
+      <c r="L21" s="110"/>
+    </row>
+    <row r="22" spans="5:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E22" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F22" s="92">
+        <v>45971</v>
+      </c>
+      <c r="G22" s="162"/>
+      <c r="H22" s="163"/>
+      <c r="I22" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="J22" s="40" t="s">
+        <v>178</v>
+      </c>
+      <c r="K22" s="188"/>
+      <c r="L22" s="110"/>
+    </row>
+    <row r="23" spans="5:12" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E23" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F23" s="59">
+        <v>46213</v>
+      </c>
+      <c r="G23" s="164"/>
+      <c r="H23" s="165"/>
+      <c r="I23" s="166"/>
+      <c r="J23" s="66"/>
+      <c r="K23" s="189"/>
+      <c r="L23" s="112"/>
+    </row>
+    <row r="24" spans="5:12" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="25" spans="5:12" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E25" s="190" t="s">
+        <v>26</v>
+      </c>
+      <c r="F25" s="191"/>
+      <c r="G25" s="191"/>
+      <c r="H25" s="191"/>
+      <c r="I25" s="191"/>
+      <c r="J25" s="191"/>
+      <c r="K25" s="191"/>
+      <c r="L25" s="192"/>
+    </row>
+    <row r="26" spans="5:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E26" s="12"/>
+      <c r="F26" s="159" t="s">
+        <v>2</v>
+      </c>
+      <c r="G26" s="160"/>
+      <c r="H26" s="161"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="K26" s="159" t="s">
+        <v>25</v>
+      </c>
+      <c r="L26" s="161"/>
+    </row>
+    <row r="27" spans="5:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E27" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F27" s="89"/>
+      <c r="G27" s="90"/>
+      <c r="H27" s="91"/>
+      <c r="I27" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J27" s="49"/>
+      <c r="K27" s="62"/>
+      <c r="L27" s="63"/>
+    </row>
+    <row r="28" spans="5:12" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E28" s="155"/>
+      <c r="F28" s="60"/>
+      <c r="G28" s="60"/>
+      <c r="H28" s="61"/>
+      <c r="I28" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="J28" s="50"/>
+      <c r="K28" s="64"/>
+      <c r="L28" s="65"/>
+    </row>
+    <row r="29" spans="5:12" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="30" spans="5:12" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E30" s="190" t="s">
+        <v>28</v>
+      </c>
+      <c r="F30" s="191"/>
+      <c r="G30" s="191"/>
+      <c r="H30" s="191"/>
+      <c r="I30" s="191"/>
+      <c r="J30" s="191"/>
+      <c r="K30" s="191"/>
+      <c r="L30" s="192"/>
+    </row>
+    <row r="31" spans="5:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E31" s="12"/>
+      <c r="F31" s="159" t="s">
+        <v>2</v>
+      </c>
+      <c r="G31" s="160"/>
+      <c r="H31" s="161"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="K31" s="159" t="s">
+        <v>25</v>
+      </c>
+      <c r="L31" s="161"/>
+    </row>
+    <row r="32" spans="5:12" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E32" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F32" s="193"/>
+      <c r="G32" s="60"/>
+      <c r="H32" s="61"/>
+      <c r="I32" s="38" t="s">
+        <v>50</v>
+      </c>
+      <c r="J32" s="50"/>
+      <c r="K32" s="194"/>
+      <c r="L32" s="195"/>
+    </row>
+    <row r="33" spans="5:12" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="34" spans="5:12" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E34" s="190" t="s">
+        <v>29</v>
+      </c>
+      <c r="F34" s="191"/>
+      <c r="G34" s="191"/>
+      <c r="H34" s="191"/>
+      <c r="I34" s="191"/>
+      <c r="J34" s="191"/>
+      <c r="K34" s="191"/>
+      <c r="L34" s="192"/>
+    </row>
+    <row r="35" spans="5:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E35" s="12"/>
+      <c r="F35" s="159" t="s">
+        <v>2</v>
+      </c>
+      <c r="G35" s="160"/>
+      <c r="H35" s="161"/>
+      <c r="I35" s="41"/>
+      <c r="J35" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="K35" s="159" t="s">
+        <v>25</v>
+      </c>
+      <c r="L35" s="161"/>
+    </row>
+    <row r="36" spans="5:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E36" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F36" s="92"/>
+      <c r="G36" s="162"/>
+      <c r="H36" s="163"/>
+      <c r="I36" s="42" t="s">
+        <v>51</v>
+      </c>
+      <c r="J36" s="49"/>
+      <c r="K36" s="62"/>
+      <c r="L36" s="63"/>
+    </row>
+    <row r="37" spans="5:12" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E37" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F37" s="59"/>
+      <c r="G37" s="164"/>
+      <c r="H37" s="165"/>
+      <c r="I37" s="166"/>
+      <c r="J37" s="66"/>
+      <c r="K37" s="64"/>
+      <c r="L37" s="65"/>
+    </row>
+    <row r="38" spans="5:12" ht="30" customHeight="1" x14ac:dyDescent="0.3"/>
+  </sheetData>
+  <mergeCells count="48">
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="E16:L16"/>
     <mergeCell ref="F36:H36"/>
     <mergeCell ref="K36:L37"/>
     <mergeCell ref="F37:H37"/>
     <mergeCell ref="I37:J37"/>
     <mergeCell ref="E34:L34"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="E25:L25"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="K26:L26"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="K27:L28"/>
-    <mergeCell ref="E28:H28"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="K35:L35"/>
     <mergeCell ref="E30:L30"/>
     <mergeCell ref="F31:H31"/>
     <mergeCell ref="K31:L31"/>
     <mergeCell ref="F32:H32"/>
     <mergeCell ref="K32:L32"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="E16:L16"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="K27:L28"/>
+    <mergeCell ref="E28:H28"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="E25:L25"/>
+    <mergeCell ref="F26:H26"/>
     <mergeCell ref="F18:H18"/>
     <mergeCell ref="K18:L23"/>
     <mergeCell ref="F19:H19"/>
     <mergeCell ref="F20:H20"/>
     <mergeCell ref="F21:H21"/>
     <mergeCell ref="F22:H22"/>
+    <mergeCell ref="E15:F15"/>
     <mergeCell ref="E13:E14"/>
     <mergeCell ref="F13:H14"/>
     <mergeCell ref="I13:I14"/>
@@ -3836,8 +6497,883 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D94A0E1-CBB3-466C-9330-3463FC42EC11}">
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26478210-C0CA-4F53-8768-85CD95C25346}">
+  <dimension ref="E1:AC38"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="5" max="5" width="25.77734375" customWidth="1"/>
+    <col min="6" max="6" width="20.77734375" customWidth="1"/>
+    <col min="7" max="8" width="10.77734375" customWidth="1"/>
+    <col min="9" max="9" width="30.77734375" customWidth="1"/>
+    <col min="10" max="10" width="45.77734375" customWidth="1"/>
+    <col min="11" max="12" width="25.77734375" customWidth="1"/>
+    <col min="14" max="14" width="25.77734375" customWidth="1"/>
+    <col min="15" max="15" width="20.77734375" customWidth="1"/>
+    <col min="16" max="17" width="10.77734375" customWidth="1"/>
+    <col min="18" max="18" width="30.77734375" customWidth="1"/>
+    <col min="19" max="19" width="45.77734375" customWidth="1"/>
+    <col min="20" max="21" width="25.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="5:29" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="5:29" x14ac:dyDescent="0.3">
+      <c r="E2" s="118" t="s">
+        <v>183</v>
+      </c>
+      <c r="F2" s="119"/>
+      <c r="G2" s="119"/>
+      <c r="H2" s="119"/>
+      <c r="I2" s="119"/>
+      <c r="J2" s="119"/>
+      <c r="K2" s="119"/>
+      <c r="L2" s="120"/>
+    </row>
+    <row r="3" spans="5:29" x14ac:dyDescent="0.3">
+      <c r="E3" s="121"/>
+      <c r="F3" s="122"/>
+      <c r="G3" s="122"/>
+      <c r="H3" s="122"/>
+      <c r="I3" s="122"/>
+      <c r="J3" s="122"/>
+      <c r="K3" s="122"/>
+      <c r="L3" s="123"/>
+    </row>
+    <row r="4" spans="5:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E4" s="124"/>
+      <c r="F4" s="125"/>
+      <c r="G4" s="125"/>
+      <c r="H4" s="125"/>
+      <c r="I4" s="125"/>
+      <c r="J4" s="125"/>
+      <c r="K4" s="125"/>
+      <c r="L4" s="126"/>
+    </row>
+    <row r="5" spans="5:29" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E5" s="132" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="133"/>
+      <c r="G5" s="133"/>
+      <c r="H5" s="133"/>
+      <c r="I5" s="133"/>
+      <c r="J5" s="133"/>
+      <c r="K5" s="133"/>
+      <c r="L5" s="134"/>
+      <c r="M5" s="23"/>
+      <c r="N5" s="23"/>
+      <c r="O5" s="23"/>
+      <c r="P5" s="23"/>
+    </row>
+    <row r="6" spans="5:29" ht="69" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E6" s="135" t="s">
+        <v>184</v>
+      </c>
+      <c r="F6" s="136"/>
+      <c r="G6" s="136"/>
+      <c r="H6" s="136"/>
+      <c r="I6" s="136"/>
+      <c r="J6" s="136"/>
+      <c r="K6" s="136"/>
+      <c r="L6" s="137"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="24"/>
+      <c r="O6" s="24"/>
+      <c r="P6" s="24"/>
+    </row>
+    <row r="7" spans="5:29" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E7" s="138" t="s">
+        <v>2</v>
+      </c>
+      <c r="F7" s="139"/>
+      <c r="G7" s="139"/>
+      <c r="H7" s="139"/>
+      <c r="I7" s="139" t="s">
+        <v>3</v>
+      </c>
+      <c r="J7" s="139"/>
+      <c r="K7" s="139"/>
+      <c r="L7" s="140"/>
+      <c r="M7" s="25"/>
+      <c r="N7" s="25"/>
+      <c r="O7" s="25"/>
+      <c r="P7" s="25"/>
+    </row>
+    <row r="8" spans="5:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E8" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="141" t="s">
+        <v>185</v>
+      </c>
+      <c r="G8" s="142"/>
+      <c r="H8" s="101"/>
+      <c r="I8" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="J8" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="K8" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="L8" s="27" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="5:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E9" s="30" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" s="127" t="s">
+        <v>186</v>
+      </c>
+      <c r="G9" s="128"/>
+      <c r="H9" s="129"/>
+      <c r="I9" s="127" t="s">
+        <v>54</v>
+      </c>
+      <c r="J9" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="K9" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="L9" s="33"/>
+    </row>
+    <row r="10" spans="5:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E10" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="127" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" s="128"/>
+      <c r="H10" s="129"/>
+      <c r="I10" s="130"/>
+      <c r="J10" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="K10" s="43" t="s">
+        <v>94</v>
+      </c>
+      <c r="L10" s="28"/>
+    </row>
+    <row r="11" spans="5:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E11" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="127" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="128"/>
+      <c r="H11" s="128"/>
+      <c r="I11" s="127" t="s">
+        <v>55</v>
+      </c>
+      <c r="J11" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="K11" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="L11" s="28"/>
+    </row>
+    <row r="12" spans="5:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E12" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="130" t="s">
+        <v>187</v>
+      </c>
+      <c r="G12" s="131"/>
+      <c r="H12" s="131"/>
+      <c r="I12" s="130"/>
+      <c r="J12" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="K12" s="43" t="s">
+        <v>94</v>
+      </c>
+      <c r="L12" s="28"/>
+    </row>
+    <row r="13" spans="5:29" x14ac:dyDescent="0.3">
+      <c r="E13" s="93" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="95">
+        <v>600283.5</v>
+      </c>
+      <c r="G13" s="96"/>
+      <c r="H13" s="97"/>
+      <c r="I13" s="143" t="s">
+        <v>56</v>
+      </c>
+      <c r="J13" s="143" t="s">
+        <v>61</v>
+      </c>
+      <c r="K13" s="167" t="s">
+        <v>92</v>
+      </c>
+      <c r="L13" s="169" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="14" spans="5:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E14" s="94"/>
+      <c r="F14" s="98"/>
+      <c r="G14" s="99"/>
+      <c r="H14" s="100"/>
+      <c r="I14" s="144"/>
+      <c r="J14" s="144"/>
+      <c r="K14" s="168"/>
+      <c r="L14" s="170"/>
+    </row>
+    <row r="15" spans="5:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E15" s="116"/>
+      <c r="F15" s="116"/>
+    </row>
+    <row r="16" spans="5:29" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E16" s="83" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" s="84"/>
+      <c r="G16" s="84"/>
+      <c r="H16" s="84"/>
+      <c r="I16" s="84"/>
+      <c r="J16" s="84"/>
+      <c r="K16" s="84"/>
+      <c r="L16" s="85"/>
+      <c r="N16" s="77" t="s">
+        <v>95</v>
+      </c>
+      <c r="O16" s="78"/>
+      <c r="P16" s="78"/>
+      <c r="Q16" s="78"/>
+      <c r="R16" s="78"/>
+      <c r="S16" s="78"/>
+      <c r="T16" s="78"/>
+      <c r="U16" s="79"/>
+      <c r="W16" s="234" t="s">
+        <v>158</v>
+      </c>
+      <c r="X16" s="234"/>
+      <c r="Y16" s="234"/>
+      <c r="AA16" s="235" t="s">
+        <v>223</v>
+      </c>
+      <c r="AB16" s="235"/>
+      <c r="AC16" s="235"/>
+    </row>
+    <row r="17" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E17" s="9"/>
+      <c r="F17" s="113" t="s">
+        <v>2</v>
+      </c>
+      <c r="G17" s="114"/>
+      <c r="H17" s="115"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="K17" s="72" t="s">
+        <v>25</v>
+      </c>
+      <c r="L17" s="74"/>
+      <c r="N17" s="9"/>
+      <c r="O17" s="113" t="s">
+        <v>2</v>
+      </c>
+      <c r="P17" s="114"/>
+      <c r="Q17" s="115"/>
+      <c r="R17" s="8"/>
+      <c r="S17" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="T17" s="113" t="s">
+        <v>25</v>
+      </c>
+      <c r="U17" s="115"/>
+    </row>
+    <row r="18" spans="5:21" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E18" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="F18" s="86" t="s">
+        <v>188</v>
+      </c>
+      <c r="G18" s="87"/>
+      <c r="H18" s="88"/>
+      <c r="I18" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="J18" s="39" t="s">
+        <v>193</v>
+      </c>
+      <c r="K18" s="107" t="s">
+        <v>189</v>
+      </c>
+      <c r="L18" s="108"/>
+      <c r="N18" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="O18" s="89" t="s">
+        <v>200</v>
+      </c>
+      <c r="P18" s="90"/>
+      <c r="Q18" s="91"/>
+      <c r="R18" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="S18" s="55" t="s">
+        <v>201</v>
+      </c>
+      <c r="T18" s="148" t="s">
+        <v>198</v>
+      </c>
+      <c r="U18" s="149"/>
+    </row>
+    <row r="19" spans="5:21" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E19" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F19" s="89" t="s">
+        <v>185</v>
+      </c>
+      <c r="G19" s="90"/>
+      <c r="H19" s="91"/>
+      <c r="I19" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="J19" s="40" t="s">
+        <v>192</v>
+      </c>
+      <c r="K19" s="109"/>
+      <c r="L19" s="110"/>
+      <c r="N19" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="O19" s="152">
+        <v>58338.41</v>
+      </c>
+      <c r="P19" s="153"/>
+      <c r="Q19" s="154"/>
+      <c r="R19" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="S19" s="52" t="s">
+        <v>202</v>
+      </c>
+      <c r="T19" s="150"/>
+      <c r="U19" s="151"/>
+    </row>
+    <row r="20" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E20" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F20" s="89" t="s">
+        <v>186</v>
+      </c>
+      <c r="G20" s="90"/>
+      <c r="H20" s="91"/>
+      <c r="I20" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="J20" s="40" t="s">
+        <v>191</v>
+      </c>
+      <c r="K20" s="109"/>
+      <c r="L20" s="110"/>
+      <c r="N20" s="155"/>
+      <c r="O20" s="60"/>
+      <c r="P20" s="60"/>
+      <c r="Q20" s="61"/>
+      <c r="R20" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="S20" s="53" t="s">
+        <v>199</v>
+      </c>
+      <c r="T20" s="64"/>
+      <c r="U20" s="65"/>
+    </row>
+    <row r="21" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E21" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F21" s="89" t="s">
+        <v>187</v>
+      </c>
+      <c r="G21" s="90"/>
+      <c r="H21" s="91"/>
+      <c r="I21" s="37" t="s">
+        <v>33</v>
+      </c>
+      <c r="J21" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="K21" s="109"/>
+      <c r="L21" s="110"/>
+    </row>
+    <row r="22" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E22" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F22" s="92">
+        <v>46093</v>
+      </c>
+      <c r="G22" s="90"/>
+      <c r="H22" s="91"/>
+      <c r="I22" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="J22" s="40" t="s">
+        <v>190</v>
+      </c>
+      <c r="K22" s="109"/>
+      <c r="L22" s="110"/>
+      <c r="N22" s="83" t="s">
+        <v>96</v>
+      </c>
+      <c r="O22" s="84"/>
+      <c r="P22" s="84"/>
+      <c r="Q22" s="84"/>
+      <c r="R22" s="84"/>
+      <c r="S22" s="84"/>
+      <c r="T22" s="84"/>
+      <c r="U22" s="85"/>
+    </row>
+    <row r="23" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E23" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F23" s="59">
+        <v>46276</v>
+      </c>
+      <c r="G23" s="60"/>
+      <c r="H23" s="61"/>
+      <c r="I23" s="147"/>
+      <c r="J23" s="67"/>
+      <c r="K23" s="111"/>
+      <c r="L23" s="112"/>
+      <c r="N23" s="9"/>
+      <c r="O23" s="113" t="s">
+        <v>2</v>
+      </c>
+      <c r="P23" s="114"/>
+      <c r="Q23" s="115"/>
+      <c r="R23" s="8"/>
+      <c r="S23" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="T23" s="113" t="s">
+        <v>25</v>
+      </c>
+      <c r="U23" s="115"/>
+    </row>
+    <row r="24" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N24" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="O24" s="171"/>
+      <c r="P24" s="172"/>
+      <c r="Q24" s="173"/>
+      <c r="R24" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="S24" s="3"/>
+      <c r="T24" s="174"/>
+      <c r="U24" s="175"/>
+    </row>
+    <row r="25" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E25" s="83" t="s">
+        <v>26</v>
+      </c>
+      <c r="F25" s="84"/>
+      <c r="G25" s="84"/>
+      <c r="H25" s="84"/>
+      <c r="I25" s="84"/>
+      <c r="J25" s="84"/>
+      <c r="K25" s="84"/>
+      <c r="L25" s="85"/>
+      <c r="N25" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="O25" s="171"/>
+      <c r="P25" s="172"/>
+      <c r="Q25" s="173"/>
+      <c r="R25" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="S25" s="3"/>
+      <c r="T25" s="176"/>
+      <c r="U25" s="177"/>
+    </row>
+    <row r="26" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E26" s="12"/>
+      <c r="F26" s="72" t="s">
+        <v>2</v>
+      </c>
+      <c r="G26" s="73"/>
+      <c r="H26" s="74"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="K26" s="72" t="s">
+        <v>25</v>
+      </c>
+      <c r="L26" s="74"/>
+      <c r="N26" s="155"/>
+      <c r="O26" s="60"/>
+      <c r="P26" s="60"/>
+      <c r="Q26" s="61"/>
+      <c r="R26" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="S26" s="11"/>
+      <c r="T26" s="178"/>
+      <c r="U26" s="179"/>
+    </row>
+    <row r="27" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E27" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F27" s="57" t="s">
+        <v>194</v>
+      </c>
+      <c r="G27" s="57"/>
+      <c r="H27" s="58"/>
+      <c r="I27" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J27" s="52" t="s">
+        <v>197</v>
+      </c>
+      <c r="K27" s="62" t="s">
+        <v>195</v>
+      </c>
+      <c r="L27" s="63"/>
+    </row>
+    <row r="28" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E28" s="80"/>
+      <c r="F28" s="81"/>
+      <c r="G28" s="81"/>
+      <c r="H28" s="82"/>
+      <c r="I28" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="J28" s="53" t="s">
+        <v>196</v>
+      </c>
+      <c r="K28" s="64"/>
+      <c r="L28" s="65"/>
+      <c r="N28" s="83" t="s">
+        <v>98</v>
+      </c>
+      <c r="O28" s="84"/>
+      <c r="P28" s="84"/>
+      <c r="Q28" s="84"/>
+      <c r="R28" s="84"/>
+      <c r="S28" s="84"/>
+      <c r="T28" s="84"/>
+      <c r="U28" s="85"/>
+    </row>
+    <row r="29" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N29" s="9"/>
+      <c r="O29" s="113" t="s">
+        <v>2</v>
+      </c>
+      <c r="P29" s="114"/>
+      <c r="Q29" s="115"/>
+      <c r="R29" s="8"/>
+      <c r="S29" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="T29" s="113" t="s">
+        <v>25</v>
+      </c>
+      <c r="U29" s="115"/>
+    </row>
+    <row r="30" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E30" s="83" t="s">
+        <v>28</v>
+      </c>
+      <c r="F30" s="84"/>
+      <c r="G30" s="84"/>
+      <c r="H30" s="84"/>
+      <c r="I30" s="84"/>
+      <c r="J30" s="84"/>
+      <c r="K30" s="84"/>
+      <c r="L30" s="85"/>
+      <c r="N30" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="O30" s="171"/>
+      <c r="P30" s="172"/>
+      <c r="Q30" s="173"/>
+      <c r="R30" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="S30" s="3"/>
+      <c r="T30" s="174"/>
+      <c r="U30" s="175"/>
+    </row>
+    <row r="31" spans="5:21" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E31" s="12"/>
+      <c r="F31" s="72" t="s">
+        <v>2</v>
+      </c>
+      <c r="G31" s="73"/>
+      <c r="H31" s="74"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="K31" s="72" t="s">
+        <v>25</v>
+      </c>
+      <c r="L31" s="74"/>
+      <c r="N31" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="O31" s="171"/>
+      <c r="P31" s="172"/>
+      <c r="Q31" s="173"/>
+      <c r="R31" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="S31" s="3"/>
+      <c r="T31" s="176"/>
+      <c r="U31" s="177"/>
+    </row>
+    <row r="32" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E32" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F32" s="75"/>
+      <c r="G32" s="75"/>
+      <c r="H32" s="76"/>
+      <c r="I32" s="38" t="s">
+        <v>50</v>
+      </c>
+      <c r="J32" s="53"/>
+      <c r="K32" s="70"/>
+      <c r="L32" s="71"/>
+      <c r="N32" s="155"/>
+      <c r="O32" s="60"/>
+      <c r="P32" s="60"/>
+      <c r="Q32" s="61"/>
+      <c r="R32" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="S32" s="11"/>
+      <c r="T32" s="178"/>
+      <c r="U32" s="179"/>
+    </row>
+    <row r="33" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="34" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E34" s="83" t="s">
+        <v>29</v>
+      </c>
+      <c r="F34" s="84"/>
+      <c r="G34" s="84"/>
+      <c r="H34" s="84"/>
+      <c r="I34" s="84"/>
+      <c r="J34" s="84"/>
+      <c r="K34" s="84"/>
+      <c r="L34" s="85"/>
+      <c r="N34" s="83" t="s">
+        <v>97</v>
+      </c>
+      <c r="O34" s="84"/>
+      <c r="P34" s="84"/>
+      <c r="Q34" s="84"/>
+      <c r="R34" s="84"/>
+      <c r="S34" s="84"/>
+      <c r="T34" s="84"/>
+      <c r="U34" s="85"/>
+    </row>
+    <row r="35" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E35" s="12"/>
+      <c r="F35" s="159" t="s">
+        <v>2</v>
+      </c>
+      <c r="G35" s="160"/>
+      <c r="H35" s="161"/>
+      <c r="I35" s="41"/>
+      <c r="J35" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="K35" s="159" t="s">
+        <v>25</v>
+      </c>
+      <c r="L35" s="161"/>
+      <c r="N35" s="9"/>
+      <c r="O35" s="113" t="s">
+        <v>2</v>
+      </c>
+      <c r="P35" s="114"/>
+      <c r="Q35" s="115"/>
+      <c r="R35" s="8"/>
+      <c r="S35" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="T35" s="113" t="s">
+        <v>25</v>
+      </c>
+      <c r="U35" s="115"/>
+    </row>
+    <row r="36" spans="5:21" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E36" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F36" s="92"/>
+      <c r="G36" s="162"/>
+      <c r="H36" s="163"/>
+      <c r="I36" s="42" t="s">
+        <v>51</v>
+      </c>
+      <c r="J36" s="52"/>
+      <c r="K36" s="62"/>
+      <c r="L36" s="63"/>
+      <c r="N36" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="O36" s="171"/>
+      <c r="P36" s="172"/>
+      <c r="Q36" s="173"/>
+      <c r="R36" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="S36" s="3"/>
+      <c r="T36" s="174"/>
+      <c r="U36" s="175"/>
+    </row>
+    <row r="37" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E37" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F37" s="59"/>
+      <c r="G37" s="164"/>
+      <c r="H37" s="165"/>
+      <c r="I37" s="166"/>
+      <c r="J37" s="66"/>
+      <c r="K37" s="64"/>
+      <c r="L37" s="65"/>
+      <c r="N37" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="O37" s="171"/>
+      <c r="P37" s="172"/>
+      <c r="Q37" s="173"/>
+      <c r="R37" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="S37" s="3"/>
+      <c r="T37" s="176"/>
+      <c r="U37" s="177"/>
+    </row>
+    <row r="38" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N38" s="155"/>
+      <c r="O38" s="60"/>
+      <c r="P38" s="60"/>
+      <c r="Q38" s="61"/>
+      <c r="R38" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="S38" s="11"/>
+      <c r="T38" s="178"/>
+      <c r="U38" s="179"/>
+    </row>
+  </sheetData>
+  <mergeCells count="78">
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="W16:Y16"/>
+    <mergeCell ref="AA16:AC16"/>
+    <mergeCell ref="E2:L4"/>
+    <mergeCell ref="E5:L5"/>
+    <mergeCell ref="E6:L6"/>
+    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="I7:L7"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="F12:H12"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="F13:H14"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E16:L16"/>
+    <mergeCell ref="N16:U16"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="T17:U17"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="K18:L23"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="T18:U20"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="N20:Q20"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="T24:U26"/>
+    <mergeCell ref="E25:L25"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="N22:U22"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="T23:U23"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="N26:Q26"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="K27:L28"/>
+    <mergeCell ref="E28:H28"/>
+    <mergeCell ref="N28:U28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="T29:U29"/>
+    <mergeCell ref="E30:L30"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="T30:U32"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="K31:L31"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="N32:Q32"/>
+    <mergeCell ref="E34:L34"/>
+    <mergeCell ref="N34:U34"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="K35:L35"/>
+    <mergeCell ref="O35:Q35"/>
+    <mergeCell ref="T35:U35"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="K36:L37"/>
+    <mergeCell ref="O36:Q36"/>
+    <mergeCell ref="T36:U38"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="O37:Q37"/>
+    <mergeCell ref="N38:Q38"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B218634-B09A-448D-BFDD-A2960099FCA7}">
   <dimension ref="E1:U38"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3857,96 +7393,96 @@
   <sheetData>
     <row r="1" spans="5:21" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="5:21" x14ac:dyDescent="0.3">
-      <c r="E2" s="138" t="s">
-        <v>118</v>
-      </c>
-      <c r="F2" s="139"/>
-      <c r="G2" s="139"/>
-      <c r="H2" s="139"/>
-      <c r="I2" s="139"/>
-      <c r="J2" s="139"/>
-      <c r="K2" s="139"/>
-      <c r="L2" s="140"/>
+      <c r="E2" s="118" t="s">
+        <v>203</v>
+      </c>
+      <c r="F2" s="119"/>
+      <c r="G2" s="119"/>
+      <c r="H2" s="119"/>
+      <c r="I2" s="119"/>
+      <c r="J2" s="119"/>
+      <c r="K2" s="119"/>
+      <c r="L2" s="120"/>
     </row>
     <row r="3" spans="5:21" x14ac:dyDescent="0.3">
-      <c r="E3" s="141"/>
-      <c r="F3" s="142"/>
-      <c r="G3" s="142"/>
-      <c r="H3" s="142"/>
-      <c r="I3" s="142"/>
-      <c r="J3" s="142"/>
-      <c r="K3" s="142"/>
-      <c r="L3" s="143"/>
+      <c r="E3" s="121"/>
+      <c r="F3" s="122"/>
+      <c r="G3" s="122"/>
+      <c r="H3" s="122"/>
+      <c r="I3" s="122"/>
+      <c r="J3" s="122"/>
+      <c r="K3" s="122"/>
+      <c r="L3" s="123"/>
     </row>
     <row r="4" spans="5:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E4" s="144"/>
-      <c r="F4" s="145"/>
-      <c r="G4" s="145"/>
-      <c r="H4" s="145"/>
-      <c r="I4" s="145"/>
-      <c r="J4" s="145"/>
-      <c r="K4" s="145"/>
-      <c r="L4" s="146"/>
+      <c r="E4" s="124"/>
+      <c r="F4" s="125"/>
+      <c r="G4" s="125"/>
+      <c r="H4" s="125"/>
+      <c r="I4" s="125"/>
+      <c r="J4" s="125"/>
+      <c r="K4" s="125"/>
+      <c r="L4" s="126"/>
     </row>
     <row r="5" spans="5:21" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E5" s="147" t="s">
+      <c r="E5" s="132" t="s">
         <v>1</v>
       </c>
-      <c r="F5" s="148"/>
-      <c r="G5" s="148"/>
-      <c r="H5" s="148"/>
-      <c r="I5" s="148"/>
-      <c r="J5" s="148"/>
-      <c r="K5" s="148"/>
-      <c r="L5" s="149"/>
+      <c r="F5" s="133"/>
+      <c r="G5" s="133"/>
+      <c r="H5" s="133"/>
+      <c r="I5" s="133"/>
+      <c r="J5" s="133"/>
+      <c r="K5" s="133"/>
+      <c r="L5" s="134"/>
       <c r="M5" s="23"/>
       <c r="N5" s="23"/>
       <c r="O5" s="23"/>
       <c r="P5" s="23"/>
     </row>
     <row r="6" spans="5:21" ht="69" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E6" s="101" t="s">
-        <v>119</v>
-      </c>
-      <c r="F6" s="102"/>
-      <c r="G6" s="102"/>
-      <c r="H6" s="102"/>
-      <c r="I6" s="102"/>
-      <c r="J6" s="102"/>
-      <c r="K6" s="102"/>
-      <c r="L6" s="103"/>
+      <c r="E6" s="135" t="s">
+        <v>205</v>
+      </c>
+      <c r="F6" s="136"/>
+      <c r="G6" s="136"/>
+      <c r="H6" s="136"/>
+      <c r="I6" s="136"/>
+      <c r="J6" s="136"/>
+      <c r="K6" s="136"/>
+      <c r="L6" s="137"/>
       <c r="M6" s="24"/>
       <c r="N6" s="24"/>
       <c r="O6" s="24"/>
       <c r="P6" s="24"/>
     </row>
     <row r="7" spans="5:21" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E7" s="104" t="s">
+      <c r="E7" s="138" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="105"/>
-      <c r="G7" s="105"/>
-      <c r="H7" s="105"/>
-      <c r="I7" s="105" t="s">
+      <c r="F7" s="139"/>
+      <c r="G7" s="139"/>
+      <c r="H7" s="139"/>
+      <c r="I7" s="139" t="s">
         <v>3</v>
       </c>
-      <c r="J7" s="105"/>
-      <c r="K7" s="105"/>
-      <c r="L7" s="106"/>
+      <c r="J7" s="139"/>
+      <c r="K7" s="139"/>
+      <c r="L7" s="140"/>
       <c r="M7" s="25"/>
       <c r="N7" s="25"/>
       <c r="O7" s="25"/>
       <c r="P7" s="25"/>
     </row>
     <row r="8" spans="5:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E8" s="29" t="s">
-        <v>4</v>
-      </c>
-      <c r="F8" s="124" t="s">
-        <v>120</v>
-      </c>
-      <c r="G8" s="125"/>
-      <c r="H8" s="113"/>
+      <c r="E8" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="F8" s="183">
+        <v>1502023</v>
+      </c>
+      <c r="G8" s="183"/>
+      <c r="H8" s="183"/>
       <c r="I8" s="26" t="s">
         <v>62</v>
       </c>
@@ -3961,15 +7497,15 @@
       </c>
     </row>
     <row r="9" spans="5:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E9" s="30" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" s="126" t="s">
-        <v>121</v>
-      </c>
-      <c r="G9" s="127"/>
-      <c r="H9" s="128"/>
-      <c r="I9" s="126" t="s">
+      <c r="E9" s="233" t="s">
+        <v>207</v>
+      </c>
+      <c r="F9" s="231" t="s">
+        <v>208</v>
+      </c>
+      <c r="G9" s="232"/>
+      <c r="H9" s="232"/>
+      <c r="I9" s="127" t="s">
         <v>54</v>
       </c>
       <c r="J9" s="32" t="s">
@@ -3981,15 +7517,11 @@
       <c r="L9" s="33"/>
     </row>
     <row r="10" spans="5:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E10" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="126" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10" s="127"/>
-      <c r="H10" s="128"/>
-      <c r="I10" s="129"/>
+      <c r="E10" s="233"/>
+      <c r="F10" s="232"/>
+      <c r="G10" s="232"/>
+      <c r="H10" s="232"/>
+      <c r="I10" s="130"/>
       <c r="J10" s="32" t="s">
         <v>58</v>
       </c>
@@ -4002,12 +7534,12 @@
       <c r="E11" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="F11" s="126" t="s">
+      <c r="F11" s="127" t="s">
         <v>10</v>
       </c>
-      <c r="G11" s="127"/>
-      <c r="H11" s="127"/>
-      <c r="I11" s="126" t="s">
+      <c r="G11" s="128"/>
+      <c r="H11" s="128"/>
+      <c r="I11" s="127" t="s">
         <v>55</v>
       </c>
       <c r="J11" s="32" t="s">
@@ -4020,14 +7552,14 @@
     </row>
     <row r="12" spans="5:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E12" s="30" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" s="129" t="s">
-        <v>122</v>
-      </c>
-      <c r="G12" s="132"/>
-      <c r="H12" s="132"/>
-      <c r="I12" s="129"/>
+        <v>8</v>
+      </c>
+      <c r="F12" s="127" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12" s="128"/>
+      <c r="H12" s="129"/>
+      <c r="I12" s="130"/>
       <c r="J12" s="32" t="s">
         <v>60</v>
       </c>
@@ -4037,622 +7569,609 @@
       <c r="L12" s="28"/>
     </row>
     <row r="13" spans="5:21" x14ac:dyDescent="0.3">
-      <c r="E13" s="87" t="s">
+      <c r="E13" s="93" t="s">
         <v>12</v>
       </c>
-      <c r="F13" s="107">
-        <v>798771.82</v>
-      </c>
-      <c r="G13" s="108"/>
-      <c r="H13" s="109"/>
-      <c r="I13" s="130" t="s">
+      <c r="F13" s="95">
+        <v>653853.88</v>
+      </c>
+      <c r="G13" s="96"/>
+      <c r="H13" s="97"/>
+      <c r="I13" s="143" t="s">
         <v>56</v>
       </c>
-      <c r="J13" s="130" t="s">
+      <c r="J13" s="143" t="s">
         <v>61</v>
       </c>
-      <c r="K13" s="174" t="s">
+      <c r="K13" s="167" t="s">
         <v>92</v>
       </c>
-      <c r="L13" s="172" t="s">
-        <v>135</v>
+      <c r="L13" s="169" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="14" spans="5:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E14" s="88"/>
-      <c r="F14" s="110"/>
-      <c r="G14" s="111"/>
-      <c r="H14" s="112"/>
-      <c r="I14" s="131"/>
-      <c r="J14" s="131"/>
-      <c r="K14" s="175"/>
-      <c r="L14" s="173"/>
+      <c r="E14" s="94"/>
+      <c r="F14" s="98"/>
+      <c r="G14" s="99"/>
+      <c r="H14" s="100"/>
+      <c r="I14" s="144"/>
+      <c r="J14" s="144"/>
+      <c r="K14" s="168"/>
+      <c r="L14" s="170"/>
     </row>
     <row r="15" spans="5:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E15" s="150"/>
-      <c r="F15" s="150"/>
+      <c r="E15" s="116"/>
+      <c r="F15" s="116"/>
     </row>
     <row r="16" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E16" s="60" t="s">
+      <c r="E16" s="83" t="s">
         <v>15</v>
       </c>
-      <c r="F16" s="61"/>
-      <c r="G16" s="61"/>
-      <c r="H16" s="61"/>
-      <c r="I16" s="61"/>
-      <c r="J16" s="61"/>
-      <c r="K16" s="61"/>
-      <c r="L16" s="62"/>
-      <c r="N16" s="60" t="s">
+      <c r="F16" s="84"/>
+      <c r="G16" s="84"/>
+      <c r="H16" s="84"/>
+      <c r="I16" s="84"/>
+      <c r="J16" s="84"/>
+      <c r="K16" s="84"/>
+      <c r="L16" s="85"/>
+      <c r="N16" s="83" t="s">
         <v>95</v>
       </c>
-      <c r="O16" s="61"/>
-      <c r="P16" s="61"/>
-      <c r="Q16" s="61"/>
-      <c r="R16" s="61"/>
-      <c r="S16" s="61"/>
-      <c r="T16" s="61"/>
-      <c r="U16" s="62"/>
+      <c r="O16" s="84"/>
+      <c r="P16" s="84"/>
+      <c r="Q16" s="84"/>
+      <c r="R16" s="84"/>
+      <c r="S16" s="84"/>
+      <c r="T16" s="84"/>
+      <c r="U16" s="85"/>
     </row>
     <row r="17" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E17" s="9"/>
-      <c r="F17" s="75" t="s">
+      <c r="F17" s="113" t="s">
         <v>2</v>
       </c>
-      <c r="G17" s="76"/>
-      <c r="H17" s="77"/>
+      <c r="G17" s="114"/>
+      <c r="H17" s="115"/>
       <c r="I17" s="14"/>
       <c r="J17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="K17" s="63" t="s">
+      <c r="K17" s="72" t="s">
         <v>25</v>
       </c>
-      <c r="L17" s="65"/>
+      <c r="L17" s="74"/>
       <c r="N17" s="9"/>
-      <c r="O17" s="75" t="s">
+      <c r="O17" s="113" t="s">
         <v>2</v>
       </c>
-      <c r="P17" s="76"/>
-      <c r="Q17" s="77"/>
+      <c r="P17" s="114"/>
+      <c r="Q17" s="115"/>
       <c r="R17" s="8"/>
       <c r="S17" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="T17" s="75" t="s">
+      <c r="T17" s="113" t="s">
         <v>25</v>
       </c>
-      <c r="U17" s="77"/>
+      <c r="U17" s="115"/>
     </row>
     <row r="18" spans="5:21" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E18" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="F18" s="162" t="s">
-        <v>124</v>
-      </c>
-      <c r="G18" s="163"/>
-      <c r="H18" s="164"/>
+      <c r="F18" s="86" t="s">
+        <v>211</v>
+      </c>
+      <c r="G18" s="87"/>
+      <c r="H18" s="88"/>
       <c r="I18" s="36" t="s">
         <v>30</v>
       </c>
       <c r="J18" s="39" t="s">
-        <v>126</v>
-      </c>
-      <c r="K18" s="152" t="s">
-        <v>125</v>
-      </c>
-      <c r="L18" s="153"/>
+        <v>213</v>
+      </c>
+      <c r="K18" s="107" t="s">
+        <v>216</v>
+      </c>
+      <c r="L18" s="108"/>
       <c r="N18" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="O18" s="133" t="s">
-        <v>113</v>
-      </c>
-      <c r="P18" s="134"/>
-      <c r="Q18" s="135"/>
+      <c r="O18" s="89"/>
+      <c r="P18" s="90"/>
+      <c r="Q18" s="91"/>
       <c r="R18" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="S18" s="45" t="s">
-        <v>146</v>
-      </c>
-      <c r="T18" s="192" t="s">
-        <v>134</v>
-      </c>
-      <c r="U18" s="193"/>
+      <c r="S18" s="52"/>
+      <c r="T18" s="148" t="s">
+        <v>221</v>
+      </c>
+      <c r="U18" s="149"/>
     </row>
     <row r="19" spans="5:21" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E19" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="F19" s="133" t="s">
-        <v>120</v>
-      </c>
-      <c r="G19" s="134"/>
-      <c r="H19" s="135"/>
+      <c r="F19" s="89" t="s">
+        <v>209</v>
+      </c>
+      <c r="G19" s="90"/>
+      <c r="H19" s="91"/>
       <c r="I19" s="37" t="s">
         <v>52</v>
       </c>
       <c r="J19" s="40" t="s">
-        <v>127</v>
-      </c>
-      <c r="K19" s="154"/>
-      <c r="L19" s="155"/>
+        <v>215</v>
+      </c>
+      <c r="K19" s="109"/>
+      <c r="L19" s="110"/>
       <c r="N19" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="O19" s="189">
-        <v>240444.78</v>
-      </c>
-      <c r="P19" s="190"/>
-      <c r="Q19" s="191"/>
+      <c r="O19" s="152">
+        <v>129054.44</v>
+      </c>
+      <c r="P19" s="153"/>
+      <c r="Q19" s="154"/>
       <c r="R19" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="S19" s="45" t="s">
-        <v>136</v>
-      </c>
-      <c r="T19" s="194"/>
-      <c r="U19" s="195"/>
+      <c r="S19" s="52"/>
+      <c r="T19" s="150"/>
+      <c r="U19" s="151"/>
     </row>
     <row r="20" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E20" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="F20" s="133" t="s">
-        <v>121</v>
-      </c>
-      <c r="G20" s="134"/>
-      <c r="H20" s="135"/>
+      <c r="F20" s="228" t="s">
+        <v>204</v>
+      </c>
+      <c r="G20" s="229"/>
+      <c r="H20" s="230"/>
       <c r="I20" s="37" t="s">
         <v>32</v>
       </c>
       <c r="J20" s="40" t="s">
-        <v>128</v>
-      </c>
-      <c r="K20" s="154"/>
-      <c r="L20" s="155"/>
-      <c r="N20" s="66"/>
-      <c r="O20" s="67"/>
-      <c r="P20" s="67"/>
-      <c r="Q20" s="68"/>
+        <v>214</v>
+      </c>
+      <c r="K20" s="109"/>
+      <c r="L20" s="110"/>
+      <c r="N20" s="155"/>
+      <c r="O20" s="60"/>
+      <c r="P20" s="60"/>
+      <c r="Q20" s="61"/>
       <c r="R20" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="S20" s="44" t="s">
+      <c r="S20" s="53" t="s">
         <v>70</v>
       </c>
-      <c r="T20" s="168"/>
-      <c r="U20" s="169"/>
+      <c r="T20" s="64"/>
+      <c r="U20" s="65"/>
     </row>
     <row r="21" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E21" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="F21" s="133" t="s">
-        <v>122</v>
-      </c>
-      <c r="G21" s="134"/>
-      <c r="H21" s="135"/>
+      <c r="F21" s="89" t="s">
+        <v>210</v>
+      </c>
+      <c r="G21" s="90"/>
+      <c r="H21" s="91"/>
       <c r="I21" s="37" t="s">
         <v>33</v>
       </c>
       <c r="J21" s="40" t="s">
         <v>70</v>
       </c>
-      <c r="K21" s="154"/>
-      <c r="L21" s="155"/>
+      <c r="K21" s="109"/>
+      <c r="L21" s="110"/>
     </row>
     <row r="22" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E22" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="F22" s="136">
-        <v>46132</v>
-      </c>
-      <c r="G22" s="134"/>
-      <c r="H22" s="135"/>
+      <c r="F22" s="92">
+        <v>45936</v>
+      </c>
+      <c r="G22" s="90"/>
+      <c r="H22" s="91"/>
       <c r="I22" s="37" t="s">
         <v>34</v>
       </c>
       <c r="J22" s="40" t="s">
-        <v>129</v>
-      </c>
-      <c r="K22" s="154"/>
-      <c r="L22" s="155"/>
-      <c r="N22" s="60" t="s">
+        <v>212</v>
+      </c>
+      <c r="K22" s="109"/>
+      <c r="L22" s="110"/>
+      <c r="N22" s="83" t="s">
         <v>96</v>
       </c>
-      <c r="O22" s="61"/>
-      <c r="P22" s="61"/>
-      <c r="Q22" s="61"/>
-      <c r="R22" s="61"/>
-      <c r="S22" s="61"/>
-      <c r="T22" s="61"/>
-      <c r="U22" s="62"/>
+      <c r="O22" s="84"/>
+      <c r="P22" s="84"/>
+      <c r="Q22" s="84"/>
+      <c r="R22" s="84"/>
+      <c r="S22" s="84"/>
+      <c r="T22" s="84"/>
+      <c r="U22" s="85"/>
     </row>
     <row r="23" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E23" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="F23" s="137">
-        <v>46315</v>
-      </c>
-      <c r="G23" s="67"/>
-      <c r="H23" s="68"/>
-      <c r="I23" s="151"/>
-      <c r="J23" s="55"/>
-      <c r="K23" s="156"/>
-      <c r="L23" s="157"/>
+      <c r="F23" s="59">
+        <v>46118</v>
+      </c>
+      <c r="G23" s="60"/>
+      <c r="H23" s="61"/>
+      <c r="I23" s="147"/>
+      <c r="J23" s="67"/>
+      <c r="K23" s="111"/>
+      <c r="L23" s="112"/>
       <c r="N23" s="9"/>
-      <c r="O23" s="75" t="s">
+      <c r="O23" s="113" t="s">
         <v>2</v>
       </c>
-      <c r="P23" s="76"/>
-      <c r="Q23" s="77"/>
+      <c r="P23" s="114"/>
+      <c r="Q23" s="115"/>
       <c r="R23" s="8"/>
       <c r="S23" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="T23" s="75" t="s">
+      <c r="T23" s="113" t="s">
         <v>25</v>
       </c>
-      <c r="U23" s="77"/>
+      <c r="U23" s="115"/>
     </row>
     <row r="24" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="N24" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="O24" s="70"/>
-      <c r="P24" s="71"/>
-      <c r="Q24" s="72"/>
+      <c r="O24" s="171"/>
+      <c r="P24" s="172"/>
+      <c r="Q24" s="173"/>
       <c r="R24" s="6" t="s">
         <v>45</v>
       </c>
       <c r="S24" s="3"/>
-      <c r="T24" s="183"/>
-      <c r="U24" s="184"/>
+      <c r="T24" s="148" t="s">
+        <v>222</v>
+      </c>
+      <c r="U24" s="149"/>
     </row>
     <row r="25" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E25" s="60" t="s">
+      <c r="E25" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="F25" s="61"/>
-      <c r="G25" s="61"/>
-      <c r="H25" s="61"/>
-      <c r="I25" s="61"/>
-      <c r="J25" s="61"/>
-      <c r="K25" s="61"/>
-      <c r="L25" s="62"/>
+      <c r="F25" s="84"/>
+      <c r="G25" s="84"/>
+      <c r="H25" s="84"/>
+      <c r="I25" s="84"/>
+      <c r="J25" s="84"/>
+      <c r="K25" s="84"/>
+      <c r="L25" s="85"/>
       <c r="N25" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="O25" s="70"/>
-      <c r="P25" s="71"/>
-      <c r="Q25" s="72"/>
+      <c r="O25" s="152">
+        <v>139771.16</v>
+      </c>
+      <c r="P25" s="153"/>
+      <c r="Q25" s="154"/>
       <c r="R25" s="6" t="s">
         <v>46</v>
       </c>
       <c r="S25" s="3"/>
-      <c r="T25" s="185"/>
-      <c r="U25" s="186"/>
+      <c r="T25" s="150"/>
+      <c r="U25" s="151"/>
     </row>
     <row r="26" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E26" s="12"/>
-      <c r="F26" s="63" t="s">
+      <c r="F26" s="72" t="s">
         <v>2</v>
       </c>
-      <c r="G26" s="64"/>
-      <c r="H26" s="65"/>
+      <c r="G26" s="73"/>
+      <c r="H26" s="74"/>
       <c r="I26" s="14"/>
       <c r="J26" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="K26" s="63" t="s">
+      <c r="K26" s="72" t="s">
         <v>25</v>
       </c>
-      <c r="L26" s="65"/>
-      <c r="N26" s="66"/>
-      <c r="O26" s="67"/>
-      <c r="P26" s="67"/>
-      <c r="Q26" s="68"/>
+      <c r="L26" s="74"/>
+      <c r="N26" s="155"/>
+      <c r="O26" s="60"/>
+      <c r="P26" s="60"/>
+      <c r="Q26" s="61"/>
       <c r="R26" s="7" t="s">
         <v>47</v>
       </c>
       <c r="S26" s="11"/>
-      <c r="T26" s="187"/>
-      <c r="U26" s="188"/>
-    </row>
-    <row r="27" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="T26" s="64"/>
+      <c r="U26" s="65"/>
+    </row>
+    <row r="27" spans="5:21" ht="34.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E27" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="F27" s="160" t="s">
-        <v>130</v>
-      </c>
-      <c r="G27" s="160"/>
-      <c r="H27" s="161"/>
+      <c r="F27" s="57" t="s">
+        <v>217</v>
+      </c>
+      <c r="G27" s="57"/>
+      <c r="H27" s="58"/>
       <c r="I27" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="J27" s="35" t="s">
-        <v>132</v>
-      </c>
-      <c r="K27" s="166" t="s">
-        <v>131</v>
-      </c>
-      <c r="L27" s="167"/>
-    </row>
-    <row r="28" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E28" s="57"/>
-      <c r="F28" s="58"/>
-      <c r="G28" s="58"/>
-      <c r="H28" s="59"/>
+      <c r="J27" s="52" t="s">
+        <v>218</v>
+      </c>
+      <c r="K27" s="62" t="s">
+        <v>220</v>
+      </c>
+      <c r="L27" s="63"/>
+    </row>
+    <row r="28" spans="5:21" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E28" s="80"/>
+      <c r="F28" s="81"/>
+      <c r="G28" s="81"/>
+      <c r="H28" s="82"/>
       <c r="I28" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="J28" s="17" t="s">
-        <v>133</v>
-      </c>
-      <c r="K28" s="168"/>
-      <c r="L28" s="169"/>
-      <c r="N28" s="60" t="s">
+      <c r="J28" s="53" t="s">
+        <v>219</v>
+      </c>
+      <c r="K28" s="64"/>
+      <c r="L28" s="65"/>
+      <c r="N28" s="83" t="s">
         <v>98</v>
       </c>
-      <c r="O28" s="61"/>
-      <c r="P28" s="61"/>
-      <c r="Q28" s="61"/>
-      <c r="R28" s="61"/>
-      <c r="S28" s="61"/>
-      <c r="T28" s="61"/>
-      <c r="U28" s="62"/>
+      <c r="O28" s="84"/>
+      <c r="P28" s="84"/>
+      <c r="Q28" s="84"/>
+      <c r="R28" s="84"/>
+      <c r="S28" s="84"/>
+      <c r="T28" s="84"/>
+      <c r="U28" s="85"/>
     </row>
     <row r="29" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="N29" s="9"/>
-      <c r="O29" s="75" t="s">
+      <c r="O29" s="113" t="s">
         <v>2</v>
       </c>
-      <c r="P29" s="76"/>
-      <c r="Q29" s="77"/>
+      <c r="P29" s="114"/>
+      <c r="Q29" s="115"/>
       <c r="R29" s="8"/>
       <c r="S29" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="T29" s="75" t="s">
+      <c r="T29" s="113" t="s">
         <v>25</v>
       </c>
-      <c r="U29" s="77"/>
+      <c r="U29" s="115"/>
     </row>
     <row r="30" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E30" s="60" t="s">
+      <c r="E30" s="83" t="s">
         <v>28</v>
       </c>
-      <c r="F30" s="61"/>
-      <c r="G30" s="61"/>
-      <c r="H30" s="61"/>
-      <c r="I30" s="61"/>
-      <c r="J30" s="61"/>
-      <c r="K30" s="61"/>
-      <c r="L30" s="62"/>
+      <c r="F30" s="84"/>
+      <c r="G30" s="84"/>
+      <c r="H30" s="84"/>
+      <c r="I30" s="84"/>
+      <c r="J30" s="84"/>
+      <c r="K30" s="84"/>
+      <c r="L30" s="85"/>
       <c r="N30" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="O30" s="70"/>
-      <c r="P30" s="71"/>
-      <c r="Q30" s="72"/>
+      <c r="O30" s="171"/>
+      <c r="P30" s="172"/>
+      <c r="Q30" s="173"/>
       <c r="R30" s="6" t="s">
         <v>45</v>
       </c>
       <c r="S30" s="3"/>
-      <c r="T30" s="183"/>
-      <c r="U30" s="184"/>
+      <c r="T30" s="174"/>
+      <c r="U30" s="175"/>
     </row>
     <row r="31" spans="5:21" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E31" s="12"/>
-      <c r="F31" s="63" t="s">
+      <c r="F31" s="72" t="s">
         <v>2</v>
       </c>
-      <c r="G31" s="64"/>
-      <c r="H31" s="65"/>
+      <c r="G31" s="73"/>
+      <c r="H31" s="74"/>
       <c r="I31" s="14"/>
       <c r="J31" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="K31" s="63" t="s">
+      <c r="K31" s="72" t="s">
         <v>25</v>
       </c>
-      <c r="L31" s="65"/>
+      <c r="L31" s="74"/>
       <c r="N31" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="O31" s="70"/>
-      <c r="P31" s="71"/>
-      <c r="Q31" s="72"/>
+      <c r="O31" s="171"/>
+      <c r="P31" s="172"/>
+      <c r="Q31" s="173"/>
       <c r="R31" s="6" t="s">
         <v>46</v>
       </c>
       <c r="S31" s="3"/>
-      <c r="T31" s="185"/>
-      <c r="U31" s="186"/>
+      <c r="T31" s="176"/>
+      <c r="U31" s="177"/>
     </row>
     <row r="32" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E32" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F32" s="48"/>
-      <c r="G32" s="48"/>
-      <c r="H32" s="49"/>
+      <c r="F32" s="75"/>
+      <c r="G32" s="75"/>
+      <c r="H32" s="76"/>
       <c r="I32" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="J32" s="17"/>
-      <c r="K32" s="158"/>
-      <c r="L32" s="159"/>
-      <c r="N32" s="66"/>
-      <c r="O32" s="67"/>
-      <c r="P32" s="67"/>
-      <c r="Q32" s="68"/>
+      <c r="J32" s="53"/>
+      <c r="K32" s="70"/>
+      <c r="L32" s="71"/>
+      <c r="N32" s="155"/>
+      <c r="O32" s="60"/>
+      <c r="P32" s="60"/>
+      <c r="Q32" s="61"/>
       <c r="R32" s="7" t="s">
         <v>47</v>
       </c>
       <c r="S32" s="11"/>
-      <c r="T32" s="187"/>
-      <c r="U32" s="188"/>
+      <c r="T32" s="178"/>
+      <c r="U32" s="179"/>
     </row>
     <row r="33" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="34" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E34" s="60" t="s">
+      <c r="E34" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="F34" s="61"/>
-      <c r="G34" s="61"/>
-      <c r="H34" s="61"/>
-      <c r="I34" s="61"/>
-      <c r="J34" s="61"/>
-      <c r="K34" s="61"/>
-      <c r="L34" s="62"/>
-      <c r="N34" s="60" t="s">
+      <c r="F34" s="84"/>
+      <c r="G34" s="84"/>
+      <c r="H34" s="84"/>
+      <c r="I34" s="84"/>
+      <c r="J34" s="84"/>
+      <c r="K34" s="84"/>
+      <c r="L34" s="85"/>
+      <c r="N34" s="83" t="s">
         <v>97</v>
       </c>
-      <c r="O34" s="61"/>
-      <c r="P34" s="61"/>
-      <c r="Q34" s="61"/>
-      <c r="R34" s="61"/>
-      <c r="S34" s="61"/>
-      <c r="T34" s="61"/>
-      <c r="U34" s="62"/>
+      <c r="O34" s="84"/>
+      <c r="P34" s="84"/>
+      <c r="Q34" s="84"/>
+      <c r="R34" s="84"/>
+      <c r="S34" s="84"/>
+      <c r="T34" s="84"/>
+      <c r="U34" s="85"/>
     </row>
     <row r="35" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E35" s="12"/>
-      <c r="F35" s="176" t="s">
+      <c r="F35" s="159" t="s">
         <v>2</v>
       </c>
-      <c r="G35" s="177"/>
-      <c r="H35" s="178"/>
+      <c r="G35" s="160"/>
+      <c r="H35" s="161"/>
       <c r="I35" s="41"/>
       <c r="J35" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="K35" s="176" t="s">
+      <c r="K35" s="159" t="s">
         <v>25</v>
       </c>
-      <c r="L35" s="178"/>
+      <c r="L35" s="161"/>
       <c r="N35" s="9"/>
-      <c r="O35" s="75" t="s">
+      <c r="O35" s="113" t="s">
         <v>2</v>
       </c>
-      <c r="P35" s="76"/>
-      <c r="Q35" s="77"/>
+      <c r="P35" s="114"/>
+      <c r="Q35" s="115"/>
       <c r="R35" s="8"/>
       <c r="S35" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="T35" s="75" t="s">
+      <c r="T35" s="113" t="s">
         <v>25</v>
       </c>
-      <c r="U35" s="77"/>
+      <c r="U35" s="115"/>
     </row>
     <row r="36" spans="5:21" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E36" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="F36" s="136"/>
-      <c r="G36" s="179"/>
-      <c r="H36" s="180"/>
+      <c r="F36" s="92"/>
+      <c r="G36" s="162"/>
+      <c r="H36" s="163"/>
       <c r="I36" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="J36" s="35"/>
-      <c r="K36" s="166"/>
-      <c r="L36" s="167"/>
+      <c r="J36" s="52"/>
+      <c r="K36" s="62"/>
+      <c r="L36" s="63"/>
       <c r="N36" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="O36" s="70"/>
-      <c r="P36" s="71"/>
-      <c r="Q36" s="72"/>
+      <c r="O36" s="171"/>
+      <c r="P36" s="172"/>
+      <c r="Q36" s="173"/>
       <c r="R36" s="6" t="s">
         <v>45</v>
       </c>
       <c r="S36" s="3"/>
-      <c r="T36" s="183"/>
-      <c r="U36" s="184"/>
+      <c r="T36" s="174"/>
+      <c r="U36" s="175"/>
     </row>
     <row r="37" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E37" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="F37" s="137"/>
-      <c r="G37" s="181"/>
-      <c r="H37" s="182"/>
-      <c r="I37" s="50"/>
-      <c r="J37" s="54"/>
-      <c r="K37" s="168"/>
-      <c r="L37" s="169"/>
+      <c r="F37" s="59"/>
+      <c r="G37" s="164"/>
+      <c r="H37" s="165"/>
+      <c r="I37" s="166"/>
+      <c r="J37" s="66"/>
+      <c r="K37" s="64"/>
+      <c r="L37" s="65"/>
       <c r="N37" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="O37" s="70"/>
-      <c r="P37" s="71"/>
-      <c r="Q37" s="72"/>
+      <c r="O37" s="171"/>
+      <c r="P37" s="172"/>
+      <c r="Q37" s="173"/>
       <c r="R37" s="6" t="s">
         <v>46</v>
       </c>
       <c r="S37" s="3"/>
-      <c r="T37" s="185"/>
-      <c r="U37" s="186"/>
+      <c r="T37" s="176"/>
+      <c r="U37" s="177"/>
     </row>
     <row r="38" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="N38" s="66"/>
-      <c r="O38" s="67"/>
-      <c r="P38" s="67"/>
-      <c r="Q38" s="68"/>
+      <c r="N38" s="155"/>
+      <c r="O38" s="60"/>
+      <c r="P38" s="60"/>
+      <c r="Q38" s="61"/>
       <c r="R38" s="7" t="s">
         <v>47</v>
       </c>
       <c r="S38" s="11"/>
-      <c r="T38" s="187"/>
-      <c r="U38" s="188"/>
+      <c r="T38" s="178"/>
+      <c r="U38" s="179"/>
     </row>
   </sheetData>
   <mergeCells count="76">
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="K36:L37"/>
-    <mergeCell ref="O36:Q36"/>
-    <mergeCell ref="T36:U38"/>
-    <mergeCell ref="F37:H37"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="O37:Q37"/>
-    <mergeCell ref="N38:Q38"/>
-    <mergeCell ref="E34:L34"/>
-    <mergeCell ref="N34:U34"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="K35:L35"/>
-    <mergeCell ref="O35:Q35"/>
-    <mergeCell ref="T35:U35"/>
-    <mergeCell ref="E30:L30"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="T30:U32"/>
-    <mergeCell ref="F31:H31"/>
-    <mergeCell ref="K31:L31"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="N32:Q32"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="K27:L28"/>
-    <mergeCell ref="E28:H28"/>
-    <mergeCell ref="N28:U28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="T29:U29"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="T24:U26"/>
-    <mergeCell ref="E25:L25"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="K26:L26"/>
-    <mergeCell ref="N26:Q26"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="F9:H10"/>
+    <mergeCell ref="E2:L4"/>
+    <mergeCell ref="E5:L5"/>
+    <mergeCell ref="E6:L6"/>
+    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="I7:L7"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="F12:H12"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="F13:H14"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E16:L16"/>
+    <mergeCell ref="N16:U16"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="T17:U17"/>
     <mergeCell ref="F18:H18"/>
     <mergeCell ref="K18:L23"/>
     <mergeCell ref="O18:Q18"/>
@@ -4663,825 +8182,24 @@
     <mergeCell ref="N20:Q20"/>
     <mergeCell ref="F21:H21"/>
     <mergeCell ref="F22:H22"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="T24:U26"/>
+    <mergeCell ref="E25:L25"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="F26:H26"/>
     <mergeCell ref="N22:U22"/>
     <mergeCell ref="F23:H23"/>
     <mergeCell ref="I23:J23"/>
     <mergeCell ref="O23:Q23"/>
     <mergeCell ref="T23:U23"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="E16:L16"/>
-    <mergeCell ref="N16:U16"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="T17:U17"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="F13:H14"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="K13:K14"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="F12:H12"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="E2:L4"/>
-    <mergeCell ref="E5:L5"/>
-    <mergeCell ref="E6:L6"/>
-    <mergeCell ref="E7:H7"/>
-    <mergeCell ref="I7:L7"/>
-  </mergeCells>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4561D198-C9B7-4DE2-8DF4-A0018AE8DF2D}">
-  <dimension ref="E1:U38"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="5" max="5" width="25.77734375" customWidth="1"/>
-    <col min="6" max="6" width="20.77734375" customWidth="1"/>
-    <col min="7" max="8" width="10.77734375" customWidth="1"/>
-    <col min="9" max="9" width="30.77734375" customWidth="1"/>
-    <col min="10" max="10" width="45.77734375" customWidth="1"/>
-    <col min="11" max="12" width="25.77734375" customWidth="1"/>
-    <col min="14" max="14" width="25.77734375" customWidth="1"/>
-    <col min="15" max="15" width="20.77734375" customWidth="1"/>
-    <col min="16" max="17" width="10.77734375" customWidth="1"/>
-    <col min="18" max="18" width="30.77734375" customWidth="1"/>
-    <col min="19" max="19" width="45.77734375" customWidth="1"/>
-    <col min="20" max="21" width="25.77734375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="5:21" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="5:21" x14ac:dyDescent="0.3">
-      <c r="E2" s="138" t="s">
-        <v>137</v>
-      </c>
-      <c r="F2" s="139"/>
-      <c r="G2" s="139"/>
-      <c r="H2" s="139"/>
-      <c r="I2" s="139"/>
-      <c r="J2" s="139"/>
-      <c r="K2" s="139"/>
-      <c r="L2" s="140"/>
-    </row>
-    <row r="3" spans="5:21" x14ac:dyDescent="0.3">
-      <c r="E3" s="141"/>
-      <c r="F3" s="142"/>
-      <c r="G3" s="142"/>
-      <c r="H3" s="142"/>
-      <c r="I3" s="142"/>
-      <c r="J3" s="142"/>
-      <c r="K3" s="142"/>
-      <c r="L3" s="143"/>
-    </row>
-    <row r="4" spans="5:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E4" s="144"/>
-      <c r="F4" s="145"/>
-      <c r="G4" s="145"/>
-      <c r="H4" s="145"/>
-      <c r="I4" s="145"/>
-      <c r="J4" s="145"/>
-      <c r="K4" s="145"/>
-      <c r="L4" s="146"/>
-    </row>
-    <row r="5" spans="5:21" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E5" s="147" t="s">
-        <v>1</v>
-      </c>
-      <c r="F5" s="148"/>
-      <c r="G5" s="148"/>
-      <c r="H5" s="148"/>
-      <c r="I5" s="148"/>
-      <c r="J5" s="148"/>
-      <c r="K5" s="148"/>
-      <c r="L5" s="149"/>
-      <c r="M5" s="23"/>
-      <c r="N5" s="23"/>
-      <c r="O5" s="23"/>
-      <c r="P5" s="23"/>
-    </row>
-    <row r="6" spans="5:21" ht="69" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E6" s="101" t="s">
-        <v>138</v>
-      </c>
-      <c r="F6" s="102"/>
-      <c r="G6" s="102"/>
-      <c r="H6" s="102"/>
-      <c r="I6" s="102"/>
-      <c r="J6" s="102"/>
-      <c r="K6" s="102"/>
-      <c r="L6" s="103"/>
-      <c r="M6" s="24"/>
-      <c r="N6" s="24"/>
-      <c r="O6" s="24"/>
-      <c r="P6" s="24"/>
-    </row>
-    <row r="7" spans="5:21" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E7" s="104" t="s">
-        <v>2</v>
-      </c>
-      <c r="F7" s="105"/>
-      <c r="G7" s="105"/>
-      <c r="H7" s="105"/>
-      <c r="I7" s="105" t="s">
-        <v>3</v>
-      </c>
-      <c r="J7" s="105"/>
-      <c r="K7" s="105"/>
-      <c r="L7" s="106"/>
-      <c r="M7" s="25"/>
-      <c r="N7" s="25"/>
-      <c r="O7" s="25"/>
-      <c r="P7" s="25"/>
-    </row>
-    <row r="8" spans="5:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E8" s="29" t="s">
-        <v>4</v>
-      </c>
-      <c r="F8" s="124" t="s">
-        <v>139</v>
-      </c>
-      <c r="G8" s="125"/>
-      <c r="H8" s="113"/>
-      <c r="I8" s="26" t="s">
-        <v>62</v>
-      </c>
-      <c r="J8" s="31" t="s">
-        <v>63</v>
-      </c>
-      <c r="K8" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="L8" s="27" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="9" spans="5:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E9" s="30" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" s="126" t="s">
-        <v>121</v>
-      </c>
-      <c r="G9" s="127"/>
-      <c r="H9" s="128"/>
-      <c r="I9" s="126" t="s">
-        <v>54</v>
-      </c>
-      <c r="J9" s="32" t="s">
-        <v>57</v>
-      </c>
-      <c r="K9" s="34" t="s">
-        <v>66</v>
-      </c>
-      <c r="L9" s="33"/>
-    </row>
-    <row r="10" spans="5:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E10" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="126" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10" s="127"/>
-      <c r="H10" s="128"/>
-      <c r="I10" s="129"/>
-      <c r="J10" s="32" t="s">
-        <v>58</v>
-      </c>
-      <c r="K10" s="43" t="s">
-        <v>94</v>
-      </c>
-      <c r="L10" s="28"/>
-    </row>
-    <row r="11" spans="5:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E11" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" s="126" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" s="127"/>
-      <c r="H11" s="127"/>
-      <c r="I11" s="126" t="s">
-        <v>55</v>
-      </c>
-      <c r="J11" s="32" t="s">
-        <v>59</v>
-      </c>
-      <c r="K11" s="34" t="s">
-        <v>66</v>
-      </c>
-      <c r="L11" s="28"/>
-    </row>
-    <row r="12" spans="5:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E12" s="30" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" s="129" t="s">
-        <v>140</v>
-      </c>
-      <c r="G12" s="132"/>
-      <c r="H12" s="132"/>
-      <c r="I12" s="129"/>
-      <c r="J12" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="K12" s="43" t="s">
-        <v>94</v>
-      </c>
-      <c r="L12" s="28"/>
-    </row>
-    <row r="13" spans="5:21" x14ac:dyDescent="0.3">
-      <c r="E13" s="87" t="s">
-        <v>12</v>
-      </c>
-      <c r="F13" s="107">
-        <v>2450210.98</v>
-      </c>
-      <c r="G13" s="108"/>
-      <c r="H13" s="109"/>
-      <c r="I13" s="130" t="s">
-        <v>56</v>
-      </c>
-      <c r="J13" s="130" t="s">
-        <v>61</v>
-      </c>
-      <c r="K13" s="174" t="s">
-        <v>92</v>
-      </c>
-      <c r="L13" s="172" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="14" spans="5:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E14" s="88"/>
-      <c r="F14" s="110"/>
-      <c r="G14" s="111"/>
-      <c r="H14" s="112"/>
-      <c r="I14" s="131"/>
-      <c r="J14" s="131"/>
-      <c r="K14" s="175"/>
-      <c r="L14" s="173"/>
-    </row>
-    <row r="15" spans="5:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E15" s="150"/>
-      <c r="F15" s="150"/>
-    </row>
-    <row r="16" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E16" s="60" t="s">
-        <v>15</v>
-      </c>
-      <c r="F16" s="61"/>
-      <c r="G16" s="61"/>
-      <c r="H16" s="61"/>
-      <c r="I16" s="61"/>
-      <c r="J16" s="61"/>
-      <c r="K16" s="61"/>
-      <c r="L16" s="62"/>
-      <c r="N16" s="60" t="s">
-        <v>95</v>
-      </c>
-      <c r="O16" s="61"/>
-      <c r="P16" s="61"/>
-      <c r="Q16" s="61"/>
-      <c r="R16" s="61"/>
-      <c r="S16" s="61"/>
-      <c r="T16" s="61"/>
-      <c r="U16" s="62"/>
-    </row>
-    <row r="17" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E17" s="9"/>
-      <c r="F17" s="75" t="s">
-        <v>2</v>
-      </c>
-      <c r="G17" s="76"/>
-      <c r="H17" s="77"/>
-      <c r="I17" s="14"/>
-      <c r="J17" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="K17" s="63" t="s">
-        <v>25</v>
-      </c>
-      <c r="L17" s="65"/>
-      <c r="N17" s="9"/>
-      <c r="O17" s="75" t="s">
-        <v>2</v>
-      </c>
-      <c r="P17" s="76"/>
-      <c r="Q17" s="77"/>
-      <c r="R17" s="8"/>
-      <c r="S17" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="T17" s="75" t="s">
-        <v>25</v>
-      </c>
-      <c r="U17" s="77"/>
-    </row>
-    <row r="18" spans="5:21" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E18" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="F18" s="162" t="s">
-        <v>141</v>
-      </c>
-      <c r="G18" s="163"/>
-      <c r="H18" s="164"/>
-      <c r="I18" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="J18" s="39" t="s">
-        <v>148</v>
-      </c>
-      <c r="K18" s="152" t="s">
-        <v>142</v>
-      </c>
-      <c r="L18" s="153"/>
-      <c r="N18" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="O18" s="70"/>
-      <c r="P18" s="71"/>
-      <c r="Q18" s="72"/>
-      <c r="R18" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="S18" s="3"/>
-      <c r="T18" s="183"/>
-      <c r="U18" s="184"/>
-    </row>
-    <row r="19" spans="5:21" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E19" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="F19" s="133" t="s">
-        <v>139</v>
-      </c>
-      <c r="G19" s="134"/>
-      <c r="H19" s="135"/>
-      <c r="I19" s="37" t="s">
-        <v>52</v>
-      </c>
-      <c r="J19" s="40" t="s">
-        <v>145</v>
-      </c>
-      <c r="K19" s="154"/>
-      <c r="L19" s="155"/>
-      <c r="N19" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="O19" s="70"/>
-      <c r="P19" s="71"/>
-      <c r="Q19" s="72"/>
-      <c r="R19" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="S19" s="3"/>
-      <c r="T19" s="185"/>
-      <c r="U19" s="186"/>
-    </row>
-    <row r="20" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E20" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="F20" s="133" t="s">
-        <v>121</v>
-      </c>
-      <c r="G20" s="134"/>
-      <c r="H20" s="135"/>
-      <c r="I20" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="J20" s="40" t="s">
-        <v>144</v>
-      </c>
-      <c r="K20" s="154"/>
-      <c r="L20" s="155"/>
-      <c r="N20" s="66"/>
-      <c r="O20" s="67"/>
-      <c r="P20" s="67"/>
-      <c r="Q20" s="68"/>
-      <c r="R20" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="S20" s="11"/>
-      <c r="T20" s="187"/>
-      <c r="U20" s="188"/>
-    </row>
-    <row r="21" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E21" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="F21" s="133" t="s">
-        <v>140</v>
-      </c>
-      <c r="G21" s="134"/>
-      <c r="H21" s="135"/>
-      <c r="I21" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="J21" s="40" t="s">
-        <v>70</v>
-      </c>
-      <c r="K21" s="154"/>
-      <c r="L21" s="155"/>
-    </row>
-    <row r="22" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E22" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="F22" s="136">
-        <v>46162</v>
-      </c>
-      <c r="G22" s="134"/>
-      <c r="H22" s="135"/>
-      <c r="I22" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="J22" s="40" t="s">
-        <v>143</v>
-      </c>
-      <c r="K22" s="154"/>
-      <c r="L22" s="155"/>
-      <c r="N22" s="60" t="s">
-        <v>96</v>
-      </c>
-      <c r="O22" s="61"/>
-      <c r="P22" s="61"/>
-      <c r="Q22" s="61"/>
-      <c r="R22" s="61"/>
-      <c r="S22" s="61"/>
-      <c r="T22" s="61"/>
-      <c r="U22" s="62"/>
-    </row>
-    <row r="23" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E23" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="F23" s="137">
-        <v>46497</v>
-      </c>
-      <c r="G23" s="67"/>
-      <c r="H23" s="68"/>
-      <c r="I23" s="151"/>
-      <c r="J23" s="55"/>
-      <c r="K23" s="156"/>
-      <c r="L23" s="157"/>
-      <c r="N23" s="9"/>
-      <c r="O23" s="75" t="s">
-        <v>2</v>
-      </c>
-      <c r="P23" s="76"/>
-      <c r="Q23" s="77"/>
-      <c r="R23" s="8"/>
-      <c r="S23" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="T23" s="75" t="s">
-        <v>25</v>
-      </c>
-      <c r="U23" s="77"/>
-    </row>
-    <row r="24" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="N24" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="O24" s="70"/>
-      <c r="P24" s="71"/>
-      <c r="Q24" s="72"/>
-      <c r="R24" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="S24" s="3"/>
-      <c r="T24" s="183"/>
-      <c r="U24" s="184"/>
-    </row>
-    <row r="25" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E25" s="60" t="s">
-        <v>26</v>
-      </c>
-      <c r="F25" s="61"/>
-      <c r="G25" s="61"/>
-      <c r="H25" s="61"/>
-      <c r="I25" s="61"/>
-      <c r="J25" s="61"/>
-      <c r="K25" s="61"/>
-      <c r="L25" s="62"/>
-      <c r="N25" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="O25" s="70"/>
-      <c r="P25" s="71"/>
-      <c r="Q25" s="72"/>
-      <c r="R25" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="S25" s="3"/>
-      <c r="T25" s="185"/>
-      <c r="U25" s="186"/>
-    </row>
-    <row r="26" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E26" s="12"/>
-      <c r="F26" s="63" t="s">
-        <v>2</v>
-      </c>
-      <c r="G26" s="64"/>
-      <c r="H26" s="65"/>
-      <c r="I26" s="14"/>
-      <c r="J26" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="K26" s="63" t="s">
-        <v>25</v>
-      </c>
-      <c r="L26" s="65"/>
-      <c r="N26" s="66"/>
-      <c r="O26" s="67"/>
-      <c r="P26" s="67"/>
-      <c r="Q26" s="68"/>
-      <c r="R26" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="S26" s="11"/>
-      <c r="T26" s="187"/>
-      <c r="U26" s="188"/>
-    </row>
-    <row r="27" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E27" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F27" s="160" t="s">
-        <v>149</v>
-      </c>
-      <c r="G27" s="160"/>
-      <c r="H27" s="161"/>
-      <c r="I27" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="J27" s="35" t="s">
-        <v>151</v>
-      </c>
-      <c r="K27" s="166" t="s">
-        <v>150</v>
-      </c>
-      <c r="L27" s="167"/>
-    </row>
-    <row r="28" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E28" s="57"/>
-      <c r="F28" s="58"/>
-      <c r="G28" s="58"/>
-      <c r="H28" s="59"/>
-      <c r="I28" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="J28" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="K28" s="168"/>
-      <c r="L28" s="169"/>
-      <c r="N28" s="60" t="s">
-        <v>98</v>
-      </c>
-      <c r="O28" s="61"/>
-      <c r="P28" s="61"/>
-      <c r="Q28" s="61"/>
-      <c r="R28" s="61"/>
-      <c r="S28" s="61"/>
-      <c r="T28" s="61"/>
-      <c r="U28" s="62"/>
-    </row>
-    <row r="29" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="N29" s="9"/>
-      <c r="O29" s="75" t="s">
-        <v>2</v>
-      </c>
-      <c r="P29" s="76"/>
-      <c r="Q29" s="77"/>
-      <c r="R29" s="8"/>
-      <c r="S29" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="T29" s="75" t="s">
-        <v>25</v>
-      </c>
-      <c r="U29" s="77"/>
-    </row>
-    <row r="30" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E30" s="60" t="s">
-        <v>28</v>
-      </c>
-      <c r="F30" s="61"/>
-      <c r="G30" s="61"/>
-      <c r="H30" s="61"/>
-      <c r="I30" s="61"/>
-      <c r="J30" s="61"/>
-      <c r="K30" s="61"/>
-      <c r="L30" s="62"/>
-      <c r="N30" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="O30" s="70"/>
-      <c r="P30" s="71"/>
-      <c r="Q30" s="72"/>
-      <c r="R30" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="S30" s="3"/>
-      <c r="T30" s="183"/>
-      <c r="U30" s="184"/>
-    </row>
-    <row r="31" spans="5:21" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E31" s="12"/>
-      <c r="F31" s="63" t="s">
-        <v>2</v>
-      </c>
-      <c r="G31" s="64"/>
-      <c r="H31" s="65"/>
-      <c r="I31" s="14"/>
-      <c r="J31" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="K31" s="63" t="s">
-        <v>25</v>
-      </c>
-      <c r="L31" s="65"/>
-      <c r="N31" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="O31" s="70"/>
-      <c r="P31" s="71"/>
-      <c r="Q31" s="72"/>
-      <c r="R31" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="S31" s="3"/>
-      <c r="T31" s="185"/>
-      <c r="U31" s="186"/>
-    </row>
-    <row r="32" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E32" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="F32" s="48"/>
-      <c r="G32" s="48"/>
-      <c r="H32" s="49"/>
-      <c r="I32" s="38" t="s">
-        <v>50</v>
-      </c>
-      <c r="J32" s="17"/>
-      <c r="K32" s="158"/>
-      <c r="L32" s="159"/>
-      <c r="N32" s="66"/>
-      <c r="O32" s="67"/>
-      <c r="P32" s="67"/>
-      <c r="Q32" s="68"/>
-      <c r="R32" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="S32" s="11"/>
-      <c r="T32" s="187"/>
-      <c r="U32" s="188"/>
-    </row>
-    <row r="33" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="34" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E34" s="60" t="s">
-        <v>29</v>
-      </c>
-      <c r="F34" s="61"/>
-      <c r="G34" s="61"/>
-      <c r="H34" s="61"/>
-      <c r="I34" s="61"/>
-      <c r="J34" s="61"/>
-      <c r="K34" s="61"/>
-      <c r="L34" s="62"/>
-      <c r="N34" s="60" t="s">
-        <v>97</v>
-      </c>
-      <c r="O34" s="61"/>
-      <c r="P34" s="61"/>
-      <c r="Q34" s="61"/>
-      <c r="R34" s="61"/>
-      <c r="S34" s="61"/>
-      <c r="T34" s="61"/>
-      <c r="U34" s="62"/>
-    </row>
-    <row r="35" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E35" s="12"/>
-      <c r="F35" s="176" t="s">
-        <v>2</v>
-      </c>
-      <c r="G35" s="177"/>
-      <c r="H35" s="178"/>
-      <c r="I35" s="41"/>
-      <c r="J35" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="K35" s="176" t="s">
-        <v>25</v>
-      </c>
-      <c r="L35" s="178"/>
-      <c r="N35" s="9"/>
-      <c r="O35" s="75" t="s">
-        <v>2</v>
-      </c>
-      <c r="P35" s="76"/>
-      <c r="Q35" s="77"/>
-      <c r="R35" s="8"/>
-      <c r="S35" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="T35" s="75" t="s">
-        <v>25</v>
-      </c>
-      <c r="U35" s="77"/>
-    </row>
-    <row r="36" spans="5:21" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E36" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="F36" s="136"/>
-      <c r="G36" s="179"/>
-      <c r="H36" s="180"/>
-      <c r="I36" s="42" t="s">
-        <v>51</v>
-      </c>
-      <c r="J36" s="35"/>
-      <c r="K36" s="166"/>
-      <c r="L36" s="167"/>
-      <c r="N36" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="O36" s="70"/>
-      <c r="P36" s="71"/>
-      <c r="Q36" s="72"/>
-      <c r="R36" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="S36" s="3"/>
-      <c r="T36" s="183"/>
-      <c r="U36" s="184"/>
-    </row>
-    <row r="37" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E37" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="F37" s="137"/>
-      <c r="G37" s="181"/>
-      <c r="H37" s="182"/>
-      <c r="I37" s="50"/>
-      <c r="J37" s="54"/>
-      <c r="K37" s="168"/>
-      <c r="L37" s="169"/>
-      <c r="N37" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="O37" s="70"/>
-      <c r="P37" s="71"/>
-      <c r="Q37" s="72"/>
-      <c r="R37" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="S37" s="3"/>
-      <c r="T37" s="185"/>
-      <c r="U37" s="186"/>
-    </row>
-    <row r="38" spans="5:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="N38" s="66"/>
-      <c r="O38" s="67"/>
-      <c r="P38" s="67"/>
-      <c r="Q38" s="68"/>
-      <c r="R38" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="S38" s="11"/>
-      <c r="T38" s="187"/>
-      <c r="U38" s="188"/>
-    </row>
-  </sheetData>
-  <mergeCells count="76">
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="K36:L37"/>
-    <mergeCell ref="O36:Q36"/>
-    <mergeCell ref="T36:U38"/>
-    <mergeCell ref="F37:H37"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="O37:Q37"/>
-    <mergeCell ref="N38:Q38"/>
-    <mergeCell ref="E34:L34"/>
-    <mergeCell ref="N34:U34"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="K35:L35"/>
-    <mergeCell ref="O35:Q35"/>
-    <mergeCell ref="T35:U35"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="N26:Q26"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="K27:L28"/>
+    <mergeCell ref="E28:H28"/>
+    <mergeCell ref="N28:U28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="T29:U29"/>
     <mergeCell ref="E30:L30"/>
     <mergeCell ref="O30:Q30"/>
     <mergeCell ref="T30:U32"/>
@@ -5491,66 +8209,30 @@
     <mergeCell ref="F32:H32"/>
     <mergeCell ref="K32:L32"/>
     <mergeCell ref="N32:Q32"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="K27:L28"/>
-    <mergeCell ref="E28:H28"/>
-    <mergeCell ref="N28:U28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="T29:U29"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="T24:U26"/>
-    <mergeCell ref="E25:L25"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="K26:L26"/>
-    <mergeCell ref="N26:Q26"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="K18:L23"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="T18:U20"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="N20:Q20"/>
-    <mergeCell ref="F21:H21"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="N22:U22"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="T23:U23"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="E16:L16"/>
-    <mergeCell ref="N16:U16"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="T17:U17"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="F13:H14"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="K13:K14"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="F12:H12"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="E2:L4"/>
-    <mergeCell ref="E5:L5"/>
-    <mergeCell ref="E6:L6"/>
-    <mergeCell ref="E7:H7"/>
-    <mergeCell ref="I7:L7"/>
+    <mergeCell ref="E34:L34"/>
+    <mergeCell ref="N34:U34"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="K35:L35"/>
+    <mergeCell ref="O35:Q35"/>
+    <mergeCell ref="T35:U35"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="K36:L37"/>
+    <mergeCell ref="O36:Q36"/>
+    <mergeCell ref="T36:U38"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="O37:Q37"/>
+    <mergeCell ref="N38:Q38"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="F9" r:id="rId1" xr:uid="{ED0CCA0E-CA9F-40FC-B053-D3520CF7C88B}"/>
+  </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId2"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5C041EC-DD6B-4236-BBFF-DFA8277DE62C}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5559,7 +8241,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17161BA0-1875-4324-913B-9E841E318654}">
   <dimension ref="B1:P52"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5575,82 +8257,82 @@
   <sheetData>
     <row r="1" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="E2" s="89" t="s">
+      <c r="E2" s="203" t="s">
         <v>67</v>
       </c>
-      <c r="F2" s="90"/>
-      <c r="G2" s="90"/>
-      <c r="H2" s="90"/>
-      <c r="I2" s="90"/>
-      <c r="J2" s="90"/>
-      <c r="K2" s="90"/>
-      <c r="L2" s="91"/>
+      <c r="F2" s="204"/>
+      <c r="G2" s="204"/>
+      <c r="H2" s="204"/>
+      <c r="I2" s="204"/>
+      <c r="J2" s="204"/>
+      <c r="K2" s="204"/>
+      <c r="L2" s="205"/>
     </row>
     <row r="3" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="E3" s="92"/>
-      <c r="F3" s="93"/>
-      <c r="G3" s="93"/>
-      <c r="H3" s="93"/>
-      <c r="I3" s="93"/>
-      <c r="J3" s="93"/>
-      <c r="K3" s="93"/>
-      <c r="L3" s="94"/>
+      <c r="E3" s="206"/>
+      <c r="F3" s="207"/>
+      <c r="G3" s="207"/>
+      <c r="H3" s="207"/>
+      <c r="I3" s="207"/>
+      <c r="J3" s="207"/>
+      <c r="K3" s="207"/>
+      <c r="L3" s="208"/>
     </row>
     <row r="4" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E4" s="95"/>
-      <c r="F4" s="96"/>
-      <c r="G4" s="96"/>
-      <c r="H4" s="96"/>
-      <c r="I4" s="96"/>
-      <c r="J4" s="96"/>
-      <c r="K4" s="96"/>
-      <c r="L4" s="97"/>
+      <c r="E4" s="209"/>
+      <c r="F4" s="210"/>
+      <c r="G4" s="210"/>
+      <c r="H4" s="210"/>
+      <c r="I4" s="210"/>
+      <c r="J4" s="210"/>
+      <c r="K4" s="210"/>
+      <c r="L4" s="211"/>
     </row>
     <row r="5" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="E5" s="98" t="s">
+      <c r="E5" s="212" t="s">
         <v>1</v>
       </c>
-      <c r="F5" s="99"/>
-      <c r="G5" s="99"/>
-      <c r="H5" s="99"/>
-      <c r="I5" s="99"/>
-      <c r="J5" s="99"/>
-      <c r="K5" s="99"/>
-      <c r="L5" s="100"/>
+      <c r="F5" s="213"/>
+      <c r="G5" s="213"/>
+      <c r="H5" s="213"/>
+      <c r="I5" s="213"/>
+      <c r="J5" s="213"/>
+      <c r="K5" s="213"/>
+      <c r="L5" s="214"/>
       <c r="M5" s="23"/>
       <c r="N5" s="23"/>
       <c r="O5" s="23"/>
       <c r="P5" s="23"/>
     </row>
     <row r="6" spans="3:16" ht="69" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E6" s="101" t="s">
+      <c r="E6" s="135" t="s">
         <v>68</v>
       </c>
-      <c r="F6" s="102"/>
-      <c r="G6" s="102"/>
-      <c r="H6" s="102"/>
-      <c r="I6" s="102"/>
-      <c r="J6" s="102"/>
-      <c r="K6" s="102"/>
-      <c r="L6" s="103"/>
+      <c r="F6" s="136"/>
+      <c r="G6" s="136"/>
+      <c r="H6" s="136"/>
+      <c r="I6" s="136"/>
+      <c r="J6" s="136"/>
+      <c r="K6" s="136"/>
+      <c r="L6" s="137"/>
       <c r="M6" s="24"/>
       <c r="N6" s="24"/>
       <c r="O6" s="24"/>
       <c r="P6" s="24"/>
     </row>
     <row r="7" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="E7" s="104" t="s">
+      <c r="E7" s="138" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="105"/>
-      <c r="G7" s="105"/>
-      <c r="H7" s="105"/>
-      <c r="I7" s="105" t="s">
+      <c r="F7" s="139"/>
+      <c r="G7" s="139"/>
+      <c r="H7" s="139"/>
+      <c r="I7" s="139" t="s">
         <v>3</v>
       </c>
-      <c r="J7" s="105"/>
-      <c r="K7" s="105"/>
-      <c r="L7" s="106"/>
+      <c r="J7" s="139"/>
+      <c r="K7" s="139"/>
+      <c r="L7" s="140"/>
       <c r="M7" s="25"/>
       <c r="N7" s="25"/>
       <c r="O7" s="25"/>
@@ -5660,11 +8342,11 @@
       <c r="E8" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="F8" s="124" t="s">
+      <c r="F8" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="G8" s="125"/>
-      <c r="H8" s="113"/>
+      <c r="G8" s="142"/>
+      <c r="H8" s="101"/>
       <c r="I8" s="26" t="s">
         <v>62</v>
       </c>
@@ -5682,12 +8364,12 @@
       <c r="E9" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="F9" s="126" t="s">
+      <c r="F9" s="127" t="s">
         <v>70</v>
       </c>
-      <c r="G9" s="127"/>
-      <c r="H9" s="128"/>
-      <c r="I9" s="126" t="s">
+      <c r="G9" s="128"/>
+      <c r="H9" s="129"/>
+      <c r="I9" s="127" t="s">
         <v>54</v>
       </c>
       <c r="J9" s="32" t="s">
@@ -5702,12 +8384,12 @@
       <c r="E10" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="F10" s="126" t="s">
+      <c r="F10" s="127" t="s">
         <v>11</v>
       </c>
-      <c r="G10" s="127"/>
-      <c r="H10" s="128"/>
-      <c r="I10" s="129"/>
+      <c r="G10" s="128"/>
+      <c r="H10" s="129"/>
+      <c r="I10" s="130"/>
       <c r="J10" s="32" t="s">
         <v>58</v>
       </c>
@@ -5720,12 +8402,12 @@
       <c r="E11" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="F11" s="126" t="s">
+      <c r="F11" s="127" t="s">
         <v>10</v>
       </c>
-      <c r="G11" s="127"/>
-      <c r="H11" s="127"/>
-      <c r="I11" s="130" t="s">
+      <c r="G11" s="128"/>
+      <c r="H11" s="128"/>
+      <c r="I11" s="143" t="s">
         <v>55</v>
       </c>
       <c r="J11" s="32" t="s">
@@ -5740,12 +8422,12 @@
       <c r="E12" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="F12" s="129" t="s">
+      <c r="F12" s="130" t="s">
         <v>70</v>
       </c>
-      <c r="G12" s="132"/>
-      <c r="H12" s="132"/>
-      <c r="I12" s="131"/>
+      <c r="G12" s="131"/>
+      <c r="H12" s="131"/>
+      <c r="I12" s="144"/>
       <c r="J12" s="32" t="s">
         <v>60</v>
       </c>
@@ -5755,32 +8437,32 @@
       <c r="L12" s="28"/>
     </row>
     <row r="13" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="E13" s="87" t="s">
+      <c r="E13" s="93" t="s">
         <v>12</v>
       </c>
-      <c r="F13" s="107" t="s">
+      <c r="F13" s="95" t="s">
         <v>70</v>
       </c>
-      <c r="G13" s="108"/>
-      <c r="H13" s="109"/>
-      <c r="I13" s="113" t="s">
+      <c r="G13" s="96"/>
+      <c r="H13" s="97"/>
+      <c r="I13" s="101" t="s">
         <v>56</v>
       </c>
-      <c r="J13" s="115" t="s">
+      <c r="J13" s="103" t="s">
         <v>61</v>
       </c>
-      <c r="K13" s="117"/>
-      <c r="L13" s="119"/>
+      <c r="K13" s="105"/>
+      <c r="L13" s="145"/>
     </row>
     <row r="14" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E14" s="88"/>
-      <c r="F14" s="110"/>
-      <c r="G14" s="111"/>
-      <c r="H14" s="112"/>
-      <c r="I14" s="114"/>
-      <c r="J14" s="116"/>
-      <c r="K14" s="118"/>
-      <c r="L14" s="120"/>
+      <c r="E14" s="94"/>
+      <c r="F14" s="98"/>
+      <c r="G14" s="99"/>
+      <c r="H14" s="100"/>
+      <c r="I14" s="102"/>
+      <c r="J14" s="104"/>
+      <c r="K14" s="106"/>
+      <c r="L14" s="146"/>
     </row>
     <row r="15" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C15" s="2"/>
@@ -5798,35 +8480,35 @@
     <row r="16" spans="3:16" s="1" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
-      <c r="E16" s="60" t="s">
+      <c r="E16" s="83" t="s">
         <v>15</v>
       </c>
-      <c r="F16" s="61"/>
-      <c r="G16" s="61"/>
-      <c r="H16" s="61"/>
-      <c r="I16" s="79"/>
-      <c r="J16" s="61"/>
-      <c r="K16" s="61"/>
-      <c r="L16" s="62"/>
+      <c r="F16" s="84"/>
+      <c r="G16" s="84"/>
+      <c r="H16" s="84"/>
+      <c r="I16" s="216"/>
+      <c r="J16" s="84"/>
+      <c r="K16" s="84"/>
+      <c r="L16" s="85"/>
       <c r="M16" s="5"/>
     </row>
     <row r="17" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="9"/>
-      <c r="F17" s="75" t="s">
+      <c r="F17" s="113" t="s">
         <v>2</v>
       </c>
-      <c r="G17" s="76"/>
-      <c r="H17" s="77"/>
+      <c r="G17" s="114"/>
+      <c r="H17" s="115"/>
       <c r="I17" s="8"/>
       <c r="J17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="K17" s="63" t="s">
+      <c r="K17" s="72" t="s">
         <v>25</v>
       </c>
-      <c r="L17" s="65"/>
+      <c r="L17" s="74"/>
       <c r="M17" s="2"/>
     </row>
     <row r="18" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -5835,15 +8517,15 @@
       <c r="E18" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="F18" s="83"/>
-      <c r="G18" s="84"/>
-      <c r="H18" s="84"/>
+      <c r="F18" s="220"/>
+      <c r="G18" s="221"/>
+      <c r="H18" s="221"/>
       <c r="I18" s="18" t="s">
         <v>30</v>
       </c>
       <c r="J18" s="15"/>
-      <c r="K18" s="73"/>
-      <c r="L18" s="74"/>
+      <c r="K18" s="222"/>
+      <c r="L18" s="223"/>
       <c r="M18" s="2"/>
     </row>
     <row r="19" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -5852,15 +8534,15 @@
       <c r="E19" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="F19" s="70"/>
-      <c r="G19" s="71"/>
-      <c r="H19" s="71"/>
+      <c r="F19" s="171"/>
+      <c r="G19" s="172"/>
+      <c r="H19" s="172"/>
       <c r="I19" s="19" t="s">
         <v>31</v>
       </c>
       <c r="J19" s="16"/>
-      <c r="K19" s="85"/>
-      <c r="L19" s="86"/>
+      <c r="K19" s="199"/>
+      <c r="L19" s="200"/>
       <c r="M19" s="2"/>
     </row>
     <row r="20" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -5869,15 +8551,15 @@
       <c r="E20" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="F20" s="70"/>
-      <c r="G20" s="71"/>
-      <c r="H20" s="71"/>
+      <c r="F20" s="171"/>
+      <c r="G20" s="172"/>
+      <c r="H20" s="172"/>
       <c r="I20" s="19" t="s">
         <v>32</v>
       </c>
       <c r="J20" s="16"/>
-      <c r="K20" s="85"/>
-      <c r="L20" s="86"/>
+      <c r="K20" s="199"/>
+      <c r="L20" s="200"/>
       <c r="M20" s="2"/>
     </row>
     <row r="21" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -5886,15 +8568,15 @@
       <c r="E21" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="F21" s="70"/>
-      <c r="G21" s="71"/>
-      <c r="H21" s="71"/>
+      <c r="F21" s="171"/>
+      <c r="G21" s="172"/>
+      <c r="H21" s="172"/>
       <c r="I21" s="19" t="s">
         <v>33</v>
       </c>
       <c r="J21" s="16"/>
-      <c r="K21" s="85"/>
-      <c r="L21" s="86"/>
+      <c r="K21" s="199"/>
+      <c r="L21" s="200"/>
       <c r="M21" s="2"/>
     </row>
     <row r="22" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -5903,15 +8585,15 @@
       <c r="E22" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="F22" s="70"/>
-      <c r="G22" s="71"/>
-      <c r="H22" s="71"/>
+      <c r="F22" s="171"/>
+      <c r="G22" s="172"/>
+      <c r="H22" s="172"/>
       <c r="I22" s="19" t="s">
         <v>34</v>
       </c>
       <c r="J22" s="16"/>
-      <c r="K22" s="85"/>
-      <c r="L22" s="86"/>
+      <c r="K22" s="199"/>
+      <c r="L22" s="200"/>
       <c r="M22" s="2"/>
     </row>
     <row r="23" spans="2:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -5920,28 +8602,28 @@
       <c r="E23" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="F23" s="53"/>
-      <c r="G23" s="51"/>
-      <c r="H23" s="51"/>
-      <c r="I23" s="121"/>
-      <c r="J23" s="122"/>
-      <c r="K23" s="122"/>
-      <c r="L23" s="123"/>
+      <c r="F23" s="201"/>
+      <c r="G23" s="202"/>
+      <c r="H23" s="202"/>
+      <c r="I23" s="196"/>
+      <c r="J23" s="197"/>
+      <c r="K23" s="197"/>
+      <c r="L23" s="198"/>
       <c r="M23" s="2"/>
     </row>
     <row r="24" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
-      <c r="E24" s="80" t="s">
+      <c r="E24" s="217" t="s">
         <v>16</v>
       </c>
-      <c r="F24" s="81"/>
-      <c r="G24" s="81"/>
-      <c r="H24" s="81"/>
-      <c r="I24" s="81"/>
-      <c r="J24" s="81"/>
-      <c r="K24" s="81"/>
-      <c r="L24" s="82"/>
+      <c r="F24" s="218"/>
+      <c r="G24" s="218"/>
+      <c r="H24" s="218"/>
+      <c r="I24" s="218"/>
+      <c r="J24" s="218"/>
+      <c r="K24" s="218"/>
+      <c r="L24" s="219"/>
       <c r="M24" s="2"/>
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.3">
@@ -5950,15 +8632,15 @@
       <c r="E25" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F25" s="70"/>
-      <c r="G25" s="71"/>
-      <c r="H25" s="78"/>
+      <c r="F25" s="171"/>
+      <c r="G25" s="172"/>
+      <c r="H25" s="215"/>
       <c r="I25" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="J25" s="70"/>
-      <c r="K25" s="71"/>
-      <c r="L25" s="72"/>
+      <c r="J25" s="171"/>
+      <c r="K25" s="172"/>
+      <c r="L25" s="173"/>
       <c r="M25" s="2"/>
     </row>
     <row r="26" spans="2:13" x14ac:dyDescent="0.3">
@@ -5967,15 +8649,15 @@
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F26" s="70"/>
-      <c r="G26" s="71"/>
-      <c r="H26" s="78"/>
+      <c r="F26" s="171"/>
+      <c r="G26" s="172"/>
+      <c r="H26" s="215"/>
       <c r="I26" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="J26" s="70"/>
-      <c r="K26" s="71"/>
-      <c r="L26" s="72"/>
+      <c r="J26" s="171"/>
+      <c r="K26" s="172"/>
+      <c r="L26" s="173"/>
       <c r="M26" s="2"/>
     </row>
     <row r="27" spans="2:13" x14ac:dyDescent="0.3">
@@ -5984,15 +8666,15 @@
       <c r="E27" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="F27" s="70"/>
-      <c r="G27" s="71"/>
-      <c r="H27" s="78"/>
+      <c r="F27" s="171"/>
+      <c r="G27" s="172"/>
+      <c r="H27" s="215"/>
       <c r="I27" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="J27" s="70"/>
-      <c r="K27" s="71"/>
-      <c r="L27" s="72"/>
+      <c r="J27" s="171"/>
+      <c r="K27" s="172"/>
+      <c r="L27" s="173"/>
       <c r="M27" s="2"/>
     </row>
     <row r="28" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6001,13 +8683,13 @@
       <c r="E28" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="F28" s="53"/>
-      <c r="G28" s="51"/>
-      <c r="H28" s="54"/>
-      <c r="I28" s="69"/>
-      <c r="J28" s="67"/>
-      <c r="K28" s="67"/>
-      <c r="L28" s="68"/>
+      <c r="F28" s="201"/>
+      <c r="G28" s="202"/>
+      <c r="H28" s="66"/>
+      <c r="I28" s="193"/>
+      <c r="J28" s="60"/>
+      <c r="K28" s="60"/>
+      <c r="L28" s="61"/>
       <c r="M28" s="2"/>
     </row>
     <row r="29" spans="2:13" x14ac:dyDescent="0.3">
@@ -6040,35 +8722,35 @@
     <row r="31" spans="2:13" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
-      <c r="E31" s="60" t="s">
+      <c r="E31" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="F31" s="61"/>
-      <c r="G31" s="61"/>
-      <c r="H31" s="61"/>
-      <c r="I31" s="61"/>
-      <c r="J31" s="61"/>
-      <c r="K31" s="61"/>
-      <c r="L31" s="62"/>
+      <c r="F31" s="84"/>
+      <c r="G31" s="84"/>
+      <c r="H31" s="84"/>
+      <c r="I31" s="84"/>
+      <c r="J31" s="84"/>
+      <c r="K31" s="84"/>
+      <c r="L31" s="85"/>
       <c r="M31" s="2"/>
     </row>
     <row r="32" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
       <c r="E32" s="12"/>
-      <c r="F32" s="63" t="s">
+      <c r="F32" s="72" t="s">
         <v>2</v>
       </c>
-      <c r="G32" s="64"/>
-      <c r="H32" s="65"/>
+      <c r="G32" s="73"/>
+      <c r="H32" s="74"/>
       <c r="I32" s="14"/>
       <c r="J32" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="K32" s="63" t="s">
+      <c r="K32" s="72" t="s">
         <v>25</v>
       </c>
-      <c r="L32" s="65"/>
+      <c r="L32" s="74"/>
       <c r="M32" s="2"/>
     </row>
     <row r="33" spans="3:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -6077,30 +8759,30 @@
       <c r="E33" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="F33" s="46"/>
-      <c r="G33" s="46"/>
-      <c r="H33" s="47"/>
+      <c r="F33" s="225"/>
+      <c r="G33" s="225"/>
+      <c r="H33" s="226"/>
       <c r="I33" s="21" t="s">
         <v>41</v>
       </c>
       <c r="J33" s="3"/>
-      <c r="K33" s="46"/>
-      <c r="L33" s="47"/>
+      <c r="K33" s="225"/>
+      <c r="L33" s="226"/>
       <c r="M33" s="2"/>
     </row>
     <row r="34" spans="3:13" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
-      <c r="E34" s="57"/>
-      <c r="F34" s="58"/>
-      <c r="G34" s="58"/>
-      <c r="H34" s="59"/>
+      <c r="E34" s="80"/>
+      <c r="F34" s="81"/>
+      <c r="G34" s="81"/>
+      <c r="H34" s="82"/>
       <c r="I34" s="22" t="s">
         <v>42</v>
       </c>
       <c r="J34" s="11"/>
-      <c r="K34" s="55"/>
-      <c r="L34" s="56"/>
+      <c r="K34" s="67"/>
+      <c r="L34" s="224"/>
       <c r="M34" s="2"/>
     </row>
     <row r="35" spans="3:13" x14ac:dyDescent="0.3">
@@ -6118,195 +8800,205 @@
     </row>
     <row r="36" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="37" spans="3:13" s="1" customFormat="1" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E37" s="60" t="s">
+      <c r="E37" s="83" t="s">
         <v>27</v>
       </c>
-      <c r="F37" s="61"/>
-      <c r="G37" s="61"/>
-      <c r="H37" s="61"/>
-      <c r="I37" s="61"/>
-      <c r="J37" s="61"/>
-      <c r="K37" s="61"/>
-      <c r="L37" s="62"/>
+      <c r="F37" s="84"/>
+      <c r="G37" s="84"/>
+      <c r="H37" s="84"/>
+      <c r="I37" s="84"/>
+      <c r="J37" s="84"/>
+      <c r="K37" s="84"/>
+      <c r="L37" s="85"/>
     </row>
     <row r="38" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E38" s="9"/>
-      <c r="F38" s="75" t="s">
+      <c r="F38" s="113" t="s">
         <v>2</v>
       </c>
-      <c r="G38" s="76"/>
-      <c r="H38" s="77"/>
+      <c r="G38" s="114"/>
+      <c r="H38" s="115"/>
       <c r="I38" s="8"/>
       <c r="J38" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="K38" s="75" t="s">
+      <c r="K38" s="113" t="s">
         <v>25</v>
       </c>
-      <c r="L38" s="77"/>
+      <c r="L38" s="115"/>
     </row>
     <row r="39" spans="3:13" x14ac:dyDescent="0.3">
       <c r="E39" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="F39" s="70"/>
-      <c r="G39" s="71"/>
-      <c r="H39" s="72"/>
+      <c r="F39" s="171"/>
+      <c r="G39" s="172"/>
+      <c r="H39" s="173"/>
       <c r="I39" s="21" t="s">
         <v>45</v>
       </c>
       <c r="J39" s="3"/>
-      <c r="K39" s="46"/>
-      <c r="L39" s="47"/>
+      <c r="K39" s="225"/>
+      <c r="L39" s="226"/>
     </row>
     <row r="40" spans="3:13" x14ac:dyDescent="0.3">
       <c r="E40" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="F40" s="70"/>
-      <c r="G40" s="71"/>
-      <c r="H40" s="72"/>
+      <c r="F40" s="171"/>
+      <c r="G40" s="172"/>
+      <c r="H40" s="173"/>
       <c r="I40" s="21" t="s">
         <v>46</v>
       </c>
       <c r="J40" s="3"/>
-      <c r="K40" s="46"/>
-      <c r="L40" s="47"/>
+      <c r="K40" s="225"/>
+      <c r="L40" s="226"/>
     </row>
     <row r="41" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E41" s="66"/>
-      <c r="F41" s="67"/>
-      <c r="G41" s="67"/>
-      <c r="H41" s="68"/>
+      <c r="E41" s="155"/>
+      <c r="F41" s="60"/>
+      <c r="G41" s="60"/>
+      <c r="H41" s="61"/>
       <c r="I41" s="22" t="s">
         <v>47</v>
       </c>
       <c r="J41" s="11"/>
-      <c r="K41" s="55"/>
-      <c r="L41" s="56"/>
+      <c r="K41" s="67"/>
+      <c r="L41" s="224"/>
     </row>
     <row r="43" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="44" spans="3:13" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E44" s="60" t="s">
+      <c r="E44" s="83" t="s">
         <v>28</v>
       </c>
-      <c r="F44" s="61"/>
-      <c r="G44" s="61"/>
-      <c r="H44" s="61"/>
-      <c r="I44" s="61"/>
-      <c r="J44" s="61"/>
-      <c r="K44" s="61"/>
-      <c r="L44" s="62"/>
+      <c r="F44" s="84"/>
+      <c r="G44" s="84"/>
+      <c r="H44" s="84"/>
+      <c r="I44" s="84"/>
+      <c r="J44" s="84"/>
+      <c r="K44" s="84"/>
+      <c r="L44" s="85"/>
     </row>
     <row r="45" spans="3:13" x14ac:dyDescent="0.3">
       <c r="E45" s="12"/>
-      <c r="F45" s="63" t="s">
+      <c r="F45" s="72" t="s">
         <v>2</v>
       </c>
-      <c r="G45" s="64"/>
-      <c r="H45" s="65"/>
+      <c r="G45" s="73"/>
+      <c r="H45" s="74"/>
       <c r="I45" s="14"/>
       <c r="J45" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="K45" s="63" t="s">
+      <c r="K45" s="72" t="s">
         <v>25</v>
       </c>
-      <c r="L45" s="65"/>
+      <c r="L45" s="74"/>
     </row>
     <row r="46" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E46" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F46" s="55"/>
-      <c r="G46" s="55"/>
-      <c r="H46" s="56"/>
+      <c r="F46" s="67"/>
+      <c r="G46" s="67"/>
+      <c r="H46" s="224"/>
       <c r="I46" s="22" t="s">
         <v>50</v>
       </c>
       <c r="J46" s="11"/>
-      <c r="K46" s="55"/>
-      <c r="L46" s="56"/>
+      <c r="K46" s="67"/>
+      <c r="L46" s="224"/>
     </row>
     <row r="48" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="49" spans="5:12" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E49" s="60" t="s">
+      <c r="E49" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="F49" s="61"/>
-      <c r="G49" s="61"/>
-      <c r="H49" s="61"/>
-      <c r="I49" s="61"/>
-      <c r="J49" s="61"/>
-      <c r="K49" s="61"/>
-      <c r="L49" s="62"/>
+      <c r="F49" s="84"/>
+      <c r="G49" s="84"/>
+      <c r="H49" s="84"/>
+      <c r="I49" s="84"/>
+      <c r="J49" s="84"/>
+      <c r="K49" s="84"/>
+      <c r="L49" s="85"/>
     </row>
     <row r="50" spans="5:12" x14ac:dyDescent="0.3">
       <c r="E50" s="12"/>
-      <c r="F50" s="63" t="s">
+      <c r="F50" s="72" t="s">
         <v>2</v>
       </c>
-      <c r="G50" s="64"/>
-      <c r="H50" s="65"/>
+      <c r="G50" s="73"/>
+      <c r="H50" s="74"/>
       <c r="I50" s="14"/>
       <c r="J50" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="K50" s="63" t="s">
+      <c r="K50" s="72" t="s">
         <v>25</v>
       </c>
-      <c r="L50" s="65"/>
+      <c r="L50" s="74"/>
     </row>
     <row r="51" spans="5:12" x14ac:dyDescent="0.3">
       <c r="E51" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="F51" s="46"/>
-      <c r="G51" s="46"/>
-      <c r="H51" s="47"/>
+      <c r="F51" s="225"/>
+      <c r="G51" s="225"/>
+      <c r="H51" s="226"/>
       <c r="I51" s="21" t="s">
         <v>51</v>
       </c>
       <c r="J51" s="3"/>
-      <c r="K51" s="46"/>
-      <c r="L51" s="47"/>
+      <c r="K51" s="225"/>
+      <c r="L51" s="226"/>
     </row>
     <row r="52" spans="5:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E52" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="F52" s="48"/>
-      <c r="G52" s="48"/>
-      <c r="H52" s="49"/>
-      <c r="I52" s="50"/>
-      <c r="J52" s="51"/>
-      <c r="K52" s="51"/>
-      <c r="L52" s="52"/>
+      <c r="F52" s="75"/>
+      <c r="G52" s="75"/>
+      <c r="H52" s="76"/>
+      <c r="I52" s="166"/>
+      <c r="J52" s="202"/>
+      <c r="K52" s="202"/>
+      <c r="L52" s="227"/>
     </row>
   </sheetData>
   <mergeCells count="70">
-    <mergeCell ref="I23:L23"/>
-    <mergeCell ref="K22:L22"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="F12:H12"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="E2:L4"/>
-    <mergeCell ref="E5:L5"/>
-    <mergeCell ref="E6:L6"/>
-    <mergeCell ref="E7:H7"/>
-    <mergeCell ref="I7:L7"/>
-    <mergeCell ref="F13:H14"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="K13:K14"/>
-    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="F51:H51"/>
+    <mergeCell ref="K51:L51"/>
+    <mergeCell ref="F52:H52"/>
+    <mergeCell ref="I52:L52"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="K33:L33"/>
+    <mergeCell ref="K34:L34"/>
+    <mergeCell ref="F46:H46"/>
+    <mergeCell ref="K46:L46"/>
+    <mergeCell ref="E34:H34"/>
+    <mergeCell ref="E44:L44"/>
+    <mergeCell ref="F45:H45"/>
+    <mergeCell ref="K45:L45"/>
+    <mergeCell ref="E41:H41"/>
+    <mergeCell ref="I28:L28"/>
+    <mergeCell ref="J25:L25"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="E49:L49"/>
+    <mergeCell ref="F50:H50"/>
+    <mergeCell ref="K50:L50"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="E37:L37"/>
+    <mergeCell ref="K41:L41"/>
+    <mergeCell ref="K38:L38"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="K39:L39"/>
+    <mergeCell ref="F40:H40"/>
+    <mergeCell ref="K40:L40"/>
+    <mergeCell ref="E31:L31"/>
+    <mergeCell ref="K32:L32"/>
     <mergeCell ref="J26:L26"/>
     <mergeCell ref="J27:L27"/>
     <mergeCell ref="F27:H27"/>
@@ -6323,38 +9015,28 @@
     <mergeCell ref="F21:H21"/>
     <mergeCell ref="K21:L21"/>
     <mergeCell ref="F22:H22"/>
-    <mergeCell ref="J25:L25"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="E49:L49"/>
-    <mergeCell ref="F50:H50"/>
-    <mergeCell ref="K50:L50"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="E37:L37"/>
-    <mergeCell ref="K41:L41"/>
-    <mergeCell ref="K38:L38"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="K39:L39"/>
-    <mergeCell ref="F40:H40"/>
-    <mergeCell ref="K40:L40"/>
-    <mergeCell ref="E31:L31"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="F51:H51"/>
-    <mergeCell ref="K51:L51"/>
-    <mergeCell ref="F52:H52"/>
-    <mergeCell ref="I52:L52"/>
-    <mergeCell ref="F28:H28"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="K33:L33"/>
-    <mergeCell ref="K34:L34"/>
-    <mergeCell ref="F46:H46"/>
-    <mergeCell ref="K46:L46"/>
-    <mergeCell ref="E34:H34"/>
-    <mergeCell ref="E44:L44"/>
-    <mergeCell ref="F45:H45"/>
-    <mergeCell ref="K45:L45"/>
-    <mergeCell ref="E41:H41"/>
-    <mergeCell ref="I28:L28"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="E2:L4"/>
+    <mergeCell ref="E5:L5"/>
+    <mergeCell ref="E6:L6"/>
+    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="I7:L7"/>
+    <mergeCell ref="F13:H14"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="I23:L23"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="F12:H12"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="K17:L17"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
